--- a/PNL.xlsx
+++ b/PNL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/apple/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B89E46D-50FF-634B-941D-D7F6C7FC5F6A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C7D211A-37C8-8B49-9342-18478B726A8B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16180" xr2:uid="{06C2047E-A20D-7B41-A100-9F165F6715E9}"/>
   </bookViews>
@@ -11580,7 +11580,7 @@
         <v>0</v>
       </c>
       <c r="C903" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D903" s="1"/>
     </row>
@@ -11592,7 +11592,7 @@
         <v>0</v>
       </c>
       <c r="C904" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D904" s="1"/>
     </row>
@@ -11604,7 +11604,7 @@
         <v>0</v>
       </c>
       <c r="C905" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D905" s="1"/>
     </row>
@@ -11616,7 +11616,7 @@
         <v>0</v>
       </c>
       <c r="C906" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D906" s="1"/>
     </row>
@@ -11628,7 +11628,7 @@
         <v>0</v>
       </c>
       <c r="C907" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D907" s="1"/>
     </row>
@@ -11640,7 +11640,7 @@
         <v>0</v>
       </c>
       <c r="C908" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D908" s="1"/>
     </row>
@@ -11652,7 +11652,7 @@
         <v>0</v>
       </c>
       <c r="C909" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D909" s="1"/>
     </row>
@@ -11664,7 +11664,7 @@
         <v>0</v>
       </c>
       <c r="C910" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D910" s="1"/>
     </row>
@@ -11676,7 +11676,7 @@
         <v>0</v>
       </c>
       <c r="C911" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D911" s="1"/>
     </row>
@@ -11688,7 +11688,7 @@
         <v>0</v>
       </c>
       <c r="C912" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D912" s="1"/>
     </row>
@@ -11700,7 +11700,7 @@
         <v>0</v>
       </c>
       <c r="C913" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D913" s="1"/>
     </row>
@@ -11712,7 +11712,7 @@
         <v>0</v>
       </c>
       <c r="C914" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D914" s="1"/>
     </row>
@@ -11724,7 +11724,7 @@
         <v>0</v>
       </c>
       <c r="C915" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D915" s="1"/>
     </row>
@@ -11736,7 +11736,7 @@
         <v>0</v>
       </c>
       <c r="C916" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D916" s="1"/>
     </row>
@@ -11748,7 +11748,7 @@
         <v>0</v>
       </c>
       <c r="C917" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D917" s="1"/>
     </row>
@@ -11760,7 +11760,7 @@
         <v>0</v>
       </c>
       <c r="C918" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D918" s="1"/>
     </row>
@@ -11772,7 +11772,7 @@
         <v>0</v>
       </c>
       <c r="C919" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D919" s="1"/>
     </row>
@@ -11784,7 +11784,7 @@
         <v>0</v>
       </c>
       <c r="C920" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D920" s="1"/>
     </row>
@@ -11796,7 +11796,7 @@
         <v>0</v>
       </c>
       <c r="C921" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D921" s="1"/>
     </row>
@@ -11808,7 +11808,7 @@
         <v>0</v>
       </c>
       <c r="C922" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D922" s="1"/>
     </row>
@@ -11820,7 +11820,7 @@
         <v>0</v>
       </c>
       <c r="C923" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D923" s="1"/>
     </row>
@@ -11832,7 +11832,7 @@
         <v>0</v>
       </c>
       <c r="C924" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D924" s="1"/>
     </row>
@@ -11844,7 +11844,7 @@
         <v>0</v>
       </c>
       <c r="C925" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D925" s="1"/>
     </row>
@@ -11856,7 +11856,7 @@
         <v>0</v>
       </c>
       <c r="C926" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D926" s="1"/>
     </row>
@@ -11868,7 +11868,7 @@
         <v>0</v>
       </c>
       <c r="C927" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D927" s="1"/>
     </row>
@@ -11880,7 +11880,7 @@
         <v>0</v>
       </c>
       <c r="C928" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D928" s="1"/>
     </row>
@@ -11892,7 +11892,7 @@
         <v>0</v>
       </c>
       <c r="C929" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D929" s="1"/>
     </row>
@@ -11904,7 +11904,7 @@
         <v>0</v>
       </c>
       <c r="C930" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D930" s="1"/>
     </row>
@@ -11916,7 +11916,7 @@
         <v>0</v>
       </c>
       <c r="C931" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D931" s="1"/>
     </row>
@@ -11928,7 +11928,7 @@
         <v>0</v>
       </c>
       <c r="C932" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D932" s="1"/>
     </row>
@@ -11940,7 +11940,7 @@
         <v>0</v>
       </c>
       <c r="C933" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D933" s="1"/>
     </row>
@@ -11952,7 +11952,7 @@
         <v>0</v>
       </c>
       <c r="C934" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D934" s="1"/>
     </row>
@@ -11964,7 +11964,7 @@
         <v>0</v>
       </c>
       <c r="C935" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D935" s="1"/>
     </row>
@@ -11976,7 +11976,7 @@
         <v>0</v>
       </c>
       <c r="C936" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D936" s="1"/>
     </row>
@@ -11988,7 +11988,7 @@
         <v>0</v>
       </c>
       <c r="C937" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D937" s="1"/>
     </row>
@@ -12000,7 +12000,7 @@
         <v>0</v>
       </c>
       <c r="C938" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D938" s="1"/>
     </row>
@@ -12012,7 +12012,7 @@
         <v>0</v>
       </c>
       <c r="C939" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D939" s="1"/>
     </row>
@@ -12024,7 +12024,7 @@
         <v>0</v>
       </c>
       <c r="C940" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D940" s="1"/>
     </row>
@@ -12036,7 +12036,7 @@
         <v>0</v>
       </c>
       <c r="C941" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D941" s="1"/>
     </row>
@@ -12048,7 +12048,7 @@
         <v>0</v>
       </c>
       <c r="C942" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D942" s="1"/>
     </row>
@@ -12060,7 +12060,7 @@
         <v>0</v>
       </c>
       <c r="C943" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D943" s="1"/>
     </row>
@@ -12072,7 +12072,7 @@
         <v>0</v>
       </c>
       <c r="C944" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D944" s="1"/>
     </row>
@@ -12084,7 +12084,7 @@
         <v>0</v>
       </c>
       <c r="C945" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D945" s="1"/>
     </row>
@@ -12096,7 +12096,7 @@
         <v>0</v>
       </c>
       <c r="C946" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D946" s="1"/>
     </row>
@@ -12108,7 +12108,7 @@
         <v>0</v>
       </c>
       <c r="C947" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D947" s="1"/>
     </row>
@@ -12120,7 +12120,7 @@
         <v>0</v>
       </c>
       <c r="C948" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D948" s="1"/>
     </row>
@@ -12132,7 +12132,7 @@
         <v>0</v>
       </c>
       <c r="C949" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D949" s="1"/>
     </row>
@@ -12144,7 +12144,7 @@
         <v>0</v>
       </c>
       <c r="C950" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D950" s="1"/>
     </row>
@@ -12156,7 +12156,7 @@
         <v>0</v>
       </c>
       <c r="C951" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D951" s="1"/>
     </row>
@@ -12168,7 +12168,7 @@
         <v>0</v>
       </c>
       <c r="C952" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D952" s="1"/>
     </row>
@@ -12180,7 +12180,7 @@
         <v>0</v>
       </c>
       <c r="C953" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D953" s="1"/>
     </row>
@@ -12192,7 +12192,7 @@
         <v>0</v>
       </c>
       <c r="C954" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D954" s="1"/>
     </row>
@@ -12204,7 +12204,7 @@
         <v>0</v>
       </c>
       <c r="C955" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D955" s="1"/>
     </row>
@@ -12216,7 +12216,7 @@
         <v>0</v>
       </c>
       <c r="C956" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D956" s="1"/>
     </row>
@@ -12228,7 +12228,7 @@
         <v>0</v>
       </c>
       <c r="C957" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D957" s="1"/>
     </row>
@@ -12240,7 +12240,7 @@
         <v>0</v>
       </c>
       <c r="C958" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D958" s="1"/>
     </row>
@@ -12252,7 +12252,7 @@
         <v>0</v>
       </c>
       <c r="C959" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D959" s="1"/>
     </row>
@@ -12264,7 +12264,7 @@
         <v>0</v>
       </c>
       <c r="C960" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D960" s="1"/>
     </row>
@@ -12276,7 +12276,7 @@
         <v>0</v>
       </c>
       <c r="C961" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D961" s="1"/>
     </row>
@@ -12288,7 +12288,7 @@
         <v>0</v>
       </c>
       <c r="C962" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D962" s="1"/>
     </row>
@@ -12300,7 +12300,7 @@
         <v>0</v>
       </c>
       <c r="C963" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D963" s="1"/>
     </row>
@@ -12312,7 +12312,7 @@
         <v>0</v>
       </c>
       <c r="C964" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D964" s="1"/>
     </row>
@@ -12324,7 +12324,7 @@
         <v>0</v>
       </c>
       <c r="C965" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D965" s="1"/>
     </row>
@@ -12336,7 +12336,7 @@
         <v>0</v>
       </c>
       <c r="C966" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D966" s="1"/>
     </row>
@@ -12348,7 +12348,7 @@
         <v>0</v>
       </c>
       <c r="C967" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D967" s="1"/>
     </row>
@@ -12360,7 +12360,7 @@
         <v>0</v>
       </c>
       <c r="C968" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D968" s="1"/>
     </row>
@@ -12372,7 +12372,7 @@
         <v>0</v>
       </c>
       <c r="C969" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D969" s="1"/>
     </row>
@@ -12384,7 +12384,7 @@
         <v>0</v>
       </c>
       <c r="C970" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D970" s="1"/>
     </row>
@@ -12396,7 +12396,7 @@
         <v>0</v>
       </c>
       <c r="C971" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D971" s="1"/>
     </row>
@@ -12408,7 +12408,7 @@
         <v>0</v>
       </c>
       <c r="C972" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D972" s="1"/>
     </row>
@@ -12420,7 +12420,7 @@
         <v>0</v>
       </c>
       <c r="C973" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D973" s="1"/>
     </row>
@@ -12432,7 +12432,7 @@
         <v>0</v>
       </c>
       <c r="C974" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D974" s="1"/>
     </row>
@@ -12444,7 +12444,7 @@
         <v>0</v>
       </c>
       <c r="C975" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D975" s="1"/>
     </row>
@@ -12456,7 +12456,7 @@
         <v>0</v>
       </c>
       <c r="C976" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D976" s="1"/>
     </row>
@@ -12468,7 +12468,7 @@
         <v>0</v>
       </c>
       <c r="C977" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D977" s="1"/>
     </row>
@@ -12480,7 +12480,7 @@
         <v>0</v>
       </c>
       <c r="C978" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D978" s="1"/>
     </row>
@@ -12492,7 +12492,7 @@
         <v>0</v>
       </c>
       <c r="C979" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D979" s="1"/>
     </row>
@@ -12504,7 +12504,7 @@
         <v>0</v>
       </c>
       <c r="C980" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D980" s="1"/>
     </row>
@@ -12516,7 +12516,7 @@
         <v>0</v>
       </c>
       <c r="C981" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D981" s="1"/>
     </row>
@@ -12528,7 +12528,7 @@
         <v>0</v>
       </c>
       <c r="C982" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D982" s="1"/>
     </row>
@@ -12540,7 +12540,7 @@
         <v>0</v>
       </c>
       <c r="C983" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D983" s="1"/>
     </row>
@@ -12552,7 +12552,7 @@
         <v>0</v>
       </c>
       <c r="C984" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D984" s="1"/>
     </row>
@@ -12564,7 +12564,7 @@
         <v>0</v>
       </c>
       <c r="C985" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D985" s="1"/>
     </row>
@@ -12576,7 +12576,7 @@
         <v>0</v>
       </c>
       <c r="C986" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D986" s="1"/>
     </row>
@@ -12588,7 +12588,7 @@
         <v>0</v>
       </c>
       <c r="C987" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D987" s="1"/>
     </row>
@@ -12600,7 +12600,7 @@
         <v>0</v>
       </c>
       <c r="C988" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D988" s="1"/>
     </row>
@@ -12612,7 +12612,7 @@
         <v>0</v>
       </c>
       <c r="C989" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D989" s="1"/>
     </row>
@@ -12624,7 +12624,7 @@
         <v>0</v>
       </c>
       <c r="C990" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D990" s="1"/>
     </row>
@@ -12636,7 +12636,7 @@
         <v>0</v>
       </c>
       <c r="C991" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D991" s="1"/>
     </row>
@@ -12648,7 +12648,7 @@
         <v>0</v>
       </c>
       <c r="C992" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D992" s="1"/>
     </row>
@@ -12660,7 +12660,7 @@
         <v>0</v>
       </c>
       <c r="C993" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D993" s="1"/>
     </row>
@@ -12672,7 +12672,7 @@
         <v>0</v>
       </c>
       <c r="C994" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D994" s="1"/>
     </row>
@@ -12684,7 +12684,7 @@
         <v>0</v>
       </c>
       <c r="C995" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D995" s="1"/>
     </row>
@@ -12696,7 +12696,7 @@
         <v>0</v>
       </c>
       <c r="C996" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D996" s="1"/>
     </row>
@@ -12708,7 +12708,7 @@
         <v>0</v>
       </c>
       <c r="C997" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D997" s="1"/>
     </row>
@@ -12720,7 +12720,7 @@
         <v>0</v>
       </c>
       <c r="C998" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D998" s="1"/>
     </row>
@@ -12732,7 +12732,7 @@
         <v>0</v>
       </c>
       <c r="C999" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D999" s="1"/>
     </row>
@@ -12744,7 +12744,7 @@
         <v>0</v>
       </c>
       <c r="C1000" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1000" s="1"/>
     </row>
@@ -12756,7 +12756,7 @@
         <v>0</v>
       </c>
       <c r="C1001" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1001" s="1"/>
     </row>
@@ -12768,7 +12768,7 @@
         <v>0</v>
       </c>
       <c r="C1002" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1002" s="1"/>
     </row>
@@ -12780,7 +12780,7 @@
         <v>0</v>
       </c>
       <c r="C1003" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1003" s="1"/>
     </row>
@@ -12792,7 +12792,7 @@
         <v>0</v>
       </c>
       <c r="C1004" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1004" s="1"/>
     </row>
@@ -12804,7 +12804,7 @@
         <v>0</v>
       </c>
       <c r="C1005" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1005" s="1"/>
     </row>
@@ -12816,7 +12816,7 @@
         <v>0</v>
       </c>
       <c r="C1006" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1006" s="1"/>
     </row>
@@ -12828,7 +12828,7 @@
         <v>0</v>
       </c>
       <c r="C1007" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1007" s="1"/>
     </row>
@@ -12840,7 +12840,7 @@
         <v>0</v>
       </c>
       <c r="C1008" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1008" s="1"/>
     </row>
@@ -12852,7 +12852,7 @@
         <v>0</v>
       </c>
       <c r="C1009" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1009" s="1"/>
     </row>
@@ -12864,7 +12864,7 @@
         <v>0</v>
       </c>
       <c r="C1010" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1010" s="1"/>
     </row>
@@ -12876,7 +12876,7 @@
         <v>0</v>
       </c>
       <c r="C1011" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1011" s="1"/>
     </row>
@@ -12888,7 +12888,7 @@
         <v>0</v>
       </c>
       <c r="C1012" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1012" s="1"/>
     </row>
@@ -12900,7 +12900,7 @@
         <v>0</v>
       </c>
       <c r="C1013" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1013" s="1"/>
     </row>
@@ -12912,7 +12912,7 @@
         <v>0</v>
       </c>
       <c r="C1014" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1014" s="1"/>
     </row>
@@ -12924,7 +12924,7 @@
         <v>0</v>
       </c>
       <c r="C1015" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1015" s="1"/>
     </row>
@@ -12936,7 +12936,7 @@
         <v>0</v>
       </c>
       <c r="C1016" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1016" s="1"/>
     </row>
@@ -12948,7 +12948,7 @@
         <v>0</v>
       </c>
       <c r="C1017" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1017" s="1"/>
     </row>
@@ -12960,7 +12960,7 @@
         <v>0</v>
       </c>
       <c r="C1018" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1018" s="1"/>
     </row>
@@ -12972,7 +12972,7 @@
         <v>0</v>
       </c>
       <c r="C1019" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1019" s="1"/>
     </row>
@@ -12984,7 +12984,7 @@
         <v>0</v>
       </c>
       <c r="C1020" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1020" s="1"/>
     </row>
@@ -12996,7 +12996,7 @@
         <v>0</v>
       </c>
       <c r="C1021" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1021" s="1"/>
     </row>
@@ -13008,7 +13008,7 @@
         <v>0</v>
       </c>
       <c r="C1022" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1022" s="1"/>
     </row>
@@ -13020,7 +13020,7 @@
         <v>0</v>
       </c>
       <c r="C1023" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1023" s="1"/>
     </row>
@@ -13032,7 +13032,7 @@
         <v>0</v>
       </c>
       <c r="C1024" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1024" s="1"/>
     </row>
@@ -13044,7 +13044,7 @@
         <v>0</v>
       </c>
       <c r="C1025" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1025" s="1"/>
     </row>
@@ -13056,7 +13056,7 @@
         <v>0</v>
       </c>
       <c r="C1026" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1026" s="1"/>
     </row>
@@ -13068,7 +13068,7 @@
         <v>0</v>
       </c>
       <c r="C1027" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1027" s="1"/>
     </row>
@@ -13080,7 +13080,7 @@
         <v>0</v>
       </c>
       <c r="C1028" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1028" s="1"/>
     </row>
@@ -13092,7 +13092,7 @@
         <v>0</v>
       </c>
       <c r="C1029" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1029" s="1"/>
     </row>
@@ -13104,7 +13104,7 @@
         <v>0</v>
       </c>
       <c r="C1030" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1030" s="1"/>
     </row>
@@ -13116,7 +13116,7 @@
         <v>0</v>
       </c>
       <c r="C1031" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1031" s="1"/>
     </row>
@@ -13128,7 +13128,7 @@
         <v>0</v>
       </c>
       <c r="C1032" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1032" s="1"/>
     </row>
@@ -13140,7 +13140,7 @@
         <v>0</v>
       </c>
       <c r="C1033" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1033" s="1"/>
     </row>
@@ -13152,7 +13152,7 @@
         <v>0</v>
       </c>
       <c r="C1034" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1034" s="1"/>
     </row>
@@ -13164,7 +13164,7 @@
         <v>0</v>
       </c>
       <c r="C1035" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1035" s="1"/>
     </row>
@@ -13176,7 +13176,7 @@
         <v>0</v>
       </c>
       <c r="C1036" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1036" s="1"/>
     </row>
@@ -13188,7 +13188,7 @@
         <v>0</v>
       </c>
       <c r="C1037" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1037" s="1"/>
     </row>
@@ -13200,7 +13200,7 @@
         <v>0</v>
       </c>
       <c r="C1038" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1038" s="1"/>
     </row>
@@ -13212,7 +13212,7 @@
         <v>0</v>
       </c>
       <c r="C1039" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1039" s="1"/>
     </row>
@@ -13224,7 +13224,7 @@
         <v>0</v>
       </c>
       <c r="C1040" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1040" s="1"/>
     </row>
@@ -13236,7 +13236,7 @@
         <v>0</v>
       </c>
       <c r="C1041" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1041" s="1"/>
     </row>
@@ -13248,7 +13248,7 @@
         <v>0</v>
       </c>
       <c r="C1042" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1042" s="1"/>
     </row>
@@ -13260,7 +13260,7 @@
         <v>0</v>
       </c>
       <c r="C1043" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1043" s="1"/>
     </row>
@@ -13272,7 +13272,7 @@
         <v>0</v>
       </c>
       <c r="C1044" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1044" s="1"/>
     </row>
@@ -13284,7 +13284,7 @@
         <v>0</v>
       </c>
       <c r="C1045" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1045" s="1"/>
     </row>
@@ -13296,7 +13296,7 @@
         <v>0</v>
       </c>
       <c r="C1046" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1046" s="1"/>
     </row>
@@ -13308,7 +13308,7 @@
         <v>0</v>
       </c>
       <c r="C1047" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1047" s="1"/>
     </row>
@@ -13320,7 +13320,7 @@
         <v>0</v>
       </c>
       <c r="C1048" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1048" s="1"/>
     </row>
@@ -13332,7 +13332,7 @@
         <v>0</v>
       </c>
       <c r="C1049" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1049" s="1"/>
     </row>
@@ -13344,7 +13344,7 @@
         <v>0</v>
       </c>
       <c r="C1050" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1050" s="1"/>
     </row>
@@ -13356,7 +13356,7 @@
         <v>0</v>
       </c>
       <c r="C1051" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1051" s="1"/>
     </row>
@@ -13368,7 +13368,7 @@
         <v>0</v>
       </c>
       <c r="C1052" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1052" s="1"/>
     </row>
@@ -13380,7 +13380,7 @@
         <v>0</v>
       </c>
       <c r="C1053" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1053" s="1"/>
     </row>
@@ -13392,7 +13392,7 @@
         <v>0</v>
       </c>
       <c r="C1054" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1054" s="1"/>
     </row>
@@ -13404,7 +13404,7 @@
         <v>0</v>
       </c>
       <c r="C1055" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1055" s="1"/>
     </row>
@@ -13416,7 +13416,7 @@
         <v>0</v>
       </c>
       <c r="C1056" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1056" s="1"/>
     </row>
@@ -13428,7 +13428,7 @@
         <v>0</v>
       </c>
       <c r="C1057" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1057" s="1"/>
     </row>
@@ -13440,7 +13440,7 @@
         <v>0</v>
       </c>
       <c r="C1058" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1058" s="1"/>
     </row>
@@ -13452,7 +13452,7 @@
         <v>0</v>
       </c>
       <c r="C1059" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1059" s="1"/>
     </row>
@@ -13464,7 +13464,7 @@
         <v>0</v>
       </c>
       <c r="C1060" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1060" s="1"/>
     </row>
@@ -13476,7 +13476,7 @@
         <v>0</v>
       </c>
       <c r="C1061" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1061" s="1"/>
     </row>
@@ -13488,7 +13488,7 @@
         <v>0</v>
       </c>
       <c r="C1062" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1062" s="1"/>
     </row>
@@ -13500,7 +13500,7 @@
         <v>0</v>
       </c>
       <c r="C1063" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1063" s="1"/>
     </row>
@@ -13512,7 +13512,7 @@
         <v>0</v>
       </c>
       <c r="C1064" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1064" s="1"/>
     </row>
@@ -13524,7 +13524,7 @@
         <v>0</v>
       </c>
       <c r="C1065" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1065" s="1"/>
     </row>
@@ -13536,7 +13536,7 @@
         <v>0</v>
       </c>
       <c r="C1066" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1066" s="1"/>
     </row>
@@ -13548,7 +13548,7 @@
         <v>0</v>
       </c>
       <c r="C1067" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1067" s="1"/>
     </row>
@@ -13560,7 +13560,7 @@
         <v>0</v>
       </c>
       <c r="C1068" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1068" s="1"/>
     </row>
@@ -13572,7 +13572,7 @@
         <v>0</v>
       </c>
       <c r="C1069" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1069" s="1"/>
     </row>
@@ -13584,7 +13584,7 @@
         <v>0</v>
       </c>
       <c r="C1070" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1070" s="1"/>
     </row>
@@ -13596,7 +13596,7 @@
         <v>0</v>
       </c>
       <c r="C1071" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1071" s="1"/>
     </row>
@@ -13608,7 +13608,7 @@
         <v>0</v>
       </c>
       <c r="C1072" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1072" s="1"/>
     </row>
@@ -13620,7 +13620,7 @@
         <v>0</v>
       </c>
       <c r="C1073" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1073" s="1"/>
     </row>
@@ -13632,7 +13632,7 @@
         <v>0</v>
       </c>
       <c r="C1074" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1074" s="1"/>
     </row>
@@ -13644,7 +13644,7 @@
         <v>0</v>
       </c>
       <c r="C1075" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1075" s="1"/>
     </row>
@@ -13656,7 +13656,7 @@
         <v>0</v>
       </c>
       <c r="C1076" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1076" s="1"/>
     </row>
@@ -13668,7 +13668,7 @@
         <v>0</v>
       </c>
       <c r="C1077" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1077" s="1"/>
     </row>
@@ -13680,7 +13680,7 @@
         <v>0</v>
       </c>
       <c r="C1078" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1078" s="1"/>
     </row>
@@ -13692,7 +13692,7 @@
         <v>0</v>
       </c>
       <c r="C1079" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1079" s="1"/>
     </row>
@@ -13704,7 +13704,7 @@
         <v>0</v>
       </c>
       <c r="C1080" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1080" s="1"/>
     </row>
@@ -13716,7 +13716,7 @@
         <v>0</v>
       </c>
       <c r="C1081" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1081" s="1"/>
     </row>
@@ -13728,7 +13728,7 @@
         <v>0</v>
       </c>
       <c r="C1082" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1082" s="1"/>
     </row>
@@ -13740,7 +13740,7 @@
         <v>0</v>
       </c>
       <c r="C1083" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1083" s="1"/>
     </row>
@@ -13752,7 +13752,7 @@
         <v>0</v>
       </c>
       <c r="C1084" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1084" s="1"/>
     </row>
@@ -13764,7 +13764,7 @@
         <v>0</v>
       </c>
       <c r="C1085" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1085" s="1"/>
     </row>
@@ -13776,7 +13776,7 @@
         <v>0</v>
       </c>
       <c r="C1086" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1086" s="1"/>
     </row>
@@ -13788,7 +13788,7 @@
         <v>0</v>
       </c>
       <c r="C1087" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1087" s="1"/>
     </row>
@@ -13800,7 +13800,7 @@
         <v>0</v>
       </c>
       <c r="C1088" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1088" s="1"/>
     </row>
@@ -13812,7 +13812,7 @@
         <v>0</v>
       </c>
       <c r="C1089" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1089" s="1"/>
     </row>
@@ -13824,7 +13824,7 @@
         <v>0</v>
       </c>
       <c r="C1090" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1090" s="1"/>
     </row>
@@ -13836,7 +13836,7 @@
         <v>0</v>
       </c>
       <c r="C1091" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1091" s="1"/>
     </row>
@@ -13848,7 +13848,7 @@
         <v>0</v>
       </c>
       <c r="C1092" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1092" s="1"/>
     </row>
@@ -13860,7 +13860,7 @@
         <v>0</v>
       </c>
       <c r="C1093" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1093" s="1"/>
     </row>
@@ -13872,7 +13872,7 @@
         <v>0</v>
       </c>
       <c r="C1094" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1094" s="1"/>
     </row>
@@ -13884,7 +13884,7 @@
         <v>0</v>
       </c>
       <c r="C1095" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1095" s="1"/>
     </row>
@@ -13896,7 +13896,7 @@
         <v>0</v>
       </c>
       <c r="C1096" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1096" s="1"/>
     </row>
@@ -13908,7 +13908,7 @@
         <v>0</v>
       </c>
       <c r="C1097" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1097" s="1"/>
     </row>
@@ -13920,7 +13920,7 @@
         <v>0</v>
       </c>
       <c r="C1098" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1098" s="1"/>
     </row>
@@ -13932,7 +13932,7 @@
         <v>0</v>
       </c>
       <c r="C1099" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1099" s="1"/>
     </row>
@@ -13944,7 +13944,7 @@
         <v>0</v>
       </c>
       <c r="C1100" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1100" s="1"/>
     </row>
@@ -13956,7 +13956,7 @@
         <v>0</v>
       </c>
       <c r="C1101" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1101" s="1"/>
     </row>
@@ -13968,7 +13968,7 @@
         <v>0</v>
       </c>
       <c r="C1102" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1102" s="1"/>
     </row>
@@ -13980,7 +13980,7 @@
         <v>0</v>
       </c>
       <c r="C1103" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1103" s="1"/>
     </row>
@@ -13992,7 +13992,7 @@
         <v>0</v>
       </c>
       <c r="C1104" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1104" s="1"/>
     </row>
@@ -14004,7 +14004,7 @@
         <v>0</v>
       </c>
       <c r="C1105" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1105" s="1"/>
     </row>
@@ -14016,7 +14016,7 @@
         <v>0</v>
       </c>
       <c r="C1106" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1106" s="1"/>
     </row>
@@ -14028,7 +14028,7 @@
         <v>0</v>
       </c>
       <c r="C1107" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1107" s="1"/>
     </row>
@@ -14040,7 +14040,7 @@
         <v>0</v>
       </c>
       <c r="C1108" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1108" s="1"/>
     </row>
@@ -14052,7 +14052,7 @@
         <v>0</v>
       </c>
       <c r="C1109" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1109" s="1"/>
     </row>
@@ -14064,7 +14064,7 @@
         <v>0</v>
       </c>
       <c r="C1110" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1110" s="1"/>
     </row>
@@ -14076,7 +14076,7 @@
         <v>0</v>
       </c>
       <c r="C1111" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1111" s="1"/>
     </row>
@@ -14088,7 +14088,7 @@
         <v>0</v>
       </c>
       <c r="C1112" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1112" s="1"/>
     </row>
@@ -14100,7 +14100,7 @@
         <v>0</v>
       </c>
       <c r="C1113" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1113" s="1"/>
     </row>
@@ -14112,7 +14112,7 @@
         <v>0</v>
       </c>
       <c r="C1114" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1114" s="1"/>
     </row>
@@ -14124,7 +14124,7 @@
         <v>0</v>
       </c>
       <c r="C1115" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1115" s="1"/>
     </row>
@@ -14136,7 +14136,7 @@
         <v>0</v>
       </c>
       <c r="C1116" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1116" s="1"/>
     </row>
@@ -14148,7 +14148,7 @@
         <v>0</v>
       </c>
       <c r="C1117" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1117" s="1"/>
     </row>
@@ -14160,7 +14160,7 @@
         <v>0</v>
       </c>
       <c r="C1118" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1118" s="1"/>
     </row>
@@ -14172,7 +14172,7 @@
         <v>0</v>
       </c>
       <c r="C1119" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1119" s="1"/>
     </row>
@@ -14184,7 +14184,7 @@
         <v>0</v>
       </c>
       <c r="C1120" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1120" s="1"/>
     </row>
@@ -14196,7 +14196,7 @@
         <v>0</v>
       </c>
       <c r="C1121" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1121" s="1"/>
     </row>
@@ -14208,7 +14208,7 @@
         <v>0</v>
       </c>
       <c r="C1122" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1122" s="1"/>
     </row>
@@ -14220,7 +14220,7 @@
         <v>0</v>
       </c>
       <c r="C1123" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1123" s="1"/>
     </row>
@@ -14232,7 +14232,7 @@
         <v>0</v>
       </c>
       <c r="C1124" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1124" s="1"/>
     </row>
@@ -14244,7 +14244,7 @@
         <v>0</v>
       </c>
       <c r="C1125" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1125" s="1"/>
     </row>
@@ -14256,7 +14256,7 @@
         <v>0</v>
       </c>
       <c r="C1126" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1126" s="1"/>
     </row>
@@ -14268,7 +14268,7 @@
         <v>0</v>
       </c>
       <c r="C1127" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1127" s="1"/>
     </row>
@@ -14280,7 +14280,7 @@
         <v>0</v>
       </c>
       <c r="C1128" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1128" s="1"/>
     </row>
@@ -14292,7 +14292,7 @@
         <v>0</v>
       </c>
       <c r="C1129" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1129" s="1"/>
     </row>
@@ -14304,7 +14304,7 @@
         <v>0</v>
       </c>
       <c r="C1130" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1130" s="1"/>
     </row>
@@ -14316,7 +14316,7 @@
         <v>0</v>
       </c>
       <c r="C1131" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1131" s="1"/>
     </row>
@@ -14328,7 +14328,7 @@
         <v>0</v>
       </c>
       <c r="C1132" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1132" s="1"/>
     </row>
@@ -14340,7 +14340,7 @@
         <v>0</v>
       </c>
       <c r="C1133" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1133" s="1"/>
     </row>
@@ -14352,7 +14352,7 @@
         <v>0</v>
       </c>
       <c r="C1134" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1134" s="1"/>
     </row>
@@ -14364,7 +14364,7 @@
         <v>0</v>
       </c>
       <c r="C1135" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1135" s="1"/>
     </row>
@@ -14376,7 +14376,7 @@
         <v>0</v>
       </c>
       <c r="C1136" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1136" s="1"/>
     </row>
@@ -14388,7 +14388,7 @@
         <v>0</v>
       </c>
       <c r="C1137" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1137" s="1"/>
     </row>
@@ -14400,7 +14400,7 @@
         <v>0</v>
       </c>
       <c r="C1138" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1138" s="1"/>
     </row>
@@ -14412,7 +14412,7 @@
         <v>0</v>
       </c>
       <c r="C1139" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1139" s="1"/>
     </row>
@@ -14424,7 +14424,7 @@
         <v>0</v>
       </c>
       <c r="C1140" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1140" s="1"/>
     </row>
@@ -14436,7 +14436,7 @@
         <v>0</v>
       </c>
       <c r="C1141" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1141" s="1"/>
     </row>
@@ -14448,7 +14448,7 @@
         <v>0</v>
       </c>
       <c r="C1142" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1142" s="1"/>
     </row>
@@ -14460,7 +14460,7 @@
         <v>0</v>
       </c>
       <c r="C1143" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1143" s="1"/>
     </row>
@@ -14472,7 +14472,7 @@
         <v>0</v>
       </c>
       <c r="C1144" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1144" s="1"/>
     </row>
@@ -14484,7 +14484,7 @@
         <v>0</v>
       </c>
       <c r="C1145" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1145" s="1"/>
     </row>
@@ -14496,7 +14496,7 @@
         <v>0</v>
       </c>
       <c r="C1146" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1146" s="1"/>
     </row>
@@ -14508,7 +14508,7 @@
         <v>0</v>
       </c>
       <c r="C1147" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1147" s="1"/>
     </row>
@@ -14520,7 +14520,7 @@
         <v>0</v>
       </c>
       <c r="C1148" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1148" s="1"/>
     </row>
@@ -14532,7 +14532,7 @@
         <v>0</v>
       </c>
       <c r="C1149" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1149" s="1"/>
     </row>
@@ -14544,7 +14544,7 @@
         <v>0</v>
       </c>
       <c r="C1150" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1150" s="1"/>
     </row>
@@ -14556,7 +14556,7 @@
         <v>0</v>
       </c>
       <c r="C1151" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1151" s="1"/>
     </row>
@@ -14568,7 +14568,7 @@
         <v>0</v>
       </c>
       <c r="C1152" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1152" s="1"/>
     </row>
@@ -14580,7 +14580,7 @@
         <v>0</v>
       </c>
       <c r="C1153" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1153" s="1"/>
     </row>
@@ -14592,7 +14592,7 @@
         <v>0</v>
       </c>
       <c r="C1154" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1154" s="1"/>
     </row>
@@ -14604,7 +14604,7 @@
         <v>0</v>
       </c>
       <c r="C1155" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1155" s="1"/>
     </row>
@@ -14616,7 +14616,7 @@
         <v>0</v>
       </c>
       <c r="C1156" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1156" s="1"/>
     </row>
@@ -14628,7 +14628,7 @@
         <v>0</v>
       </c>
       <c r="C1157" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1157" s="1"/>
     </row>
@@ -14640,7 +14640,7 @@
         <v>0</v>
       </c>
       <c r="C1158" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1158" s="1"/>
     </row>
@@ -14652,7 +14652,7 @@
         <v>0</v>
       </c>
       <c r="C1159" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1159" s="1"/>
     </row>
@@ -14664,7 +14664,7 @@
         <v>0</v>
       </c>
       <c r="C1160" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1160" s="1"/>
     </row>
@@ -14676,7 +14676,7 @@
         <v>0</v>
       </c>
       <c r="C1161" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1161" s="1"/>
     </row>
@@ -14688,7 +14688,7 @@
         <v>0</v>
       </c>
       <c r="C1162" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1162" s="1"/>
     </row>
@@ -14700,7 +14700,7 @@
         <v>0</v>
       </c>
       <c r="C1163" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1163" s="1"/>
     </row>
@@ -14712,7 +14712,7 @@
         <v>0</v>
       </c>
       <c r="C1164" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1164" s="1"/>
     </row>
@@ -14724,7 +14724,7 @@
         <v>0</v>
       </c>
       <c r="C1165" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1165" s="1"/>
     </row>
@@ -14736,7 +14736,7 @@
         <v>0</v>
       </c>
       <c r="C1166" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1166" s="1"/>
     </row>
@@ -14748,7 +14748,7 @@
         <v>0</v>
       </c>
       <c r="C1167" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1167" s="1"/>
     </row>
@@ -14760,7 +14760,7 @@
         <v>0</v>
       </c>
       <c r="C1168" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1168" s="1"/>
     </row>
@@ -14772,7 +14772,7 @@
         <v>0</v>
       </c>
       <c r="C1169" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1169" s="1"/>
     </row>
@@ -14784,7 +14784,7 @@
         <v>0</v>
       </c>
       <c r="C1170" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1170" s="1"/>
     </row>
@@ -14796,7 +14796,7 @@
         <v>0</v>
       </c>
       <c r="C1171" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1171" s="1"/>
     </row>
@@ -14808,7 +14808,7 @@
         <v>0</v>
       </c>
       <c r="C1172" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1172" s="1"/>
     </row>
@@ -14820,7 +14820,7 @@
         <v>0</v>
       </c>
       <c r="C1173" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1173" s="1"/>
     </row>
@@ -14832,7 +14832,7 @@
         <v>0</v>
       </c>
       <c r="C1174" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1174" s="1"/>
     </row>
@@ -14844,7 +14844,7 @@
         <v>0</v>
       </c>
       <c r="C1175" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1175" s="1"/>
     </row>
@@ -14856,7 +14856,7 @@
         <v>0</v>
       </c>
       <c r="C1176" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1176" s="1"/>
     </row>
@@ -14868,7 +14868,7 @@
         <v>0</v>
       </c>
       <c r="C1177" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1177" s="1"/>
     </row>
@@ -14880,7 +14880,7 @@
         <v>0</v>
       </c>
       <c r="C1178" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1178" s="1"/>
     </row>
@@ -14892,7 +14892,7 @@
         <v>0</v>
       </c>
       <c r="C1179" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1179" s="1"/>
     </row>
@@ -14904,7 +14904,7 @@
         <v>0</v>
       </c>
       <c r="C1180" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1180" s="1"/>
     </row>
@@ -14916,7 +14916,7 @@
         <v>0</v>
       </c>
       <c r="C1181" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1181" s="1"/>
     </row>
@@ -14928,7 +14928,7 @@
         <v>0</v>
       </c>
       <c r="C1182" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1182" s="1"/>
     </row>
@@ -14940,7 +14940,7 @@
         <v>0</v>
       </c>
       <c r="C1183" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1183" s="1"/>
     </row>
@@ -14952,7 +14952,7 @@
         <v>0</v>
       </c>
       <c r="C1184" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1184" s="1"/>
     </row>
@@ -14964,7 +14964,7 @@
         <v>0</v>
       </c>
       <c r="C1185" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1185" s="1"/>
     </row>
@@ -14976,7 +14976,7 @@
         <v>0</v>
       </c>
       <c r="C1186" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1186" s="1"/>
     </row>
@@ -14988,7 +14988,7 @@
         <v>0</v>
       </c>
       <c r="C1187" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1187" s="1"/>
     </row>
@@ -15000,7 +15000,7 @@
         <v>0</v>
       </c>
       <c r="C1188" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1188" s="1"/>
     </row>
@@ -15012,7 +15012,7 @@
         <v>0</v>
       </c>
       <c r="C1189" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1189" s="1"/>
     </row>
@@ -15024,7 +15024,7 @@
         <v>0</v>
       </c>
       <c r="C1190" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1190" s="1"/>
     </row>
@@ -15036,7 +15036,7 @@
         <v>0</v>
       </c>
       <c r="C1191" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1191" s="1"/>
     </row>
@@ -15048,7 +15048,7 @@
         <v>0</v>
       </c>
       <c r="C1192" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1192" s="1"/>
     </row>
@@ -15060,7 +15060,7 @@
         <v>0</v>
       </c>
       <c r="C1193" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1193" s="1"/>
     </row>
@@ -15072,7 +15072,7 @@
         <v>0</v>
       </c>
       <c r="C1194" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1194" s="1"/>
     </row>
@@ -15084,7 +15084,7 @@
         <v>0</v>
       </c>
       <c r="C1195" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1195" s="1"/>
     </row>
@@ -15096,7 +15096,7 @@
         <v>0</v>
       </c>
       <c r="C1196" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1196" s="1"/>
     </row>
@@ -15108,7 +15108,7 @@
         <v>0</v>
       </c>
       <c r="C1197" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1197" s="1"/>
     </row>
@@ -15120,7 +15120,7 @@
         <v>0</v>
       </c>
       <c r="C1198" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1198" s="1"/>
     </row>
@@ -15132,7 +15132,7 @@
         <v>0</v>
       </c>
       <c r="C1199" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1199" s="1"/>
     </row>
@@ -15144,7 +15144,7 @@
         <v>0</v>
       </c>
       <c r="C1200" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1200" s="1"/>
     </row>
@@ -15156,7 +15156,7 @@
         <v>0</v>
       </c>
       <c r="C1201" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1201" s="1"/>
     </row>
@@ -15168,7 +15168,7 @@
         <v>0</v>
       </c>
       <c r="C1202" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1202" s="1"/>
     </row>
@@ -15180,7 +15180,7 @@
         <v>0</v>
       </c>
       <c r="C1203" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1203" s="1"/>
     </row>
@@ -15192,7 +15192,7 @@
         <v>0</v>
       </c>
       <c r="C1204" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1204" s="1"/>
     </row>
@@ -15204,7 +15204,7 @@
         <v>0</v>
       </c>
       <c r="C1205" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1205" s="1"/>
     </row>
@@ -15216,7 +15216,7 @@
         <v>0</v>
       </c>
       <c r="C1206" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1206" s="1"/>
     </row>
@@ -15228,7 +15228,7 @@
         <v>0</v>
       </c>
       <c r="C1207" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1207" s="1"/>
     </row>
@@ -15240,7 +15240,7 @@
         <v>0</v>
       </c>
       <c r="C1208" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1208" s="1"/>
     </row>
@@ -15252,7 +15252,7 @@
         <v>0</v>
       </c>
       <c r="C1209" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1209" s="1"/>
     </row>
@@ -15264,7 +15264,7 @@
         <v>0</v>
       </c>
       <c r="C1210" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1210" s="1"/>
     </row>
@@ -15276,7 +15276,7 @@
         <v>0</v>
       </c>
       <c r="C1211" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1211" s="1"/>
     </row>
@@ -15288,7 +15288,7 @@
         <v>0</v>
       </c>
       <c r="C1212" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1212" s="1"/>
     </row>
@@ -15300,7 +15300,7 @@
         <v>0</v>
       </c>
       <c r="C1213" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1213" s="1"/>
     </row>
@@ -15312,7 +15312,7 @@
         <v>0</v>
       </c>
       <c r="C1214" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1214" s="1"/>
     </row>
@@ -15324,7 +15324,7 @@
         <v>0</v>
       </c>
       <c r="C1215" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1215" s="1"/>
     </row>
@@ -15336,7 +15336,7 @@
         <v>0</v>
       </c>
       <c r="C1216" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1216" s="1"/>
     </row>
@@ -15348,7 +15348,7 @@
         <v>0</v>
       </c>
       <c r="C1217" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1217" s="1"/>
     </row>
@@ -15360,7 +15360,7 @@
         <v>0</v>
       </c>
       <c r="C1218" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1218" s="1"/>
     </row>
@@ -15372,7 +15372,7 @@
         <v>0</v>
       </c>
       <c r="C1219" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1219" s="1"/>
     </row>
@@ -15384,7 +15384,7 @@
         <v>0</v>
       </c>
       <c r="C1220" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1220" s="1"/>
     </row>
@@ -15396,7 +15396,7 @@
         <v>0</v>
       </c>
       <c r="C1221" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1221" s="1"/>
     </row>
@@ -15408,7 +15408,7 @@
         <v>0</v>
       </c>
       <c r="C1222" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1222" s="1"/>
     </row>
@@ -15420,7 +15420,7 @@
         <v>0</v>
       </c>
       <c r="C1223" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1223" s="1"/>
     </row>
@@ -15432,7 +15432,7 @@
         <v>0</v>
       </c>
       <c r="C1224" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1224" s="1"/>
     </row>
@@ -15444,7 +15444,7 @@
         <v>0</v>
       </c>
       <c r="C1225" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1225" s="1"/>
     </row>
@@ -15456,7 +15456,7 @@
         <v>0</v>
       </c>
       <c r="C1226" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1226" s="1"/>
     </row>
@@ -15468,7 +15468,7 @@
         <v>0</v>
       </c>
       <c r="C1227" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1227" s="1"/>
     </row>
@@ -15480,7 +15480,7 @@
         <v>0</v>
       </c>
       <c r="C1228" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1228" s="1"/>
     </row>
@@ -15492,7 +15492,7 @@
         <v>0</v>
       </c>
       <c r="C1229" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1229" s="1"/>
     </row>
@@ -15504,7 +15504,7 @@
         <v>0</v>
       </c>
       <c r="C1230" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1230" s="1"/>
     </row>
@@ -15516,7 +15516,7 @@
         <v>0</v>
       </c>
       <c r="C1231" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1231" s="1"/>
     </row>
@@ -15528,7 +15528,7 @@
         <v>0</v>
       </c>
       <c r="C1232" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1232" s="1"/>
     </row>
@@ -15540,7 +15540,7 @@
         <v>0</v>
       </c>
       <c r="C1233" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1233" s="1"/>
     </row>
@@ -15552,7 +15552,7 @@
         <v>0</v>
       </c>
       <c r="C1234" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1234" s="1"/>
     </row>
@@ -15564,7 +15564,7 @@
         <v>0</v>
       </c>
       <c r="C1235" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1235" s="1"/>
     </row>
@@ -15576,7 +15576,7 @@
         <v>0</v>
       </c>
       <c r="C1236" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1236" s="1"/>
     </row>
@@ -15588,7 +15588,7 @@
         <v>0</v>
       </c>
       <c r="C1237" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1237" s="1"/>
     </row>
@@ -15600,7 +15600,7 @@
         <v>0</v>
       </c>
       <c r="C1238" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1238" s="1"/>
     </row>
@@ -15612,7 +15612,7 @@
         <v>0</v>
       </c>
       <c r="C1239" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1239" s="1"/>
     </row>
@@ -15624,7 +15624,7 @@
         <v>0</v>
       </c>
       <c r="C1240" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1240" s="1"/>
     </row>
@@ -15636,7 +15636,7 @@
         <v>0</v>
       </c>
       <c r="C1241" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1241" s="1"/>
     </row>
@@ -15648,7 +15648,7 @@
         <v>0</v>
       </c>
       <c r="C1242" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1242" s="1"/>
     </row>
@@ -15660,7 +15660,7 @@
         <v>0</v>
       </c>
       <c r="C1243" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1243" s="1"/>
     </row>
@@ -15672,7 +15672,7 @@
         <v>0</v>
       </c>
       <c r="C1244" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1244" s="1"/>
     </row>
@@ -15684,7 +15684,7 @@
         <v>0</v>
       </c>
       <c r="C1245" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1245" s="1"/>
     </row>
@@ -15696,7 +15696,7 @@
         <v>0</v>
       </c>
       <c r="C1246" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1246" s="1"/>
     </row>
@@ -15708,7 +15708,7 @@
         <v>0</v>
       </c>
       <c r="C1247" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1247" s="1"/>
     </row>
@@ -15720,7 +15720,7 @@
         <v>0</v>
       </c>
       <c r="C1248" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1248" s="1"/>
     </row>
@@ -15732,7 +15732,7 @@
         <v>0</v>
       </c>
       <c r="C1249" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1249" s="1"/>
     </row>
@@ -15744,7 +15744,7 @@
         <v>0</v>
       </c>
       <c r="C1250" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1250" s="1"/>
     </row>
@@ -15756,7 +15756,7 @@
         <v>0</v>
       </c>
       <c r="C1251" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1251" s="1"/>
     </row>
@@ -15768,7 +15768,7 @@
         <v>0</v>
       </c>
       <c r="C1252" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1252" s="1"/>
     </row>
@@ -15780,7 +15780,7 @@
         <v>0</v>
       </c>
       <c r="C1253" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1253" s="1"/>
     </row>
@@ -15792,7 +15792,7 @@
         <v>0</v>
       </c>
       <c r="C1254" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1254" s="1"/>
     </row>
@@ -15804,7 +15804,7 @@
         <v>0</v>
       </c>
       <c r="C1255" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1255" s="1"/>
     </row>
@@ -15816,7 +15816,7 @@
         <v>0</v>
       </c>
       <c r="C1256" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1256" s="1"/>
     </row>
@@ -15828,7 +15828,7 @@
         <v>0</v>
       </c>
       <c r="C1257" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1257" s="1"/>
     </row>
@@ -15840,7 +15840,7 @@
         <v>0</v>
       </c>
       <c r="C1258" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1258" s="1"/>
     </row>
@@ -15852,7 +15852,7 @@
         <v>0</v>
       </c>
       <c r="C1259" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1259" s="1"/>
     </row>
@@ -15864,7 +15864,7 @@
         <v>0</v>
       </c>
       <c r="C1260" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1260" s="1"/>
     </row>
@@ -15876,7 +15876,7 @@
         <v>0</v>
       </c>
       <c r="C1261" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1261" s="1"/>
     </row>
@@ -15888,7 +15888,7 @@
         <v>0</v>
       </c>
       <c r="C1262" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1262" s="1"/>
     </row>
@@ -15900,7 +15900,7 @@
         <v>0</v>
       </c>
       <c r="C1263" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1263" s="1"/>
     </row>
@@ -15912,7 +15912,7 @@
         <v>0</v>
       </c>
       <c r="C1264" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1264" s="1"/>
     </row>
@@ -15924,7 +15924,7 @@
         <v>0</v>
       </c>
       <c r="C1265" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1265" s="1"/>
     </row>
@@ -15936,7 +15936,7 @@
         <v>0</v>
       </c>
       <c r="C1266" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1266" s="1"/>
     </row>
@@ -15948,7 +15948,7 @@
         <v>0</v>
       </c>
       <c r="C1267" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1267" s="1"/>
     </row>
@@ -15960,7 +15960,7 @@
         <v>0</v>
       </c>
       <c r="C1268" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1268" s="1"/>
     </row>
@@ -15972,7 +15972,7 @@
         <v>0</v>
       </c>
       <c r="C1269" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1269" s="1"/>
     </row>
@@ -15984,7 +15984,7 @@
         <v>0</v>
       </c>
       <c r="C1270" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1270" s="1"/>
     </row>
@@ -15996,7 +15996,7 @@
         <v>0</v>
       </c>
       <c r="C1271" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1271" s="1"/>
     </row>
@@ -16008,7 +16008,7 @@
         <v>0</v>
       </c>
       <c r="C1272" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1272" s="1"/>
     </row>
@@ -16020,7 +16020,7 @@
         <v>0</v>
       </c>
       <c r="C1273" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1273" s="1"/>
     </row>
@@ -16032,7 +16032,7 @@
         <v>0</v>
       </c>
       <c r="C1274" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1274" s="1"/>
     </row>
@@ -16044,7 +16044,7 @@
         <v>0</v>
       </c>
       <c r="C1275" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1275" s="1"/>
     </row>
@@ -16056,7 +16056,7 @@
         <v>0</v>
       </c>
       <c r="C1276" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1276" s="1"/>
     </row>
@@ -16068,7 +16068,7 @@
         <v>0</v>
       </c>
       <c r="C1277" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1277" s="1"/>
     </row>
@@ -16080,7 +16080,7 @@
         <v>0</v>
       </c>
       <c r="C1278" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1278" s="1"/>
     </row>
@@ -16092,7 +16092,7 @@
         <v>0</v>
       </c>
       <c r="C1279" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1279" s="1"/>
     </row>
@@ -16104,7 +16104,7 @@
         <v>0</v>
       </c>
       <c r="C1280" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1280" s="1"/>
     </row>
@@ -16116,7 +16116,7 @@
         <v>0</v>
       </c>
       <c r="C1281" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1281" s="1"/>
     </row>
@@ -16128,7 +16128,7 @@
         <v>0</v>
       </c>
       <c r="C1282" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1282" s="1"/>
     </row>
@@ -16140,7 +16140,7 @@
         <v>0</v>
       </c>
       <c r="C1283" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1283" s="1"/>
     </row>
@@ -16152,7 +16152,7 @@
         <v>0</v>
       </c>
       <c r="C1284" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1284" s="1"/>
     </row>
@@ -16164,7 +16164,7 @@
         <v>0</v>
       </c>
       <c r="C1285" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1285" s="1"/>
     </row>
@@ -16176,7 +16176,7 @@
         <v>0</v>
       </c>
       <c r="C1286" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1286" s="1"/>
     </row>
@@ -16188,7 +16188,7 @@
         <v>0</v>
       </c>
       <c r="C1287" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1287" s="1"/>
     </row>
@@ -16200,7 +16200,7 @@
         <v>0</v>
       </c>
       <c r="C1288" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1288" s="1"/>
     </row>
@@ -16212,7 +16212,7 @@
         <v>0</v>
       </c>
       <c r="C1289" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1289" s="1"/>
     </row>
@@ -16224,7 +16224,7 @@
         <v>0</v>
       </c>
       <c r="C1290" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1290" s="1"/>
     </row>
@@ -16236,7 +16236,7 @@
         <v>0</v>
       </c>
       <c r="C1291" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1291" s="1"/>
     </row>
@@ -16248,7 +16248,7 @@
         <v>0</v>
       </c>
       <c r="C1292" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1292" s="1"/>
     </row>
@@ -16260,7 +16260,7 @@
         <v>0</v>
       </c>
       <c r="C1293" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1293" s="1"/>
     </row>
@@ -16272,7 +16272,7 @@
         <v>0</v>
       </c>
       <c r="C1294" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1294" s="1"/>
     </row>
@@ -16284,7 +16284,7 @@
         <v>0</v>
       </c>
       <c r="C1295" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1295" s="1"/>
     </row>
@@ -16296,7 +16296,7 @@
         <v>0</v>
       </c>
       <c r="C1296" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1296" s="1"/>
     </row>
@@ -16308,7 +16308,7 @@
         <v>0</v>
       </c>
       <c r="C1297" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1297" s="1"/>
     </row>
@@ -16320,7 +16320,7 @@
         <v>0</v>
       </c>
       <c r="C1298" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1298" s="1"/>
     </row>
@@ -16332,7 +16332,7 @@
         <v>0</v>
       </c>
       <c r="C1299" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1299" s="1"/>
     </row>
@@ -16344,7 +16344,7 @@
         <v>0</v>
       </c>
       <c r="C1300" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1300" s="1"/>
     </row>
@@ -16356,7 +16356,7 @@
         <v>0</v>
       </c>
       <c r="C1301" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D1301" s="1"/>
     </row>

--- a/PNL.xlsx
+++ b/PNL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/apple/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C7D211A-37C8-8B49-9342-18478B726A8B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2797652-13D6-AE48-8334-63FD2A29B226}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16180" xr2:uid="{06C2047E-A20D-7B41-A100-9F165F6715E9}"/>
   </bookViews>
@@ -11580,7 +11580,7 @@
         <v>0</v>
       </c>
       <c r="C903" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D903" s="1"/>
     </row>
@@ -11592,7 +11592,7 @@
         <v>0</v>
       </c>
       <c r="C904" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D904" s="1"/>
     </row>
@@ -11604,7 +11604,7 @@
         <v>0</v>
       </c>
       <c r="C905" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D905" s="1"/>
     </row>
@@ -11616,7 +11616,7 @@
         <v>0</v>
       </c>
       <c r="C906" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D906" s="1"/>
     </row>
@@ -11628,7 +11628,7 @@
         <v>0</v>
       </c>
       <c r="C907" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D907" s="1"/>
     </row>
@@ -11640,7 +11640,7 @@
         <v>0</v>
       </c>
       <c r="C908" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D908" s="1"/>
     </row>
@@ -11652,7 +11652,7 @@
         <v>0</v>
       </c>
       <c r="C909" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D909" s="1"/>
     </row>
@@ -11664,7 +11664,7 @@
         <v>0</v>
       </c>
       <c r="C910" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D910" s="1"/>
     </row>
@@ -11676,7 +11676,7 @@
         <v>0</v>
       </c>
       <c r="C911" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D911" s="1"/>
     </row>
@@ -11688,7 +11688,7 @@
         <v>0</v>
       </c>
       <c r="C912" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D912" s="1"/>
     </row>
@@ -11700,7 +11700,7 @@
         <v>0</v>
       </c>
       <c r="C913" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D913" s="1"/>
     </row>
@@ -11712,7 +11712,7 @@
         <v>0</v>
       </c>
       <c r="C914" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D914" s="1"/>
     </row>
@@ -11724,7 +11724,7 @@
         <v>0</v>
       </c>
       <c r="C915" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D915" s="1"/>
     </row>
@@ -11736,7 +11736,7 @@
         <v>0</v>
       </c>
       <c r="C916" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D916" s="1"/>
     </row>
@@ -11748,7 +11748,7 @@
         <v>0</v>
       </c>
       <c r="C917" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D917" s="1"/>
     </row>
@@ -11760,7 +11760,7 @@
         <v>0</v>
       </c>
       <c r="C918" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D918" s="1"/>
     </row>
@@ -11772,7 +11772,7 @@
         <v>0</v>
       </c>
       <c r="C919" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D919" s="1"/>
     </row>
@@ -11784,7 +11784,7 @@
         <v>0</v>
       </c>
       <c r="C920" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D920" s="1"/>
     </row>
@@ -11796,7 +11796,7 @@
         <v>0</v>
       </c>
       <c r="C921" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D921" s="1"/>
     </row>
@@ -11808,7 +11808,7 @@
         <v>0</v>
       </c>
       <c r="C922" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D922" s="1"/>
     </row>
@@ -11820,7 +11820,7 @@
         <v>0</v>
       </c>
       <c r="C923" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D923" s="1"/>
     </row>
@@ -11832,7 +11832,7 @@
         <v>0</v>
       </c>
       <c r="C924" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D924" s="1"/>
     </row>
@@ -11844,7 +11844,7 @@
         <v>0</v>
       </c>
       <c r="C925" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D925" s="1"/>
     </row>
@@ -11856,7 +11856,7 @@
         <v>0</v>
       </c>
       <c r="C926" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D926" s="1"/>
     </row>
@@ -11868,7 +11868,7 @@
         <v>0</v>
       </c>
       <c r="C927" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D927" s="1"/>
     </row>
@@ -11880,7 +11880,7 @@
         <v>0</v>
       </c>
       <c r="C928" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D928" s="1"/>
     </row>
@@ -11892,7 +11892,7 @@
         <v>0</v>
       </c>
       <c r="C929" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D929" s="1"/>
     </row>
@@ -11904,7 +11904,7 @@
         <v>0</v>
       </c>
       <c r="C930" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D930" s="1"/>
     </row>
@@ -11916,7 +11916,7 @@
         <v>0</v>
       </c>
       <c r="C931" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D931" s="1"/>
     </row>
@@ -11928,7 +11928,7 @@
         <v>0</v>
       </c>
       <c r="C932" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D932" s="1"/>
     </row>
@@ -11940,7 +11940,7 @@
         <v>0</v>
       </c>
       <c r="C933" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D933" s="1"/>
     </row>
@@ -11952,7 +11952,7 @@
         <v>0</v>
       </c>
       <c r="C934" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D934" s="1"/>
     </row>
@@ -11964,7 +11964,7 @@
         <v>0</v>
       </c>
       <c r="C935" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D935" s="1"/>
     </row>
@@ -11976,7 +11976,7 @@
         <v>0</v>
       </c>
       <c r="C936" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D936" s="1"/>
     </row>
@@ -11988,7 +11988,7 @@
         <v>0</v>
       </c>
       <c r="C937" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D937" s="1"/>
     </row>
@@ -12000,7 +12000,7 @@
         <v>0</v>
       </c>
       <c r="C938" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D938" s="1"/>
     </row>
@@ -12012,7 +12012,7 @@
         <v>0</v>
       </c>
       <c r="C939" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D939" s="1"/>
     </row>
@@ -12024,7 +12024,7 @@
         <v>0</v>
       </c>
       <c r="C940" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D940" s="1"/>
     </row>
@@ -12036,7 +12036,7 @@
         <v>0</v>
       </c>
       <c r="C941" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D941" s="1"/>
     </row>
@@ -12048,7 +12048,7 @@
         <v>0</v>
       </c>
       <c r="C942" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D942" s="1"/>
     </row>
@@ -12060,7 +12060,7 @@
         <v>0</v>
       </c>
       <c r="C943" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D943" s="1"/>
     </row>
@@ -12072,7 +12072,7 @@
         <v>0</v>
       </c>
       <c r="C944" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D944" s="1"/>
     </row>
@@ -12084,7 +12084,7 @@
         <v>0</v>
       </c>
       <c r="C945" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D945" s="1"/>
     </row>
@@ -12096,7 +12096,7 @@
         <v>0</v>
       </c>
       <c r="C946" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D946" s="1"/>
     </row>
@@ -12108,7 +12108,7 @@
         <v>0</v>
       </c>
       <c r="C947" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D947" s="1"/>
     </row>
@@ -12120,7 +12120,7 @@
         <v>0</v>
       </c>
       <c r="C948" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D948" s="1"/>
     </row>
@@ -12132,7 +12132,7 @@
         <v>0</v>
       </c>
       <c r="C949" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D949" s="1"/>
     </row>
@@ -12144,7 +12144,7 @@
         <v>0</v>
       </c>
       <c r="C950" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D950" s="1"/>
     </row>
@@ -12156,7 +12156,7 @@
         <v>0</v>
       </c>
       <c r="C951" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D951" s="1"/>
     </row>
@@ -12168,7 +12168,7 @@
         <v>0</v>
       </c>
       <c r="C952" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D952" s="1"/>
     </row>
@@ -12180,7 +12180,7 @@
         <v>0</v>
       </c>
       <c r="C953" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D953" s="1"/>
     </row>
@@ -12192,7 +12192,7 @@
         <v>0</v>
       </c>
       <c r="C954" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D954" s="1"/>
     </row>
@@ -12204,7 +12204,7 @@
         <v>0</v>
       </c>
       <c r="C955" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D955" s="1"/>
     </row>
@@ -12216,7 +12216,7 @@
         <v>0</v>
       </c>
       <c r="C956" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D956" s="1"/>
     </row>
@@ -12228,7 +12228,7 @@
         <v>0</v>
       </c>
       <c r="C957" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D957" s="1"/>
     </row>
@@ -12240,7 +12240,7 @@
         <v>0</v>
       </c>
       <c r="C958" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D958" s="1"/>
     </row>
@@ -12252,7 +12252,7 @@
         <v>0</v>
       </c>
       <c r="C959" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D959" s="1"/>
     </row>
@@ -12264,7 +12264,7 @@
         <v>0</v>
       </c>
       <c r="C960" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D960" s="1"/>
     </row>
@@ -12276,7 +12276,7 @@
         <v>0</v>
       </c>
       <c r="C961" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D961" s="1"/>
     </row>
@@ -12288,7 +12288,7 @@
         <v>0</v>
       </c>
       <c r="C962" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D962" s="1"/>
     </row>
@@ -12300,7 +12300,7 @@
         <v>0</v>
       </c>
       <c r="C963" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D963" s="1"/>
     </row>
@@ -12312,7 +12312,7 @@
         <v>0</v>
       </c>
       <c r="C964" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D964" s="1"/>
     </row>
@@ -12324,7 +12324,7 @@
         <v>0</v>
       </c>
       <c r="C965" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D965" s="1"/>
     </row>
@@ -12336,7 +12336,7 @@
         <v>0</v>
       </c>
       <c r="C966" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D966" s="1"/>
     </row>
@@ -12348,7 +12348,7 @@
         <v>0</v>
       </c>
       <c r="C967" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D967" s="1"/>
     </row>
@@ -12360,7 +12360,7 @@
         <v>0</v>
       </c>
       <c r="C968" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D968" s="1"/>
     </row>
@@ -12372,7 +12372,7 @@
         <v>0</v>
       </c>
       <c r="C969" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D969" s="1"/>
     </row>
@@ -12384,7 +12384,7 @@
         <v>0</v>
       </c>
       <c r="C970" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D970" s="1"/>
     </row>
@@ -12396,7 +12396,7 @@
         <v>0</v>
       </c>
       <c r="C971" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D971" s="1"/>
     </row>
@@ -12408,7 +12408,7 @@
         <v>0</v>
       </c>
       <c r="C972" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D972" s="1"/>
     </row>
@@ -12420,7 +12420,7 @@
         <v>0</v>
       </c>
       <c r="C973" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D973" s="1"/>
     </row>
@@ -12432,7 +12432,7 @@
         <v>0</v>
       </c>
       <c r="C974" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D974" s="1"/>
     </row>
@@ -12444,7 +12444,7 @@
         <v>0</v>
       </c>
       <c r="C975" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D975" s="1"/>
     </row>
@@ -12456,7 +12456,7 @@
         <v>0</v>
       </c>
       <c r="C976" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D976" s="1"/>
     </row>
@@ -12468,7 +12468,7 @@
         <v>0</v>
       </c>
       <c r="C977" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D977" s="1"/>
     </row>
@@ -12480,7 +12480,7 @@
         <v>0</v>
       </c>
       <c r="C978" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D978" s="1"/>
     </row>
@@ -12492,7 +12492,7 @@
         <v>0</v>
       </c>
       <c r="C979" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D979" s="1"/>
     </row>
@@ -12504,7 +12504,7 @@
         <v>0</v>
       </c>
       <c r="C980" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D980" s="1"/>
     </row>
@@ -12516,7 +12516,7 @@
         <v>0</v>
       </c>
       <c r="C981" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D981" s="1"/>
     </row>
@@ -12528,7 +12528,7 @@
         <v>0</v>
       </c>
       <c r="C982" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D982" s="1"/>
     </row>
@@ -12540,7 +12540,7 @@
         <v>0</v>
       </c>
       <c r="C983" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D983" s="1"/>
     </row>
@@ -12552,7 +12552,7 @@
         <v>0</v>
       </c>
       <c r="C984" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D984" s="1"/>
     </row>
@@ -12564,7 +12564,7 @@
         <v>0</v>
       </c>
       <c r="C985" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D985" s="1"/>
     </row>
@@ -12576,7 +12576,7 @@
         <v>0</v>
       </c>
       <c r="C986" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D986" s="1"/>
     </row>
@@ -12588,7 +12588,7 @@
         <v>0</v>
       </c>
       <c r="C987" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D987" s="1"/>
     </row>
@@ -12600,7 +12600,7 @@
         <v>0</v>
       </c>
       <c r="C988" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D988" s="1"/>
     </row>
@@ -12612,7 +12612,7 @@
         <v>0</v>
       </c>
       <c r="C989" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D989" s="1"/>
     </row>
@@ -12624,7 +12624,7 @@
         <v>0</v>
       </c>
       <c r="C990" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D990" s="1"/>
     </row>
@@ -12636,7 +12636,7 @@
         <v>0</v>
       </c>
       <c r="C991" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D991" s="1"/>
     </row>
@@ -12648,7 +12648,7 @@
         <v>0</v>
       </c>
       <c r="C992" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D992" s="1"/>
     </row>
@@ -12660,7 +12660,7 @@
         <v>0</v>
       </c>
       <c r="C993" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D993" s="1"/>
     </row>
@@ -12672,7 +12672,7 @@
         <v>0</v>
       </c>
       <c r="C994" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D994" s="1"/>
     </row>
@@ -12684,7 +12684,7 @@
         <v>0</v>
       </c>
       <c r="C995" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D995" s="1"/>
     </row>
@@ -12696,7 +12696,7 @@
         <v>0</v>
       </c>
       <c r="C996" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D996" s="1"/>
     </row>
@@ -12708,7 +12708,7 @@
         <v>0</v>
       </c>
       <c r="C997" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D997" s="1"/>
     </row>
@@ -12720,7 +12720,7 @@
         <v>0</v>
       </c>
       <c r="C998" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D998" s="1"/>
     </row>
@@ -12732,7 +12732,7 @@
         <v>0</v>
       </c>
       <c r="C999" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D999" s="1"/>
     </row>
@@ -12744,7 +12744,7 @@
         <v>0</v>
       </c>
       <c r="C1000" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1000" s="1"/>
     </row>
@@ -12756,7 +12756,7 @@
         <v>0</v>
       </c>
       <c r="C1001" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1001" s="1"/>
     </row>
@@ -12768,7 +12768,7 @@
         <v>0</v>
       </c>
       <c r="C1002" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1002" s="1"/>
     </row>
@@ -12780,7 +12780,7 @@
         <v>0</v>
       </c>
       <c r="C1003" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1003" s="1"/>
     </row>
@@ -12792,7 +12792,7 @@
         <v>0</v>
       </c>
       <c r="C1004" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1004" s="1"/>
     </row>
@@ -12804,7 +12804,7 @@
         <v>0</v>
       </c>
       <c r="C1005" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1005" s="1"/>
     </row>
@@ -12816,7 +12816,7 @@
         <v>0</v>
       </c>
       <c r="C1006" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1006" s="1"/>
     </row>
@@ -12828,7 +12828,7 @@
         <v>0</v>
       </c>
       <c r="C1007" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1007" s="1"/>
     </row>
@@ -12840,7 +12840,7 @@
         <v>0</v>
       </c>
       <c r="C1008" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1008" s="1"/>
     </row>
@@ -12852,7 +12852,7 @@
         <v>0</v>
       </c>
       <c r="C1009" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1009" s="1"/>
     </row>
@@ -12864,7 +12864,7 @@
         <v>0</v>
       </c>
       <c r="C1010" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1010" s="1"/>
     </row>
@@ -12876,7 +12876,7 @@
         <v>0</v>
       </c>
       <c r="C1011" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1011" s="1"/>
     </row>
@@ -12888,7 +12888,7 @@
         <v>0</v>
       </c>
       <c r="C1012" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1012" s="1"/>
     </row>
@@ -12900,7 +12900,7 @@
         <v>0</v>
       </c>
       <c r="C1013" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1013" s="1"/>
     </row>
@@ -12912,7 +12912,7 @@
         <v>0</v>
       </c>
       <c r="C1014" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1014" s="1"/>
     </row>
@@ -12924,7 +12924,7 @@
         <v>0</v>
       </c>
       <c r="C1015" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1015" s="1"/>
     </row>
@@ -12936,7 +12936,7 @@
         <v>0</v>
       </c>
       <c r="C1016" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1016" s="1"/>
     </row>
@@ -12948,7 +12948,7 @@
         <v>0</v>
       </c>
       <c r="C1017" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1017" s="1"/>
     </row>
@@ -12960,7 +12960,7 @@
         <v>0</v>
       </c>
       <c r="C1018" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1018" s="1"/>
     </row>
@@ -12972,7 +12972,7 @@
         <v>0</v>
       </c>
       <c r="C1019" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1019" s="1"/>
     </row>
@@ -12984,7 +12984,7 @@
         <v>0</v>
       </c>
       <c r="C1020" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1020" s="1"/>
     </row>
@@ -12996,7 +12996,7 @@
         <v>0</v>
       </c>
       <c r="C1021" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1021" s="1"/>
     </row>
@@ -13008,7 +13008,7 @@
         <v>0</v>
       </c>
       <c r="C1022" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1022" s="1"/>
     </row>
@@ -13020,7 +13020,7 @@
         <v>0</v>
       </c>
       <c r="C1023" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1023" s="1"/>
     </row>
@@ -13032,7 +13032,7 @@
         <v>0</v>
       </c>
       <c r="C1024" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1024" s="1"/>
     </row>
@@ -13044,7 +13044,7 @@
         <v>0</v>
       </c>
       <c r="C1025" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1025" s="1"/>
     </row>
@@ -13056,7 +13056,7 @@
         <v>0</v>
       </c>
       <c r="C1026" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1026" s="1"/>
     </row>
@@ -13068,7 +13068,7 @@
         <v>0</v>
       </c>
       <c r="C1027" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1027" s="1"/>
     </row>
@@ -13080,7 +13080,7 @@
         <v>0</v>
       </c>
       <c r="C1028" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1028" s="1"/>
     </row>
@@ -13092,7 +13092,7 @@
         <v>0</v>
       </c>
       <c r="C1029" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1029" s="1"/>
     </row>
@@ -13104,7 +13104,7 @@
         <v>0</v>
       </c>
       <c r="C1030" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1030" s="1"/>
     </row>
@@ -13116,7 +13116,7 @@
         <v>0</v>
       </c>
       <c r="C1031" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1031" s="1"/>
     </row>
@@ -13128,7 +13128,7 @@
         <v>0</v>
       </c>
       <c r="C1032" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1032" s="1"/>
     </row>
@@ -13140,7 +13140,7 @@
         <v>0</v>
       </c>
       <c r="C1033" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1033" s="1"/>
     </row>
@@ -13152,7 +13152,7 @@
         <v>0</v>
       </c>
       <c r="C1034" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1034" s="1"/>
     </row>
@@ -13164,7 +13164,7 @@
         <v>0</v>
       </c>
       <c r="C1035" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1035" s="1"/>
     </row>
@@ -13176,7 +13176,7 @@
         <v>0</v>
       </c>
       <c r="C1036" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1036" s="1"/>
     </row>
@@ -13188,7 +13188,7 @@
         <v>0</v>
       </c>
       <c r="C1037" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1037" s="1"/>
     </row>
@@ -13200,7 +13200,7 @@
         <v>0</v>
       </c>
       <c r="C1038" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1038" s="1"/>
     </row>
@@ -13212,7 +13212,7 @@
         <v>0</v>
       </c>
       <c r="C1039" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1039" s="1"/>
     </row>
@@ -13224,7 +13224,7 @@
         <v>0</v>
       </c>
       <c r="C1040" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1040" s="1"/>
     </row>
@@ -13236,7 +13236,7 @@
         <v>0</v>
       </c>
       <c r="C1041" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1041" s="1"/>
     </row>
@@ -13248,7 +13248,7 @@
         <v>0</v>
       </c>
       <c r="C1042" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1042" s="1"/>
     </row>
@@ -13260,7 +13260,7 @@
         <v>0</v>
       </c>
       <c r="C1043" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1043" s="1"/>
     </row>
@@ -13272,7 +13272,7 @@
         <v>0</v>
       </c>
       <c r="C1044" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1044" s="1"/>
     </row>
@@ -13284,7 +13284,7 @@
         <v>0</v>
       </c>
       <c r="C1045" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1045" s="1"/>
     </row>
@@ -13296,7 +13296,7 @@
         <v>0</v>
       </c>
       <c r="C1046" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1046" s="1"/>
     </row>
@@ -13308,7 +13308,7 @@
         <v>0</v>
       </c>
       <c r="C1047" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1047" s="1"/>
     </row>
@@ -13320,7 +13320,7 @@
         <v>0</v>
       </c>
       <c r="C1048" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1048" s="1"/>
     </row>
@@ -13332,7 +13332,7 @@
         <v>0</v>
       </c>
       <c r="C1049" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1049" s="1"/>
     </row>
@@ -13344,7 +13344,7 @@
         <v>0</v>
       </c>
       <c r="C1050" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1050" s="1"/>
     </row>
@@ -13356,7 +13356,7 @@
         <v>0</v>
       </c>
       <c r="C1051" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1051" s="1"/>
     </row>
@@ -13368,7 +13368,7 @@
         <v>0</v>
       </c>
       <c r="C1052" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1052" s="1"/>
     </row>
@@ -13380,7 +13380,7 @@
         <v>0</v>
       </c>
       <c r="C1053" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1053" s="1"/>
     </row>
@@ -13392,7 +13392,7 @@
         <v>0</v>
       </c>
       <c r="C1054" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1054" s="1"/>
     </row>
@@ -13404,7 +13404,7 @@
         <v>0</v>
       </c>
       <c r="C1055" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1055" s="1"/>
     </row>
@@ -13416,7 +13416,7 @@
         <v>0</v>
       </c>
       <c r="C1056" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1056" s="1"/>
     </row>
@@ -13428,7 +13428,7 @@
         <v>0</v>
       </c>
       <c r="C1057" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1057" s="1"/>
     </row>
@@ -13440,7 +13440,7 @@
         <v>0</v>
       </c>
       <c r="C1058" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1058" s="1"/>
     </row>
@@ -13452,7 +13452,7 @@
         <v>0</v>
       </c>
       <c r="C1059" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1059" s="1"/>
     </row>
@@ -13464,7 +13464,7 @@
         <v>0</v>
       </c>
       <c r="C1060" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1060" s="1"/>
     </row>
@@ -13476,7 +13476,7 @@
         <v>0</v>
       </c>
       <c r="C1061" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1061" s="1"/>
     </row>
@@ -13488,7 +13488,7 @@
         <v>0</v>
       </c>
       <c r="C1062" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1062" s="1"/>
     </row>
@@ -13500,7 +13500,7 @@
         <v>0</v>
       </c>
       <c r="C1063" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1063" s="1"/>
     </row>
@@ -13512,7 +13512,7 @@
         <v>0</v>
       </c>
       <c r="C1064" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1064" s="1"/>
     </row>
@@ -13524,7 +13524,7 @@
         <v>0</v>
       </c>
       <c r="C1065" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1065" s="1"/>
     </row>
@@ -13536,7 +13536,7 @@
         <v>0</v>
       </c>
       <c r="C1066" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1066" s="1"/>
     </row>
@@ -13548,7 +13548,7 @@
         <v>0</v>
       </c>
       <c r="C1067" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1067" s="1"/>
     </row>
@@ -13560,7 +13560,7 @@
         <v>0</v>
       </c>
       <c r="C1068" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1068" s="1"/>
     </row>
@@ -13572,7 +13572,7 @@
         <v>0</v>
       </c>
       <c r="C1069" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1069" s="1"/>
     </row>
@@ -13584,7 +13584,7 @@
         <v>0</v>
       </c>
       <c r="C1070" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1070" s="1"/>
     </row>
@@ -13596,7 +13596,7 @@
         <v>0</v>
       </c>
       <c r="C1071" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1071" s="1"/>
     </row>
@@ -13608,7 +13608,7 @@
         <v>0</v>
       </c>
       <c r="C1072" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1072" s="1"/>
     </row>
@@ -13620,7 +13620,7 @@
         <v>0</v>
       </c>
       <c r="C1073" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1073" s="1"/>
     </row>
@@ -13632,7 +13632,7 @@
         <v>0</v>
       </c>
       <c r="C1074" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1074" s="1"/>
     </row>
@@ -13644,7 +13644,7 @@
         <v>0</v>
       </c>
       <c r="C1075" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1075" s="1"/>
     </row>
@@ -13656,7 +13656,7 @@
         <v>0</v>
       </c>
       <c r="C1076" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1076" s="1"/>
     </row>
@@ -13668,7 +13668,7 @@
         <v>0</v>
       </c>
       <c r="C1077" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1077" s="1"/>
     </row>
@@ -13680,7 +13680,7 @@
         <v>0</v>
       </c>
       <c r="C1078" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1078" s="1"/>
     </row>
@@ -13692,7 +13692,7 @@
         <v>0</v>
       </c>
       <c r="C1079" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1079" s="1"/>
     </row>
@@ -13704,7 +13704,7 @@
         <v>0</v>
       </c>
       <c r="C1080" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1080" s="1"/>
     </row>
@@ -13716,7 +13716,7 @@
         <v>0</v>
       </c>
       <c r="C1081" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1081" s="1"/>
     </row>
@@ -13728,7 +13728,7 @@
         <v>0</v>
       </c>
       <c r="C1082" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1082" s="1"/>
     </row>
@@ -13740,7 +13740,7 @@
         <v>0</v>
       </c>
       <c r="C1083" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1083" s="1"/>
     </row>
@@ -13752,7 +13752,7 @@
         <v>0</v>
       </c>
       <c r="C1084" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1084" s="1"/>
     </row>
@@ -13764,7 +13764,7 @@
         <v>0</v>
       </c>
       <c r="C1085" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1085" s="1"/>
     </row>
@@ -13776,7 +13776,7 @@
         <v>0</v>
       </c>
       <c r="C1086" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1086" s="1"/>
     </row>
@@ -13788,7 +13788,7 @@
         <v>0</v>
       </c>
       <c r="C1087" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1087" s="1"/>
     </row>
@@ -13800,7 +13800,7 @@
         <v>0</v>
       </c>
       <c r="C1088" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1088" s="1"/>
     </row>
@@ -13812,7 +13812,7 @@
         <v>0</v>
       </c>
       <c r="C1089" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1089" s="1"/>
     </row>
@@ -13824,7 +13824,7 @@
         <v>0</v>
       </c>
       <c r="C1090" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1090" s="1"/>
     </row>
@@ -13836,7 +13836,7 @@
         <v>0</v>
       </c>
       <c r="C1091" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1091" s="1"/>
     </row>
@@ -13848,7 +13848,7 @@
         <v>0</v>
       </c>
       <c r="C1092" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1092" s="1"/>
     </row>
@@ -13860,7 +13860,7 @@
         <v>0</v>
       </c>
       <c r="C1093" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1093" s="1"/>
     </row>
@@ -13872,7 +13872,7 @@
         <v>0</v>
       </c>
       <c r="C1094" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1094" s="1"/>
     </row>
@@ -13884,7 +13884,7 @@
         <v>0</v>
       </c>
       <c r="C1095" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1095" s="1"/>
     </row>
@@ -13896,7 +13896,7 @@
         <v>0</v>
       </c>
       <c r="C1096" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1096" s="1"/>
     </row>
@@ -13908,7 +13908,7 @@
         <v>0</v>
       </c>
       <c r="C1097" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1097" s="1"/>
     </row>
@@ -13920,7 +13920,7 @@
         <v>0</v>
       </c>
       <c r="C1098" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1098" s="1"/>
     </row>
@@ -13932,7 +13932,7 @@
         <v>0</v>
       </c>
       <c r="C1099" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1099" s="1"/>
     </row>
@@ -13944,7 +13944,7 @@
         <v>0</v>
       </c>
       <c r="C1100" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1100" s="1"/>
     </row>
@@ -13956,7 +13956,7 @@
         <v>0</v>
       </c>
       <c r="C1101" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1101" s="1"/>
     </row>
@@ -13968,7 +13968,7 @@
         <v>0</v>
       </c>
       <c r="C1102" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1102" s="1"/>
     </row>
@@ -13980,7 +13980,7 @@
         <v>0</v>
       </c>
       <c r="C1103" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1103" s="1"/>
     </row>
@@ -13992,7 +13992,7 @@
         <v>0</v>
       </c>
       <c r="C1104" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1104" s="1"/>
     </row>
@@ -14004,7 +14004,7 @@
         <v>0</v>
       </c>
       <c r="C1105" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1105" s="1"/>
     </row>
@@ -14016,7 +14016,7 @@
         <v>0</v>
       </c>
       <c r="C1106" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1106" s="1"/>
     </row>
@@ -14028,7 +14028,7 @@
         <v>0</v>
       </c>
       <c r="C1107" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1107" s="1"/>
     </row>
@@ -14040,7 +14040,7 @@
         <v>0</v>
       </c>
       <c r="C1108" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1108" s="1"/>
     </row>
@@ -14052,7 +14052,7 @@
         <v>0</v>
       </c>
       <c r="C1109" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1109" s="1"/>
     </row>
@@ -14064,7 +14064,7 @@
         <v>0</v>
       </c>
       <c r="C1110" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1110" s="1"/>
     </row>
@@ -14076,7 +14076,7 @@
         <v>0</v>
       </c>
       <c r="C1111" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1111" s="1"/>
     </row>
@@ -14088,7 +14088,7 @@
         <v>0</v>
       </c>
       <c r="C1112" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1112" s="1"/>
     </row>
@@ -14100,7 +14100,7 @@
         <v>0</v>
       </c>
       <c r="C1113" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1113" s="1"/>
     </row>
@@ -14112,7 +14112,7 @@
         <v>0</v>
       </c>
       <c r="C1114" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1114" s="1"/>
     </row>
@@ -14124,7 +14124,7 @@
         <v>0</v>
       </c>
       <c r="C1115" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1115" s="1"/>
     </row>
@@ -14136,7 +14136,7 @@
         <v>0</v>
       </c>
       <c r="C1116" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1116" s="1"/>
     </row>
@@ -14148,7 +14148,7 @@
         <v>0</v>
       </c>
       <c r="C1117" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1117" s="1"/>
     </row>
@@ -14160,7 +14160,7 @@
         <v>0</v>
       </c>
       <c r="C1118" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1118" s="1"/>
     </row>
@@ -14172,7 +14172,7 @@
         <v>0</v>
       </c>
       <c r="C1119" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1119" s="1"/>
     </row>
@@ -14184,7 +14184,7 @@
         <v>0</v>
       </c>
       <c r="C1120" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1120" s="1"/>
     </row>
@@ -14196,7 +14196,7 @@
         <v>0</v>
       </c>
       <c r="C1121" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1121" s="1"/>
     </row>
@@ -14208,7 +14208,7 @@
         <v>0</v>
       </c>
       <c r="C1122" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1122" s="1"/>
     </row>
@@ -14220,7 +14220,7 @@
         <v>0</v>
       </c>
       <c r="C1123" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1123" s="1"/>
     </row>
@@ -14232,7 +14232,7 @@
         <v>0</v>
       </c>
       <c r="C1124" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1124" s="1"/>
     </row>
@@ -14244,7 +14244,7 @@
         <v>0</v>
       </c>
       <c r="C1125" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1125" s="1"/>
     </row>
@@ -14256,7 +14256,7 @@
         <v>0</v>
       </c>
       <c r="C1126" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1126" s="1"/>
     </row>
@@ -14268,7 +14268,7 @@
         <v>0</v>
       </c>
       <c r="C1127" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1127" s="1"/>
     </row>
@@ -14280,7 +14280,7 @@
         <v>0</v>
       </c>
       <c r="C1128" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1128" s="1"/>
     </row>
@@ -14292,7 +14292,7 @@
         <v>0</v>
       </c>
       <c r="C1129" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1129" s="1"/>
     </row>
@@ -14304,7 +14304,7 @@
         <v>0</v>
       </c>
       <c r="C1130" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1130" s="1"/>
     </row>
@@ -14316,7 +14316,7 @@
         <v>0</v>
       </c>
       <c r="C1131" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1131" s="1"/>
     </row>
@@ -14328,7 +14328,7 @@
         <v>0</v>
       </c>
       <c r="C1132" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1132" s="1"/>
     </row>
@@ -14340,7 +14340,7 @@
         <v>0</v>
       </c>
       <c r="C1133" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1133" s="1"/>
     </row>
@@ -14352,7 +14352,7 @@
         <v>0</v>
       </c>
       <c r="C1134" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1134" s="1"/>
     </row>
@@ -14364,7 +14364,7 @@
         <v>0</v>
       </c>
       <c r="C1135" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1135" s="1"/>
     </row>
@@ -14376,7 +14376,7 @@
         <v>0</v>
       </c>
       <c r="C1136" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1136" s="1"/>
     </row>
@@ -14388,7 +14388,7 @@
         <v>0</v>
       </c>
       <c r="C1137" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1137" s="1"/>
     </row>
@@ -14400,7 +14400,7 @@
         <v>0</v>
       </c>
       <c r="C1138" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1138" s="1"/>
     </row>
@@ -14412,7 +14412,7 @@
         <v>0</v>
       </c>
       <c r="C1139" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1139" s="1"/>
     </row>
@@ -14424,7 +14424,7 @@
         <v>0</v>
       </c>
       <c r="C1140" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1140" s="1"/>
     </row>
@@ -14436,7 +14436,7 @@
         <v>0</v>
       </c>
       <c r="C1141" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1141" s="1"/>
     </row>
@@ -14448,7 +14448,7 @@
         <v>0</v>
       </c>
       <c r="C1142" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1142" s="1"/>
     </row>
@@ -14460,7 +14460,7 @@
         <v>0</v>
       </c>
       <c r="C1143" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1143" s="1"/>
     </row>
@@ -14472,7 +14472,7 @@
         <v>0</v>
       </c>
       <c r="C1144" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1144" s="1"/>
     </row>
@@ -14484,7 +14484,7 @@
         <v>0</v>
       </c>
       <c r="C1145" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1145" s="1"/>
     </row>
@@ -14496,7 +14496,7 @@
         <v>0</v>
       </c>
       <c r="C1146" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1146" s="1"/>
     </row>
@@ -14508,7 +14508,7 @@
         <v>0</v>
       </c>
       <c r="C1147" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1147" s="1"/>
     </row>
@@ -14520,7 +14520,7 @@
         <v>0</v>
       </c>
       <c r="C1148" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1148" s="1"/>
     </row>
@@ -14532,7 +14532,7 @@
         <v>0</v>
       </c>
       <c r="C1149" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1149" s="1"/>
     </row>
@@ -14544,7 +14544,7 @@
         <v>0</v>
       </c>
       <c r="C1150" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1150" s="1"/>
     </row>
@@ -14556,7 +14556,7 @@
         <v>0</v>
       </c>
       <c r="C1151" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1151" s="1"/>
     </row>
@@ -14568,7 +14568,7 @@
         <v>0</v>
       </c>
       <c r="C1152" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1152" s="1"/>
     </row>
@@ -14580,7 +14580,7 @@
         <v>0</v>
       </c>
       <c r="C1153" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1153" s="1"/>
     </row>
@@ -14592,7 +14592,7 @@
         <v>0</v>
       </c>
       <c r="C1154" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1154" s="1"/>
     </row>
@@ -14604,7 +14604,7 @@
         <v>0</v>
       </c>
       <c r="C1155" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1155" s="1"/>
     </row>
@@ -14616,7 +14616,7 @@
         <v>0</v>
       </c>
       <c r="C1156" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1156" s="1"/>
     </row>
@@ -14628,7 +14628,7 @@
         <v>0</v>
       </c>
       <c r="C1157" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1157" s="1"/>
     </row>
@@ -14640,7 +14640,7 @@
         <v>0</v>
       </c>
       <c r="C1158" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1158" s="1"/>
     </row>
@@ -14652,7 +14652,7 @@
         <v>0</v>
       </c>
       <c r="C1159" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1159" s="1"/>
     </row>
@@ -14664,7 +14664,7 @@
         <v>0</v>
       </c>
       <c r="C1160" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1160" s="1"/>
     </row>
@@ -14676,7 +14676,7 @@
         <v>0</v>
       </c>
       <c r="C1161" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1161" s="1"/>
     </row>
@@ -14688,7 +14688,7 @@
         <v>0</v>
       </c>
       <c r="C1162" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1162" s="1"/>
     </row>
@@ -14700,7 +14700,7 @@
         <v>0</v>
       </c>
       <c r="C1163" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1163" s="1"/>
     </row>
@@ -14712,7 +14712,7 @@
         <v>0</v>
       </c>
       <c r="C1164" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1164" s="1"/>
     </row>
@@ -14724,7 +14724,7 @@
         <v>0</v>
       </c>
       <c r="C1165" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1165" s="1"/>
     </row>
@@ -14736,7 +14736,7 @@
         <v>0</v>
       </c>
       <c r="C1166" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1166" s="1"/>
     </row>
@@ -14748,7 +14748,7 @@
         <v>0</v>
       </c>
       <c r="C1167" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1167" s="1"/>
     </row>
@@ -14760,7 +14760,7 @@
         <v>0</v>
       </c>
       <c r="C1168" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1168" s="1"/>
     </row>
@@ -14772,7 +14772,7 @@
         <v>0</v>
       </c>
       <c r="C1169" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1169" s="1"/>
     </row>
@@ -14784,7 +14784,7 @@
         <v>0</v>
       </c>
       <c r="C1170" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1170" s="1"/>
     </row>
@@ -14796,7 +14796,7 @@
         <v>0</v>
       </c>
       <c r="C1171" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1171" s="1"/>
     </row>
@@ -14808,7 +14808,7 @@
         <v>0</v>
       </c>
       <c r="C1172" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1172" s="1"/>
     </row>
@@ -14820,7 +14820,7 @@
         <v>0</v>
       </c>
       <c r="C1173" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1173" s="1"/>
     </row>
@@ -14832,7 +14832,7 @@
         <v>0</v>
       </c>
       <c r="C1174" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1174" s="1"/>
     </row>
@@ -14844,7 +14844,7 @@
         <v>0</v>
       </c>
       <c r="C1175" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1175" s="1"/>
     </row>
@@ -14856,7 +14856,7 @@
         <v>0</v>
       </c>
       <c r="C1176" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1176" s="1"/>
     </row>
@@ -14868,7 +14868,7 @@
         <v>0</v>
       </c>
       <c r="C1177" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1177" s="1"/>
     </row>
@@ -14880,7 +14880,7 @@
         <v>0</v>
       </c>
       <c r="C1178" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1178" s="1"/>
     </row>
@@ -14892,7 +14892,7 @@
         <v>0</v>
       </c>
       <c r="C1179" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1179" s="1"/>
     </row>
@@ -14904,7 +14904,7 @@
         <v>0</v>
       </c>
       <c r="C1180" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1180" s="1"/>
     </row>
@@ -14916,7 +14916,7 @@
         <v>0</v>
       </c>
       <c r="C1181" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1181" s="1"/>
     </row>
@@ -14928,7 +14928,7 @@
         <v>0</v>
       </c>
       <c r="C1182" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1182" s="1"/>
     </row>
@@ -14940,7 +14940,7 @@
         <v>0</v>
       </c>
       <c r="C1183" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1183" s="1"/>
     </row>
@@ -14952,7 +14952,7 @@
         <v>0</v>
       </c>
       <c r="C1184" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1184" s="1"/>
     </row>
@@ -14964,7 +14964,7 @@
         <v>0</v>
       </c>
       <c r="C1185" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1185" s="1"/>
     </row>
@@ -14976,7 +14976,7 @@
         <v>0</v>
       </c>
       <c r="C1186" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1186" s="1"/>
     </row>
@@ -14988,7 +14988,7 @@
         <v>0</v>
       </c>
       <c r="C1187" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1187" s="1"/>
     </row>
@@ -15000,7 +15000,7 @@
         <v>0</v>
       </c>
       <c r="C1188" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1188" s="1"/>
     </row>
@@ -15012,7 +15012,7 @@
         <v>0</v>
       </c>
       <c r="C1189" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1189" s="1"/>
     </row>
@@ -15024,7 +15024,7 @@
         <v>0</v>
       </c>
       <c r="C1190" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1190" s="1"/>
     </row>
@@ -15036,7 +15036,7 @@
         <v>0</v>
       </c>
       <c r="C1191" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1191" s="1"/>
     </row>
@@ -15048,7 +15048,7 @@
         <v>0</v>
       </c>
       <c r="C1192" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1192" s="1"/>
     </row>
@@ -15060,7 +15060,7 @@
         <v>0</v>
       </c>
       <c r="C1193" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1193" s="1"/>
     </row>
@@ -15072,7 +15072,7 @@
         <v>0</v>
       </c>
       <c r="C1194" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1194" s="1"/>
     </row>
@@ -15084,7 +15084,7 @@
         <v>0</v>
       </c>
       <c r="C1195" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1195" s="1"/>
     </row>
@@ -15096,7 +15096,7 @@
         <v>0</v>
       </c>
       <c r="C1196" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1196" s="1"/>
     </row>
@@ -15108,7 +15108,7 @@
         <v>0</v>
       </c>
       <c r="C1197" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1197" s="1"/>
     </row>
@@ -15120,7 +15120,7 @@
         <v>0</v>
       </c>
       <c r="C1198" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1198" s="1"/>
     </row>
@@ -15132,7 +15132,7 @@
         <v>0</v>
       </c>
       <c r="C1199" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1199" s="1"/>
     </row>
@@ -15144,7 +15144,7 @@
         <v>0</v>
       </c>
       <c r="C1200" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1200" s="1"/>
     </row>
@@ -15156,7 +15156,7 @@
         <v>0</v>
       </c>
       <c r="C1201" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1201" s="1"/>
     </row>
@@ -15168,7 +15168,7 @@
         <v>0</v>
       </c>
       <c r="C1202" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1202" s="1"/>
     </row>
@@ -15180,7 +15180,7 @@
         <v>0</v>
       </c>
       <c r="C1203" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1203" s="1"/>
     </row>
@@ -15192,7 +15192,7 @@
         <v>0</v>
       </c>
       <c r="C1204" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1204" s="1"/>
     </row>
@@ -15204,7 +15204,7 @@
         <v>0</v>
       </c>
       <c r="C1205" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1205" s="1"/>
     </row>
@@ -15216,7 +15216,7 @@
         <v>0</v>
       </c>
       <c r="C1206" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1206" s="1"/>
     </row>
@@ -15228,7 +15228,7 @@
         <v>0</v>
       </c>
       <c r="C1207" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1207" s="1"/>
     </row>
@@ -15240,7 +15240,7 @@
         <v>0</v>
       </c>
       <c r="C1208" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1208" s="1"/>
     </row>
@@ -15252,7 +15252,7 @@
         <v>0</v>
       </c>
       <c r="C1209" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1209" s="1"/>
     </row>
@@ -15264,7 +15264,7 @@
         <v>0</v>
       </c>
       <c r="C1210" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1210" s="1"/>
     </row>
@@ -15276,7 +15276,7 @@
         <v>0</v>
       </c>
       <c r="C1211" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1211" s="1"/>
     </row>
@@ -15288,7 +15288,7 @@
         <v>0</v>
       </c>
       <c r="C1212" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1212" s="1"/>
     </row>
@@ -15300,7 +15300,7 @@
         <v>0</v>
       </c>
       <c r="C1213" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1213" s="1"/>
     </row>
@@ -15312,7 +15312,7 @@
         <v>0</v>
       </c>
       <c r="C1214" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1214" s="1"/>
     </row>
@@ -15324,7 +15324,7 @@
         <v>0</v>
       </c>
       <c r="C1215" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1215" s="1"/>
     </row>
@@ -15336,7 +15336,7 @@
         <v>0</v>
       </c>
       <c r="C1216" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1216" s="1"/>
     </row>
@@ -15348,7 +15348,7 @@
         <v>0</v>
       </c>
       <c r="C1217" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1217" s="1"/>
     </row>
@@ -15360,7 +15360,7 @@
         <v>0</v>
       </c>
       <c r="C1218" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1218" s="1"/>
     </row>
@@ -15372,7 +15372,7 @@
         <v>0</v>
       </c>
       <c r="C1219" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1219" s="1"/>
     </row>
@@ -15384,7 +15384,7 @@
         <v>0</v>
       </c>
       <c r="C1220" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1220" s="1"/>
     </row>
@@ -15396,7 +15396,7 @@
         <v>0</v>
       </c>
       <c r="C1221" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1221" s="1"/>
     </row>
@@ -15408,7 +15408,7 @@
         <v>0</v>
       </c>
       <c r="C1222" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1222" s="1"/>
     </row>
@@ -15420,7 +15420,7 @@
         <v>0</v>
       </c>
       <c r="C1223" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1223" s="1"/>
     </row>
@@ -15432,7 +15432,7 @@
         <v>0</v>
       </c>
       <c r="C1224" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1224" s="1"/>
     </row>
@@ -15444,7 +15444,7 @@
         <v>0</v>
       </c>
       <c r="C1225" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1225" s="1"/>
     </row>
@@ -15456,7 +15456,7 @@
         <v>0</v>
       </c>
       <c r="C1226" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1226" s="1"/>
     </row>
@@ -15468,7 +15468,7 @@
         <v>0</v>
       </c>
       <c r="C1227" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1227" s="1"/>
     </row>
@@ -15480,7 +15480,7 @@
         <v>0</v>
       </c>
       <c r="C1228" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1228" s="1"/>
     </row>
@@ -15492,7 +15492,7 @@
         <v>0</v>
       </c>
       <c r="C1229" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1229" s="1"/>
     </row>
@@ -15504,7 +15504,7 @@
         <v>0</v>
       </c>
       <c r="C1230" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1230" s="1"/>
     </row>
@@ -15516,7 +15516,7 @@
         <v>0</v>
       </c>
       <c r="C1231" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1231" s="1"/>
     </row>
@@ -15528,7 +15528,7 @@
         <v>0</v>
       </c>
       <c r="C1232" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1232" s="1"/>
     </row>
@@ -15540,7 +15540,7 @@
         <v>0</v>
       </c>
       <c r="C1233" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1233" s="1"/>
     </row>
@@ -15552,7 +15552,7 @@
         <v>0</v>
       </c>
       <c r="C1234" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1234" s="1"/>
     </row>
@@ -15564,7 +15564,7 @@
         <v>0</v>
       </c>
       <c r="C1235" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1235" s="1"/>
     </row>
@@ -15576,7 +15576,7 @@
         <v>0</v>
       </c>
       <c r="C1236" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1236" s="1"/>
     </row>
@@ -15588,7 +15588,7 @@
         <v>0</v>
       </c>
       <c r="C1237" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1237" s="1"/>
     </row>
@@ -15600,7 +15600,7 @@
         <v>0</v>
       </c>
       <c r="C1238" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1238" s="1"/>
     </row>
@@ -15612,7 +15612,7 @@
         <v>0</v>
       </c>
       <c r="C1239" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1239" s="1"/>
     </row>
@@ -15624,7 +15624,7 @@
         <v>0</v>
       </c>
       <c r="C1240" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1240" s="1"/>
     </row>
@@ -15636,7 +15636,7 @@
         <v>0</v>
       </c>
       <c r="C1241" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1241" s="1"/>
     </row>
@@ -15648,7 +15648,7 @@
         <v>0</v>
       </c>
       <c r="C1242" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1242" s="1"/>
     </row>
@@ -15660,7 +15660,7 @@
         <v>0</v>
       </c>
       <c r="C1243" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1243" s="1"/>
     </row>
@@ -15672,7 +15672,7 @@
         <v>0</v>
       </c>
       <c r="C1244" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1244" s="1"/>
     </row>
@@ -15684,7 +15684,7 @@
         <v>0</v>
       </c>
       <c r="C1245" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1245" s="1"/>
     </row>
@@ -15696,7 +15696,7 @@
         <v>0</v>
       </c>
       <c r="C1246" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1246" s="1"/>
     </row>
@@ -15708,7 +15708,7 @@
         <v>0</v>
       </c>
       <c r="C1247" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1247" s="1"/>
     </row>
@@ -15720,7 +15720,7 @@
         <v>0</v>
       </c>
       <c r="C1248" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1248" s="1"/>
     </row>
@@ -15732,7 +15732,7 @@
         <v>0</v>
       </c>
       <c r="C1249" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1249" s="1"/>
     </row>
@@ -15744,7 +15744,7 @@
         <v>0</v>
       </c>
       <c r="C1250" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1250" s="1"/>
     </row>
@@ -15756,7 +15756,7 @@
         <v>0</v>
       </c>
       <c r="C1251" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1251" s="1"/>
     </row>
@@ -15768,7 +15768,7 @@
         <v>0</v>
       </c>
       <c r="C1252" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1252" s="1"/>
     </row>
@@ -15780,7 +15780,7 @@
         <v>0</v>
       </c>
       <c r="C1253" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1253" s="1"/>
     </row>
@@ -15792,7 +15792,7 @@
         <v>0</v>
       </c>
       <c r="C1254" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1254" s="1"/>
     </row>
@@ -15804,7 +15804,7 @@
         <v>0</v>
       </c>
       <c r="C1255" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1255" s="1"/>
     </row>
@@ -15816,7 +15816,7 @@
         <v>0</v>
       </c>
       <c r="C1256" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1256" s="1"/>
     </row>
@@ -15828,7 +15828,7 @@
         <v>0</v>
       </c>
       <c r="C1257" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1257" s="1"/>
     </row>
@@ -15840,7 +15840,7 @@
         <v>0</v>
       </c>
       <c r="C1258" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1258" s="1"/>
     </row>
@@ -15852,7 +15852,7 @@
         <v>0</v>
       </c>
       <c r="C1259" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1259" s="1"/>
     </row>
@@ -15864,7 +15864,7 @@
         <v>0</v>
       </c>
       <c r="C1260" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1260" s="1"/>
     </row>
@@ -15876,7 +15876,7 @@
         <v>0</v>
       </c>
       <c r="C1261" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1261" s="1"/>
     </row>
@@ -15888,7 +15888,7 @@
         <v>0</v>
       </c>
       <c r="C1262" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1262" s="1"/>
     </row>
@@ -15900,7 +15900,7 @@
         <v>0</v>
       </c>
       <c r="C1263" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1263" s="1"/>
     </row>
@@ -15912,7 +15912,7 @@
         <v>0</v>
       </c>
       <c r="C1264" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1264" s="1"/>
     </row>
@@ -15924,7 +15924,7 @@
         <v>0</v>
       </c>
       <c r="C1265" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1265" s="1"/>
     </row>
@@ -15936,7 +15936,7 @@
         <v>0</v>
       </c>
       <c r="C1266" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1266" s="1"/>
     </row>
@@ -15948,7 +15948,7 @@
         <v>0</v>
       </c>
       <c r="C1267" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1267" s="1"/>
     </row>
@@ -15960,7 +15960,7 @@
         <v>0</v>
       </c>
       <c r="C1268" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1268" s="1"/>
     </row>
@@ -15972,7 +15972,7 @@
         <v>0</v>
       </c>
       <c r="C1269" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1269" s="1"/>
     </row>
@@ -15984,7 +15984,7 @@
         <v>0</v>
       </c>
       <c r="C1270" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1270" s="1"/>
     </row>
@@ -15996,7 +15996,7 @@
         <v>0</v>
       </c>
       <c r="C1271" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1271" s="1"/>
     </row>
@@ -16008,7 +16008,7 @@
         <v>0</v>
       </c>
       <c r="C1272" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1272" s="1"/>
     </row>
@@ -16020,7 +16020,7 @@
         <v>0</v>
       </c>
       <c r="C1273" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1273" s="1"/>
     </row>
@@ -16032,7 +16032,7 @@
         <v>0</v>
       </c>
       <c r="C1274" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1274" s="1"/>
     </row>
@@ -16044,7 +16044,7 @@
         <v>0</v>
       </c>
       <c r="C1275" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1275" s="1"/>
     </row>
@@ -16056,7 +16056,7 @@
         <v>0</v>
       </c>
       <c r="C1276" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1276" s="1"/>
     </row>
@@ -16068,7 +16068,7 @@
         <v>0</v>
       </c>
       <c r="C1277" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1277" s="1"/>
     </row>
@@ -16080,7 +16080,7 @@
         <v>0</v>
       </c>
       <c r="C1278" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1278" s="1"/>
     </row>
@@ -16092,7 +16092,7 @@
         <v>0</v>
       </c>
       <c r="C1279" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1279" s="1"/>
     </row>
@@ -16104,7 +16104,7 @@
         <v>0</v>
       </c>
       <c r="C1280" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1280" s="1"/>
     </row>
@@ -16116,7 +16116,7 @@
         <v>0</v>
       </c>
       <c r="C1281" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1281" s="1"/>
     </row>
@@ -16128,7 +16128,7 @@
         <v>0</v>
       </c>
       <c r="C1282" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1282" s="1"/>
     </row>
@@ -16140,7 +16140,7 @@
         <v>0</v>
       </c>
       <c r="C1283" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1283" s="1"/>
     </row>
@@ -16152,7 +16152,7 @@
         <v>0</v>
       </c>
       <c r="C1284" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1284" s="1"/>
     </row>
@@ -16164,7 +16164,7 @@
         <v>0</v>
       </c>
       <c r="C1285" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1285" s="1"/>
     </row>
@@ -16176,7 +16176,7 @@
         <v>0</v>
       </c>
       <c r="C1286" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1286" s="1"/>
     </row>
@@ -16188,7 +16188,7 @@
         <v>0</v>
       </c>
       <c r="C1287" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1287" s="1"/>
     </row>
@@ -16200,7 +16200,7 @@
         <v>0</v>
       </c>
       <c r="C1288" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1288" s="1"/>
     </row>
@@ -16212,7 +16212,7 @@
         <v>0</v>
       </c>
       <c r="C1289" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1289" s="1"/>
     </row>
@@ -16224,7 +16224,7 @@
         <v>0</v>
       </c>
       <c r="C1290" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1290" s="1"/>
     </row>
@@ -16236,7 +16236,7 @@
         <v>0</v>
       </c>
       <c r="C1291" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1291" s="1"/>
     </row>
@@ -16248,7 +16248,7 @@
         <v>0</v>
       </c>
       <c r="C1292" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1292" s="1"/>
     </row>
@@ -16260,7 +16260,7 @@
         <v>0</v>
       </c>
       <c r="C1293" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1293" s="1"/>
     </row>
@@ -16272,7 +16272,7 @@
         <v>0</v>
       </c>
       <c r="C1294" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1294" s="1"/>
     </row>
@@ -16284,7 +16284,7 @@
         <v>0</v>
       </c>
       <c r="C1295" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1295" s="1"/>
     </row>
@@ -16296,7 +16296,7 @@
         <v>0</v>
       </c>
       <c r="C1296" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1296" s="1"/>
     </row>
@@ -16308,7 +16308,7 @@
         <v>0</v>
       </c>
       <c r="C1297" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1297" s="1"/>
     </row>
@@ -16320,7 +16320,7 @@
         <v>0</v>
       </c>
       <c r="C1298" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1298" s="1"/>
     </row>
@@ -16332,7 +16332,7 @@
         <v>0</v>
       </c>
       <c r="C1299" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1299" s="1"/>
     </row>
@@ -16344,7 +16344,7 @@
         <v>0</v>
       </c>
       <c r="C1300" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1300" s="1"/>
     </row>
@@ -16356,7 +16356,7 @@
         <v>0</v>
       </c>
       <c r="C1301" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="D1301" s="1"/>
     </row>

--- a/PNL.xlsx
+++ b/PNL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/apple/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2797652-13D6-AE48-8334-63FD2A29B226}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9B55AAD-FDDD-BD40-BE17-BEB32C3B9BB7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16180" xr2:uid="{06C2047E-A20D-7B41-A100-9F165F6715E9}"/>
   </bookViews>
@@ -11579,9 +11579,7 @@
       <c r="B903" s="1">
         <v>0</v>
       </c>
-      <c r="C903" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C903" s="1"/>
       <c r="D903" s="1"/>
     </row>
     <row r="904" spans="1:4">
@@ -11591,9 +11589,7 @@
       <c r="B904" s="1">
         <v>0</v>
       </c>
-      <c r="C904" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C904" s="1"/>
       <c r="D904" s="1"/>
     </row>
     <row r="905" spans="1:4">
@@ -11603,9 +11599,7 @@
       <c r="B905" s="1">
         <v>0</v>
       </c>
-      <c r="C905" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C905" s="1"/>
       <c r="D905" s="1"/>
     </row>
     <row r="906" spans="1:4">
@@ -11615,9 +11609,7 @@
       <c r="B906" s="1">
         <v>0</v>
       </c>
-      <c r="C906" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C906" s="1"/>
       <c r="D906" s="1"/>
     </row>
     <row r="907" spans="1:4">
@@ -11627,9 +11619,7 @@
       <c r="B907" s="1">
         <v>0</v>
       </c>
-      <c r="C907" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C907" s="1"/>
       <c r="D907" s="1"/>
     </row>
     <row r="908" spans="1:4">
@@ -11639,9 +11629,7 @@
       <c r="B908" s="1">
         <v>0</v>
       </c>
-      <c r="C908" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C908" s="1"/>
       <c r="D908" s="1"/>
     </row>
     <row r="909" spans="1:4">
@@ -11651,9 +11639,7 @@
       <c r="B909" s="1">
         <v>0</v>
       </c>
-      <c r="C909" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C909" s="1"/>
       <c r="D909" s="1"/>
     </row>
     <row r="910" spans="1:4">
@@ -11663,9 +11649,7 @@
       <c r="B910" s="1">
         <v>0</v>
       </c>
-      <c r="C910" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C910" s="1"/>
       <c r="D910" s="1"/>
     </row>
     <row r="911" spans="1:4">
@@ -11675,9 +11659,7 @@
       <c r="B911" s="1">
         <v>0</v>
       </c>
-      <c r="C911" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C911" s="1"/>
       <c r="D911" s="1"/>
     </row>
     <row r="912" spans="1:4">
@@ -11687,9 +11669,7 @@
       <c r="B912" s="1">
         <v>0</v>
       </c>
-      <c r="C912" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C912" s="1"/>
       <c r="D912" s="1"/>
     </row>
     <row r="913" spans="1:4">
@@ -11699,9 +11679,7 @@
       <c r="B913" s="1">
         <v>0</v>
       </c>
-      <c r="C913" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C913" s="1"/>
       <c r="D913" s="1"/>
     </row>
     <row r="914" spans="1:4">
@@ -11711,9 +11689,7 @@
       <c r="B914" s="1">
         <v>0</v>
       </c>
-      <c r="C914" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C914" s="1"/>
       <c r="D914" s="1"/>
     </row>
     <row r="915" spans="1:4">
@@ -11723,9 +11699,7 @@
       <c r="B915" s="1">
         <v>0</v>
       </c>
-      <c r="C915" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C915" s="1"/>
       <c r="D915" s="1"/>
     </row>
     <row r="916" spans="1:4">
@@ -11735,9 +11709,7 @@
       <c r="B916" s="1">
         <v>0</v>
       </c>
-      <c r="C916" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C916" s="1"/>
       <c r="D916" s="1"/>
     </row>
     <row r="917" spans="1:4">
@@ -11747,9 +11719,7 @@
       <c r="B917" s="1">
         <v>0</v>
       </c>
-      <c r="C917" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C917" s="1"/>
       <c r="D917" s="1"/>
     </row>
     <row r="918" spans="1:4">
@@ -11759,9 +11729,7 @@
       <c r="B918" s="1">
         <v>0</v>
       </c>
-      <c r="C918" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C918" s="1"/>
       <c r="D918" s="1"/>
     </row>
     <row r="919" spans="1:4">
@@ -11771,9 +11739,7 @@
       <c r="B919" s="1">
         <v>0</v>
       </c>
-      <c r="C919" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C919" s="1"/>
       <c r="D919" s="1"/>
     </row>
     <row r="920" spans="1:4">
@@ -11783,9 +11749,7 @@
       <c r="B920" s="1">
         <v>0</v>
       </c>
-      <c r="C920" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C920" s="1"/>
       <c r="D920" s="1"/>
     </row>
     <row r="921" spans="1:4">
@@ -11795,9 +11759,7 @@
       <c r="B921" s="1">
         <v>0</v>
       </c>
-      <c r="C921" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C921" s="1"/>
       <c r="D921" s="1"/>
     </row>
     <row r="922" spans="1:4">
@@ -11807,9 +11769,7 @@
       <c r="B922" s="1">
         <v>0</v>
       </c>
-      <c r="C922" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C922" s="1"/>
       <c r="D922" s="1"/>
     </row>
     <row r="923" spans="1:4">
@@ -11819,9 +11779,7 @@
       <c r="B923" s="1">
         <v>0</v>
       </c>
-      <c r="C923" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C923" s="1"/>
       <c r="D923" s="1"/>
     </row>
     <row r="924" spans="1:4">
@@ -11831,9 +11789,7 @@
       <c r="B924" s="1">
         <v>0</v>
       </c>
-      <c r="C924" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C924" s="1"/>
       <c r="D924" s="1"/>
     </row>
     <row r="925" spans="1:4">
@@ -11843,9 +11799,7 @@
       <c r="B925" s="1">
         <v>0</v>
       </c>
-      <c r="C925" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C925" s="1"/>
       <c r="D925" s="1"/>
     </row>
     <row r="926" spans="1:4">
@@ -11855,9 +11809,7 @@
       <c r="B926" s="1">
         <v>0</v>
       </c>
-      <c r="C926" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C926" s="1"/>
       <c r="D926" s="1"/>
     </row>
     <row r="927" spans="1:4">
@@ -11867,9 +11819,7 @@
       <c r="B927" s="1">
         <v>0</v>
       </c>
-      <c r="C927" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C927" s="1"/>
       <c r="D927" s="1"/>
     </row>
     <row r="928" spans="1:4">
@@ -11879,9 +11829,7 @@
       <c r="B928" s="1">
         <v>0</v>
       </c>
-      <c r="C928" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C928" s="1"/>
       <c r="D928" s="1"/>
     </row>
     <row r="929" spans="1:4">
@@ -11891,9 +11839,7 @@
       <c r="B929" s="1">
         <v>0</v>
       </c>
-      <c r="C929" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C929" s="1"/>
       <c r="D929" s="1"/>
     </row>
     <row r="930" spans="1:4">
@@ -11903,9 +11849,7 @@
       <c r="B930" s="1">
         <v>0</v>
       </c>
-      <c r="C930" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C930" s="1"/>
       <c r="D930" s="1"/>
     </row>
     <row r="931" spans="1:4">
@@ -11915,9 +11859,7 @@
       <c r="B931" s="1">
         <v>0</v>
       </c>
-      <c r="C931" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C931" s="1"/>
       <c r="D931" s="1"/>
     </row>
     <row r="932" spans="1:4">
@@ -11927,9 +11869,7 @@
       <c r="B932" s="1">
         <v>0</v>
       </c>
-      <c r="C932" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C932" s="1"/>
       <c r="D932" s="1"/>
     </row>
     <row r="933" spans="1:4">
@@ -11939,9 +11879,7 @@
       <c r="B933" s="1">
         <v>0</v>
       </c>
-      <c r="C933" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C933" s="1"/>
       <c r="D933" s="1"/>
     </row>
     <row r="934" spans="1:4">
@@ -11951,9 +11889,7 @@
       <c r="B934" s="1">
         <v>0</v>
       </c>
-      <c r="C934" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C934" s="1"/>
       <c r="D934" s="1"/>
     </row>
     <row r="935" spans="1:4">
@@ -11963,9 +11899,7 @@
       <c r="B935" s="1">
         <v>0</v>
       </c>
-      <c r="C935" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C935" s="1"/>
       <c r="D935" s="1"/>
     </row>
     <row r="936" spans="1:4">
@@ -11975,9 +11909,7 @@
       <c r="B936" s="1">
         <v>0</v>
       </c>
-      <c r="C936" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C936" s="1"/>
       <c r="D936" s="1"/>
     </row>
     <row r="937" spans="1:4">
@@ -11987,9 +11919,7 @@
       <c r="B937" s="1">
         <v>0</v>
       </c>
-      <c r="C937" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C937" s="1"/>
       <c r="D937" s="1"/>
     </row>
     <row r="938" spans="1:4">
@@ -11999,9 +11929,7 @@
       <c r="B938" s="1">
         <v>0</v>
       </c>
-      <c r="C938" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C938" s="1"/>
       <c r="D938" s="1"/>
     </row>
     <row r="939" spans="1:4">
@@ -12011,9 +11939,7 @@
       <c r="B939" s="1">
         <v>0</v>
       </c>
-      <c r="C939" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C939" s="1"/>
       <c r="D939" s="1"/>
     </row>
     <row r="940" spans="1:4">
@@ -12023,9 +11949,7 @@
       <c r="B940" s="1">
         <v>0</v>
       </c>
-      <c r="C940" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C940" s="1"/>
       <c r="D940" s="1"/>
     </row>
     <row r="941" spans="1:4">
@@ -12035,9 +11959,7 @@
       <c r="B941" s="1">
         <v>0</v>
       </c>
-      <c r="C941" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C941" s="1"/>
       <c r="D941" s="1"/>
     </row>
     <row r="942" spans="1:4">
@@ -12047,9 +11969,7 @@
       <c r="B942" s="1">
         <v>0</v>
       </c>
-      <c r="C942" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C942" s="1"/>
       <c r="D942" s="1"/>
     </row>
     <row r="943" spans="1:4">
@@ -12059,9 +11979,7 @@
       <c r="B943" s="1">
         <v>0</v>
       </c>
-      <c r="C943" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C943" s="1"/>
       <c r="D943" s="1"/>
     </row>
     <row r="944" spans="1:4">
@@ -12071,9 +11989,7 @@
       <c r="B944" s="1">
         <v>0</v>
       </c>
-      <c r="C944" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C944" s="1"/>
       <c r="D944" s="1"/>
     </row>
     <row r="945" spans="1:4">
@@ -12083,9 +11999,7 @@
       <c r="B945" s="1">
         <v>0</v>
       </c>
-      <c r="C945" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C945" s="1"/>
       <c r="D945" s="1"/>
     </row>
     <row r="946" spans="1:4">
@@ -12095,9 +12009,7 @@
       <c r="B946" s="1">
         <v>0</v>
       </c>
-      <c r="C946" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C946" s="1"/>
       <c r="D946" s="1"/>
     </row>
     <row r="947" spans="1:4">
@@ -12107,9 +12019,7 @@
       <c r="B947" s="1">
         <v>0</v>
       </c>
-      <c r="C947" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C947" s="1"/>
       <c r="D947" s="1"/>
     </row>
     <row r="948" spans="1:4">
@@ -12119,9 +12029,7 @@
       <c r="B948" s="1">
         <v>0</v>
       </c>
-      <c r="C948" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C948" s="1"/>
       <c r="D948" s="1"/>
     </row>
     <row r="949" spans="1:4">
@@ -12131,9 +12039,7 @@
       <c r="B949" s="1">
         <v>0</v>
       </c>
-      <c r="C949" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C949" s="1"/>
       <c r="D949" s="1"/>
     </row>
     <row r="950" spans="1:4">
@@ -12143,9 +12049,7 @@
       <c r="B950" s="1">
         <v>0</v>
       </c>
-      <c r="C950" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C950" s="1"/>
       <c r="D950" s="1"/>
     </row>
     <row r="951" spans="1:4">
@@ -12155,9 +12059,7 @@
       <c r="B951" s="1">
         <v>0</v>
       </c>
-      <c r="C951" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C951" s="1"/>
       <c r="D951" s="1"/>
     </row>
     <row r="952" spans="1:4">
@@ -12167,9 +12069,7 @@
       <c r="B952" s="1">
         <v>0</v>
       </c>
-      <c r="C952" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C952" s="1"/>
       <c r="D952" s="1"/>
     </row>
     <row r="953" spans="1:4">
@@ -12179,9 +12079,7 @@
       <c r="B953" s="1">
         <v>0</v>
       </c>
-      <c r="C953" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C953" s="1"/>
       <c r="D953" s="1"/>
     </row>
     <row r="954" spans="1:4">
@@ -12191,9 +12089,7 @@
       <c r="B954" s="1">
         <v>0</v>
       </c>
-      <c r="C954" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C954" s="1"/>
       <c r="D954" s="1"/>
     </row>
     <row r="955" spans="1:4">
@@ -12203,9 +12099,7 @@
       <c r="B955" s="1">
         <v>0</v>
       </c>
-      <c r="C955" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C955" s="1"/>
       <c r="D955" s="1"/>
     </row>
     <row r="956" spans="1:4">
@@ -12215,9 +12109,7 @@
       <c r="B956" s="1">
         <v>0</v>
       </c>
-      <c r="C956" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C956" s="1"/>
       <c r="D956" s="1"/>
     </row>
     <row r="957" spans="1:4">
@@ -12227,9 +12119,7 @@
       <c r="B957" s="1">
         <v>0</v>
       </c>
-      <c r="C957" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C957" s="1"/>
       <c r="D957" s="1"/>
     </row>
     <row r="958" spans="1:4">
@@ -12239,9 +12129,7 @@
       <c r="B958" s="1">
         <v>0</v>
       </c>
-      <c r="C958" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C958" s="1"/>
       <c r="D958" s="1"/>
     </row>
     <row r="959" spans="1:4">
@@ -12251,9 +12139,7 @@
       <c r="B959" s="1">
         <v>0</v>
       </c>
-      <c r="C959" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C959" s="1"/>
       <c r="D959" s="1"/>
     </row>
     <row r="960" spans="1:4">
@@ -12263,9 +12149,7 @@
       <c r="B960" s="1">
         <v>0</v>
       </c>
-      <c r="C960" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C960" s="1"/>
       <c r="D960" s="1"/>
     </row>
     <row r="961" spans="1:4">
@@ -12275,9 +12159,7 @@
       <c r="B961" s="1">
         <v>0</v>
       </c>
-      <c r="C961" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C961" s="1"/>
       <c r="D961" s="1"/>
     </row>
     <row r="962" spans="1:4">
@@ -12287,9 +12169,7 @@
       <c r="B962" s="1">
         <v>0</v>
       </c>
-      <c r="C962" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C962" s="1"/>
       <c r="D962" s="1"/>
     </row>
     <row r="963" spans="1:4">
@@ -12299,9 +12179,7 @@
       <c r="B963" s="1">
         <v>0</v>
       </c>
-      <c r="C963" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C963" s="1"/>
       <c r="D963" s="1"/>
     </row>
     <row r="964" spans="1:4">
@@ -12311,9 +12189,7 @@
       <c r="B964" s="1">
         <v>0</v>
       </c>
-      <c r="C964" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C964" s="1"/>
       <c r="D964" s="1"/>
     </row>
     <row r="965" spans="1:4">
@@ -12323,9 +12199,7 @@
       <c r="B965" s="1">
         <v>0</v>
       </c>
-      <c r="C965" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C965" s="1"/>
       <c r="D965" s="1"/>
     </row>
     <row r="966" spans="1:4">
@@ -12335,9 +12209,7 @@
       <c r="B966" s="1">
         <v>0</v>
       </c>
-      <c r="C966" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C966" s="1"/>
       <c r="D966" s="1"/>
     </row>
     <row r="967" spans="1:4">
@@ -12347,9 +12219,7 @@
       <c r="B967" s="1">
         <v>0</v>
       </c>
-      <c r="C967" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C967" s="1"/>
       <c r="D967" s="1"/>
     </row>
     <row r="968" spans="1:4">
@@ -12359,9 +12229,7 @@
       <c r="B968" s="1">
         <v>0</v>
       </c>
-      <c r="C968" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C968" s="1"/>
       <c r="D968" s="1"/>
     </row>
     <row r="969" spans="1:4">
@@ -12371,9 +12239,7 @@
       <c r="B969" s="1">
         <v>0</v>
       </c>
-      <c r="C969" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C969" s="1"/>
       <c r="D969" s="1"/>
     </row>
     <row r="970" spans="1:4">
@@ -12383,9 +12249,7 @@
       <c r="B970" s="1">
         <v>0</v>
       </c>
-      <c r="C970" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C970" s="1"/>
       <c r="D970" s="1"/>
     </row>
     <row r="971" spans="1:4">
@@ -12395,9 +12259,7 @@
       <c r="B971" s="1">
         <v>0</v>
       </c>
-      <c r="C971" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C971" s="1"/>
       <c r="D971" s="1"/>
     </row>
     <row r="972" spans="1:4">
@@ -12407,9 +12269,7 @@
       <c r="B972" s="1">
         <v>0</v>
       </c>
-      <c r="C972" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C972" s="1"/>
       <c r="D972" s="1"/>
     </row>
     <row r="973" spans="1:4">
@@ -12419,9 +12279,7 @@
       <c r="B973" s="1">
         <v>0</v>
       </c>
-      <c r="C973" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C973" s="1"/>
       <c r="D973" s="1"/>
     </row>
     <row r="974" spans="1:4">
@@ -12431,9 +12289,7 @@
       <c r="B974" s="1">
         <v>0</v>
       </c>
-      <c r="C974" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C974" s="1"/>
       <c r="D974" s="1"/>
     </row>
     <row r="975" spans="1:4">
@@ -12443,9 +12299,7 @@
       <c r="B975" s="1">
         <v>0</v>
       </c>
-      <c r="C975" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C975" s="1"/>
       <c r="D975" s="1"/>
     </row>
     <row r="976" spans="1:4">
@@ -12455,9 +12309,7 @@
       <c r="B976" s="1">
         <v>0</v>
       </c>
-      <c r="C976" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C976" s="1"/>
       <c r="D976" s="1"/>
     </row>
     <row r="977" spans="1:4">
@@ -12467,9 +12319,7 @@
       <c r="B977" s="1">
         <v>0</v>
       </c>
-      <c r="C977" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C977" s="1"/>
       <c r="D977" s="1"/>
     </row>
     <row r="978" spans="1:4">
@@ -12479,9 +12329,7 @@
       <c r="B978" s="1">
         <v>0</v>
       </c>
-      <c r="C978" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C978" s="1"/>
       <c r="D978" s="1"/>
     </row>
     <row r="979" spans="1:4">
@@ -12491,9 +12339,7 @@
       <c r="B979" s="1">
         <v>0</v>
       </c>
-      <c r="C979" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C979" s="1"/>
       <c r="D979" s="1"/>
     </row>
     <row r="980" spans="1:4">
@@ -12503,9 +12349,7 @@
       <c r="B980" s="1">
         <v>0</v>
       </c>
-      <c r="C980" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C980" s="1"/>
       <c r="D980" s="1"/>
     </row>
     <row r="981" spans="1:4">
@@ -12515,9 +12359,7 @@
       <c r="B981" s="1">
         <v>0</v>
       </c>
-      <c r="C981" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C981" s="1"/>
       <c r="D981" s="1"/>
     </row>
     <row r="982" spans="1:4">
@@ -12527,9 +12369,7 @@
       <c r="B982" s="1">
         <v>0</v>
       </c>
-      <c r="C982" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C982" s="1"/>
       <c r="D982" s="1"/>
     </row>
     <row r="983" spans="1:4">
@@ -12539,9 +12379,7 @@
       <c r="B983" s="1">
         <v>0</v>
       </c>
-      <c r="C983" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C983" s="1"/>
       <c r="D983" s="1"/>
     </row>
     <row r="984" spans="1:4">
@@ -12551,9 +12389,7 @@
       <c r="B984" s="1">
         <v>0</v>
       </c>
-      <c r="C984" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C984" s="1"/>
       <c r="D984" s="1"/>
     </row>
     <row r="985" spans="1:4">
@@ -12563,9 +12399,7 @@
       <c r="B985" s="1">
         <v>0</v>
       </c>
-      <c r="C985" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C985" s="1"/>
       <c r="D985" s="1"/>
     </row>
     <row r="986" spans="1:4">
@@ -12575,9 +12409,7 @@
       <c r="B986" s="1">
         <v>0</v>
       </c>
-      <c r="C986" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C986" s="1"/>
       <c r="D986" s="1"/>
     </row>
     <row r="987" spans="1:4">
@@ -12587,9 +12419,7 @@
       <c r="B987" s="1">
         <v>0</v>
       </c>
-      <c r="C987" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C987" s="1"/>
       <c r="D987" s="1"/>
     </row>
     <row r="988" spans="1:4">
@@ -12599,9 +12429,7 @@
       <c r="B988" s="1">
         <v>0</v>
       </c>
-      <c r="C988" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C988" s="1"/>
       <c r="D988" s="1"/>
     </row>
     <row r="989" spans="1:4">
@@ -12611,9 +12439,7 @@
       <c r="B989" s="1">
         <v>0</v>
       </c>
-      <c r="C989" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C989" s="1"/>
       <c r="D989" s="1"/>
     </row>
     <row r="990" spans="1:4">
@@ -12623,9 +12449,7 @@
       <c r="B990" s="1">
         <v>0</v>
       </c>
-      <c r="C990" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C990" s="1"/>
       <c r="D990" s="1"/>
     </row>
     <row r="991" spans="1:4">
@@ -12635,9 +12459,7 @@
       <c r="B991" s="1">
         <v>0</v>
       </c>
-      <c r="C991" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C991" s="1"/>
       <c r="D991" s="1"/>
     </row>
     <row r="992" spans="1:4">
@@ -12647,9 +12469,7 @@
       <c r="B992" s="1">
         <v>0</v>
       </c>
-      <c r="C992" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C992" s="1"/>
       <c r="D992" s="1"/>
     </row>
     <row r="993" spans="1:4">
@@ -12659,9 +12479,7 @@
       <c r="B993" s="1">
         <v>0</v>
       </c>
-      <c r="C993" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C993" s="1"/>
       <c r="D993" s="1"/>
     </row>
     <row r="994" spans="1:4">
@@ -12671,9 +12489,7 @@
       <c r="B994" s="1">
         <v>0</v>
       </c>
-      <c r="C994" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C994" s="1"/>
       <c r="D994" s="1"/>
     </row>
     <row r="995" spans="1:4">
@@ -12683,9 +12499,7 @@
       <c r="B995" s="1">
         <v>0</v>
       </c>
-      <c r="C995" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C995" s="1"/>
       <c r="D995" s="1"/>
     </row>
     <row r="996" spans="1:4">
@@ -12695,9 +12509,7 @@
       <c r="B996" s="1">
         <v>0</v>
       </c>
-      <c r="C996" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C996" s="1"/>
       <c r="D996" s="1"/>
     </row>
     <row r="997" spans="1:4">
@@ -12707,9 +12519,7 @@
       <c r="B997" s="1">
         <v>0</v>
       </c>
-      <c r="C997" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C997" s="1"/>
       <c r="D997" s="1"/>
     </row>
     <row r="998" spans="1:4">
@@ -12719,9 +12529,7 @@
       <c r="B998" s="1">
         <v>0</v>
       </c>
-      <c r="C998" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C998" s="1"/>
       <c r="D998" s="1"/>
     </row>
     <row r="999" spans="1:4">
@@ -12731,9 +12539,7 @@
       <c r="B999" s="1">
         <v>0</v>
       </c>
-      <c r="C999" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C999" s="1"/>
       <c r="D999" s="1"/>
     </row>
     <row r="1000" spans="1:4">
@@ -12743,9 +12549,7 @@
       <c r="B1000" s="1">
         <v>0</v>
       </c>
-      <c r="C1000" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1000" s="1"/>
       <c r="D1000" s="1"/>
     </row>
     <row r="1001" spans="1:4">
@@ -12755,9 +12559,7 @@
       <c r="B1001" s="1">
         <v>0</v>
       </c>
-      <c r="C1001" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1001" s="1"/>
       <c r="D1001" s="1"/>
     </row>
     <row r="1002" spans="1:4">
@@ -12767,9 +12569,7 @@
       <c r="B1002" s="1">
         <v>0</v>
       </c>
-      <c r="C1002" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1002" s="1"/>
       <c r="D1002" s="1"/>
     </row>
     <row r="1003" spans="1:4">
@@ -12779,9 +12579,7 @@
       <c r="B1003" s="1">
         <v>0</v>
       </c>
-      <c r="C1003" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1003" s="1"/>
       <c r="D1003" s="1"/>
     </row>
     <row r="1004" spans="1:4">
@@ -12791,9 +12589,7 @@
       <c r="B1004" s="1">
         <v>0</v>
       </c>
-      <c r="C1004" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1004" s="1"/>
       <c r="D1004" s="1"/>
     </row>
     <row r="1005" spans="1:4">
@@ -12803,9 +12599,7 @@
       <c r="B1005" s="1">
         <v>0</v>
       </c>
-      <c r="C1005" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1005" s="1"/>
       <c r="D1005" s="1"/>
     </row>
     <row r="1006" spans="1:4">
@@ -12815,9 +12609,7 @@
       <c r="B1006" s="1">
         <v>0</v>
       </c>
-      <c r="C1006" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1006" s="1"/>
       <c r="D1006" s="1"/>
     </row>
     <row r="1007" spans="1:4">
@@ -12827,9 +12619,7 @@
       <c r="B1007" s="1">
         <v>0</v>
       </c>
-      <c r="C1007" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1007" s="1"/>
       <c r="D1007" s="1"/>
     </row>
     <row r="1008" spans="1:4">
@@ -12839,9 +12629,7 @@
       <c r="B1008" s="1">
         <v>0</v>
       </c>
-      <c r="C1008" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1008" s="1"/>
       <c r="D1008" s="1"/>
     </row>
     <row r="1009" spans="1:4">
@@ -12851,9 +12639,7 @@
       <c r="B1009" s="1">
         <v>0</v>
       </c>
-      <c r="C1009" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1009" s="1"/>
       <c r="D1009" s="1"/>
     </row>
     <row r="1010" spans="1:4">
@@ -12863,9 +12649,7 @@
       <c r="B1010" s="1">
         <v>0</v>
       </c>
-      <c r="C1010" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1010" s="1"/>
       <c r="D1010" s="1"/>
     </row>
     <row r="1011" spans="1:4">
@@ -12875,9 +12659,7 @@
       <c r="B1011" s="1">
         <v>0</v>
       </c>
-      <c r="C1011" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1011" s="1"/>
       <c r="D1011" s="1"/>
     </row>
     <row r="1012" spans="1:4">
@@ -12887,9 +12669,7 @@
       <c r="B1012" s="1">
         <v>0</v>
       </c>
-      <c r="C1012" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1012" s="1"/>
       <c r="D1012" s="1"/>
     </row>
     <row r="1013" spans="1:4">
@@ -12899,9 +12679,7 @@
       <c r="B1013" s="1">
         <v>0</v>
       </c>
-      <c r="C1013" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1013" s="1"/>
       <c r="D1013" s="1"/>
     </row>
     <row r="1014" spans="1:4">
@@ -12911,9 +12689,7 @@
       <c r="B1014" s="1">
         <v>0</v>
       </c>
-      <c r="C1014" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1014" s="1"/>
       <c r="D1014" s="1"/>
     </row>
     <row r="1015" spans="1:4">
@@ -12923,9 +12699,7 @@
       <c r="B1015" s="1">
         <v>0</v>
       </c>
-      <c r="C1015" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1015" s="1"/>
       <c r="D1015" s="1"/>
     </row>
     <row r="1016" spans="1:4">
@@ -12935,9 +12709,7 @@
       <c r="B1016" s="1">
         <v>0</v>
       </c>
-      <c r="C1016" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1016" s="1"/>
       <c r="D1016" s="1"/>
     </row>
     <row r="1017" spans="1:4">
@@ -12947,9 +12719,7 @@
       <c r="B1017" s="1">
         <v>0</v>
       </c>
-      <c r="C1017" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1017" s="1"/>
       <c r="D1017" s="1"/>
     </row>
     <row r="1018" spans="1:4">
@@ -12959,9 +12729,7 @@
       <c r="B1018" s="1">
         <v>0</v>
       </c>
-      <c r="C1018" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1018" s="1"/>
       <c r="D1018" s="1"/>
     </row>
     <row r="1019" spans="1:4">
@@ -12971,9 +12739,7 @@
       <c r="B1019" s="1">
         <v>0</v>
       </c>
-      <c r="C1019" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1019" s="1"/>
       <c r="D1019" s="1"/>
     </row>
     <row r="1020" spans="1:4">
@@ -12983,9 +12749,7 @@
       <c r="B1020" s="1">
         <v>0</v>
       </c>
-      <c r="C1020" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1020" s="1"/>
       <c r="D1020" s="1"/>
     </row>
     <row r="1021" spans="1:4">
@@ -12995,9 +12759,7 @@
       <c r="B1021" s="1">
         <v>0</v>
       </c>
-      <c r="C1021" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1021" s="1"/>
       <c r="D1021" s="1"/>
     </row>
     <row r="1022" spans="1:4">
@@ -13007,9 +12769,7 @@
       <c r="B1022" s="1">
         <v>0</v>
       </c>
-      <c r="C1022" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1022" s="1"/>
       <c r="D1022" s="1"/>
     </row>
     <row r="1023" spans="1:4">
@@ -13019,9 +12779,7 @@
       <c r="B1023" s="1">
         <v>0</v>
       </c>
-      <c r="C1023" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1023" s="1"/>
       <c r="D1023" s="1"/>
     </row>
     <row r="1024" spans="1:4">
@@ -13031,9 +12789,7 @@
       <c r="B1024" s="1">
         <v>0</v>
       </c>
-      <c r="C1024" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1024" s="1"/>
       <c r="D1024" s="1"/>
     </row>
     <row r="1025" spans="1:4">
@@ -13043,9 +12799,7 @@
       <c r="B1025" s="1">
         <v>0</v>
       </c>
-      <c r="C1025" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1025" s="1"/>
       <c r="D1025" s="1"/>
     </row>
     <row r="1026" spans="1:4">
@@ -13055,9 +12809,7 @@
       <c r="B1026" s="1">
         <v>0</v>
       </c>
-      <c r="C1026" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1026" s="1"/>
       <c r="D1026" s="1"/>
     </row>
     <row r="1027" spans="1:4">
@@ -13067,9 +12819,7 @@
       <c r="B1027" s="1">
         <v>0</v>
       </c>
-      <c r="C1027" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1027" s="1"/>
       <c r="D1027" s="1"/>
     </row>
     <row r="1028" spans="1:4">
@@ -13079,9 +12829,7 @@
       <c r="B1028" s="1">
         <v>0</v>
       </c>
-      <c r="C1028" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1028" s="1"/>
       <c r="D1028" s="1"/>
     </row>
     <row r="1029" spans="1:4">
@@ -13091,9 +12839,7 @@
       <c r="B1029" s="1">
         <v>0</v>
       </c>
-      <c r="C1029" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1029" s="1"/>
       <c r="D1029" s="1"/>
     </row>
     <row r="1030" spans="1:4">
@@ -13103,9 +12849,7 @@
       <c r="B1030" s="1">
         <v>0</v>
       </c>
-      <c r="C1030" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1030" s="1"/>
       <c r="D1030" s="1"/>
     </row>
     <row r="1031" spans="1:4">
@@ -13115,9 +12859,7 @@
       <c r="B1031" s="1">
         <v>0</v>
       </c>
-      <c r="C1031" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1031" s="1"/>
       <c r="D1031" s="1"/>
     </row>
     <row r="1032" spans="1:4">
@@ -13127,9 +12869,7 @@
       <c r="B1032" s="1">
         <v>0</v>
       </c>
-      <c r="C1032" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1032" s="1"/>
       <c r="D1032" s="1"/>
     </row>
     <row r="1033" spans="1:4">
@@ -13139,9 +12879,7 @@
       <c r="B1033" s="1">
         <v>0</v>
       </c>
-      <c r="C1033" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1033" s="1"/>
       <c r="D1033" s="1"/>
     </row>
     <row r="1034" spans="1:4">
@@ -13151,9 +12889,7 @@
       <c r="B1034" s="1">
         <v>0</v>
       </c>
-      <c r="C1034" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1034" s="1"/>
       <c r="D1034" s="1"/>
     </row>
     <row r="1035" spans="1:4">
@@ -13163,9 +12899,7 @@
       <c r="B1035" s="1">
         <v>0</v>
       </c>
-      <c r="C1035" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1035" s="1"/>
       <c r="D1035" s="1"/>
     </row>
     <row r="1036" spans="1:4">
@@ -13175,9 +12909,7 @@
       <c r="B1036" s="1">
         <v>0</v>
       </c>
-      <c r="C1036" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1036" s="1"/>
       <c r="D1036" s="1"/>
     </row>
     <row r="1037" spans="1:4">
@@ -13187,9 +12919,7 @@
       <c r="B1037" s="1">
         <v>0</v>
       </c>
-      <c r="C1037" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1037" s="1"/>
       <c r="D1037" s="1"/>
     </row>
     <row r="1038" spans="1:4">
@@ -13199,9 +12929,7 @@
       <c r="B1038" s="1">
         <v>0</v>
       </c>
-      <c r="C1038" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1038" s="1"/>
       <c r="D1038" s="1"/>
     </row>
     <row r="1039" spans="1:4">
@@ -13211,9 +12939,7 @@
       <c r="B1039" s="1">
         <v>0</v>
       </c>
-      <c r="C1039" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1039" s="1"/>
       <c r="D1039" s="1"/>
     </row>
     <row r="1040" spans="1:4">
@@ -13223,9 +12949,7 @@
       <c r="B1040" s="1">
         <v>0</v>
       </c>
-      <c r="C1040" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1040" s="1"/>
       <c r="D1040" s="1"/>
     </row>
     <row r="1041" spans="1:4">
@@ -13235,9 +12959,7 @@
       <c r="B1041" s="1">
         <v>0</v>
       </c>
-      <c r="C1041" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1041" s="1"/>
       <c r="D1041" s="1"/>
     </row>
     <row r="1042" spans="1:4">
@@ -13247,9 +12969,7 @@
       <c r="B1042" s="1">
         <v>0</v>
       </c>
-      <c r="C1042" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1042" s="1"/>
       <c r="D1042" s="1"/>
     </row>
     <row r="1043" spans="1:4">
@@ -13259,9 +12979,7 @@
       <c r="B1043" s="1">
         <v>0</v>
       </c>
-      <c r="C1043" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1043" s="1"/>
       <c r="D1043" s="1"/>
     </row>
     <row r="1044" spans="1:4">
@@ -13271,9 +12989,7 @@
       <c r="B1044" s="1">
         <v>0</v>
       </c>
-      <c r="C1044" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1044" s="1"/>
       <c r="D1044" s="1"/>
     </row>
     <row r="1045" spans="1:4">
@@ -13283,9 +12999,7 @@
       <c r="B1045" s="1">
         <v>0</v>
       </c>
-      <c r="C1045" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1045" s="1"/>
       <c r="D1045" s="1"/>
     </row>
     <row r="1046" spans="1:4">
@@ -13295,9 +13009,7 @@
       <c r="B1046" s="1">
         <v>0</v>
       </c>
-      <c r="C1046" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1046" s="1"/>
       <c r="D1046" s="1"/>
     </row>
     <row r="1047" spans="1:4">
@@ -13307,9 +13019,7 @@
       <c r="B1047" s="1">
         <v>0</v>
       </c>
-      <c r="C1047" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1047" s="1"/>
       <c r="D1047" s="1"/>
     </row>
     <row r="1048" spans="1:4">
@@ -13319,9 +13029,7 @@
       <c r="B1048" s="1">
         <v>0</v>
       </c>
-      <c r="C1048" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1048" s="1"/>
       <c r="D1048" s="1"/>
     </row>
     <row r="1049" spans="1:4">
@@ -13331,9 +13039,7 @@
       <c r="B1049" s="1">
         <v>0</v>
       </c>
-      <c r="C1049" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1049" s="1"/>
       <c r="D1049" s="1"/>
     </row>
     <row r="1050" spans="1:4">
@@ -13343,9 +13049,7 @@
       <c r="B1050" s="1">
         <v>0</v>
       </c>
-      <c r="C1050" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1050" s="1"/>
       <c r="D1050" s="1"/>
     </row>
     <row r="1051" spans="1:4">
@@ -13355,9 +13059,7 @@
       <c r="B1051" s="1">
         <v>0</v>
       </c>
-      <c r="C1051" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1051" s="1"/>
       <c r="D1051" s="1"/>
     </row>
     <row r="1052" spans="1:4">
@@ -13367,9 +13069,7 @@
       <c r="B1052" s="1">
         <v>0</v>
       </c>
-      <c r="C1052" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1052" s="1"/>
       <c r="D1052" s="1"/>
     </row>
     <row r="1053" spans="1:4">
@@ -13379,9 +13079,7 @@
       <c r="B1053" s="1">
         <v>0</v>
       </c>
-      <c r="C1053" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1053" s="1"/>
       <c r="D1053" s="1"/>
     </row>
     <row r="1054" spans="1:4">
@@ -13391,9 +13089,7 @@
       <c r="B1054" s="1">
         <v>0</v>
       </c>
-      <c r="C1054" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1054" s="1"/>
       <c r="D1054" s="1"/>
     </row>
     <row r="1055" spans="1:4">
@@ -13403,9 +13099,7 @@
       <c r="B1055" s="1">
         <v>0</v>
       </c>
-      <c r="C1055" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1055" s="1"/>
       <c r="D1055" s="1"/>
     </row>
     <row r="1056" spans="1:4">
@@ -13415,9 +13109,7 @@
       <c r="B1056" s="1">
         <v>0</v>
       </c>
-      <c r="C1056" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1056" s="1"/>
       <c r="D1056" s="1"/>
     </row>
     <row r="1057" spans="1:4">
@@ -13427,9 +13119,7 @@
       <c r="B1057" s="1">
         <v>0</v>
       </c>
-      <c r="C1057" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1057" s="1"/>
       <c r="D1057" s="1"/>
     </row>
     <row r="1058" spans="1:4">
@@ -13439,9 +13129,7 @@
       <c r="B1058" s="1">
         <v>0</v>
       </c>
-      <c r="C1058" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1058" s="1"/>
       <c r="D1058" s="1"/>
     </row>
     <row r="1059" spans="1:4">
@@ -13451,9 +13139,7 @@
       <c r="B1059" s="1">
         <v>0</v>
       </c>
-      <c r="C1059" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1059" s="1"/>
       <c r="D1059" s="1"/>
     </row>
     <row r="1060" spans="1:4">
@@ -13463,9 +13149,7 @@
       <c r="B1060" s="1">
         <v>0</v>
       </c>
-      <c r="C1060" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1060" s="1"/>
       <c r="D1060" s="1"/>
     </row>
     <row r="1061" spans="1:4">
@@ -13475,9 +13159,7 @@
       <c r="B1061" s="1">
         <v>0</v>
       </c>
-      <c r="C1061" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1061" s="1"/>
       <c r="D1061" s="1"/>
     </row>
     <row r="1062" spans="1:4">
@@ -13487,9 +13169,7 @@
       <c r="B1062" s="1">
         <v>0</v>
       </c>
-      <c r="C1062" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1062" s="1"/>
       <c r="D1062" s="1"/>
     </row>
     <row r="1063" spans="1:4">
@@ -13499,9 +13179,7 @@
       <c r="B1063" s="1">
         <v>0</v>
       </c>
-      <c r="C1063" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1063" s="1"/>
       <c r="D1063" s="1"/>
     </row>
     <row r="1064" spans="1:4">
@@ -13511,9 +13189,7 @@
       <c r="B1064" s="1">
         <v>0</v>
       </c>
-      <c r="C1064" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1064" s="1"/>
       <c r="D1064" s="1"/>
     </row>
     <row r="1065" spans="1:4">
@@ -13523,9 +13199,7 @@
       <c r="B1065" s="1">
         <v>0</v>
       </c>
-      <c r="C1065" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1065" s="1"/>
       <c r="D1065" s="1"/>
     </row>
     <row r="1066" spans="1:4">
@@ -13535,9 +13209,7 @@
       <c r="B1066" s="1">
         <v>0</v>
       </c>
-      <c r="C1066" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1066" s="1"/>
       <c r="D1066" s="1"/>
     </row>
     <row r="1067" spans="1:4">
@@ -13547,9 +13219,7 @@
       <c r="B1067" s="1">
         <v>0</v>
       </c>
-      <c r="C1067" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1067" s="1"/>
       <c r="D1067" s="1"/>
     </row>
     <row r="1068" spans="1:4">
@@ -13559,9 +13229,7 @@
       <c r="B1068" s="1">
         <v>0</v>
       </c>
-      <c r="C1068" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1068" s="1"/>
       <c r="D1068" s="1"/>
     </row>
     <row r="1069" spans="1:4">
@@ -13571,9 +13239,7 @@
       <c r="B1069" s="1">
         <v>0</v>
       </c>
-      <c r="C1069" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1069" s="1"/>
       <c r="D1069" s="1"/>
     </row>
     <row r="1070" spans="1:4">
@@ -13583,9 +13249,7 @@
       <c r="B1070" s="1">
         <v>0</v>
       </c>
-      <c r="C1070" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1070" s="1"/>
       <c r="D1070" s="1"/>
     </row>
     <row r="1071" spans="1:4">
@@ -13595,9 +13259,7 @@
       <c r="B1071" s="1">
         <v>0</v>
       </c>
-      <c r="C1071" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1071" s="1"/>
       <c r="D1071" s="1"/>
     </row>
     <row r="1072" spans="1:4">
@@ -13607,9 +13269,7 @@
       <c r="B1072" s="1">
         <v>0</v>
       </c>
-      <c r="C1072" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1072" s="1"/>
       <c r="D1072" s="1"/>
     </row>
     <row r="1073" spans="1:4">
@@ -13619,9 +13279,7 @@
       <c r="B1073" s="1">
         <v>0</v>
       </c>
-      <c r="C1073" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1073" s="1"/>
       <c r="D1073" s="1"/>
     </row>
     <row r="1074" spans="1:4">
@@ -13631,9 +13289,7 @@
       <c r="B1074" s="1">
         <v>0</v>
       </c>
-      <c r="C1074" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1074" s="1"/>
       <c r="D1074" s="1"/>
     </row>
     <row r="1075" spans="1:4">
@@ -13643,9 +13299,7 @@
       <c r="B1075" s="1">
         <v>0</v>
       </c>
-      <c r="C1075" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1075" s="1"/>
       <c r="D1075" s="1"/>
     </row>
     <row r="1076" spans="1:4">
@@ -13655,9 +13309,7 @@
       <c r="B1076" s="1">
         <v>0</v>
       </c>
-      <c r="C1076" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1076" s="1"/>
       <c r="D1076" s="1"/>
     </row>
     <row r="1077" spans="1:4">
@@ -13667,9 +13319,7 @@
       <c r="B1077" s="1">
         <v>0</v>
       </c>
-      <c r="C1077" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1077" s="1"/>
       <c r="D1077" s="1"/>
     </row>
     <row r="1078" spans="1:4">
@@ -13679,9 +13329,7 @@
       <c r="B1078" s="1">
         <v>0</v>
       </c>
-      <c r="C1078" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1078" s="1"/>
       <c r="D1078" s="1"/>
     </row>
     <row r="1079" spans="1:4">
@@ -13691,9 +13339,7 @@
       <c r="B1079" s="1">
         <v>0</v>
       </c>
-      <c r="C1079" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1079" s="1"/>
       <c r="D1079" s="1"/>
     </row>
     <row r="1080" spans="1:4">
@@ -13703,9 +13349,7 @@
       <c r="B1080" s="1">
         <v>0</v>
       </c>
-      <c r="C1080" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1080" s="1"/>
       <c r="D1080" s="1"/>
     </row>
     <row r="1081" spans="1:4">
@@ -13715,9 +13359,7 @@
       <c r="B1081" s="1">
         <v>0</v>
       </c>
-      <c r="C1081" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1081" s="1"/>
       <c r="D1081" s="1"/>
     </row>
     <row r="1082" spans="1:4">
@@ -13727,9 +13369,7 @@
       <c r="B1082" s="1">
         <v>0</v>
       </c>
-      <c r="C1082" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1082" s="1"/>
       <c r="D1082" s="1"/>
     </row>
     <row r="1083" spans="1:4">
@@ -13739,9 +13379,7 @@
       <c r="B1083" s="1">
         <v>0</v>
       </c>
-      <c r="C1083" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1083" s="1"/>
       <c r="D1083" s="1"/>
     </row>
     <row r="1084" spans="1:4">
@@ -13751,9 +13389,7 @@
       <c r="B1084" s="1">
         <v>0</v>
       </c>
-      <c r="C1084" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1084" s="1"/>
       <c r="D1084" s="1"/>
     </row>
     <row r="1085" spans="1:4">
@@ -13763,9 +13399,7 @@
       <c r="B1085" s="1">
         <v>0</v>
       </c>
-      <c r="C1085" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1085" s="1"/>
       <c r="D1085" s="1"/>
     </row>
     <row r="1086" spans="1:4">
@@ -13775,9 +13409,7 @@
       <c r="B1086" s="1">
         <v>0</v>
       </c>
-      <c r="C1086" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1086" s="1"/>
       <c r="D1086" s="1"/>
     </row>
     <row r="1087" spans="1:4">
@@ -13787,9 +13419,7 @@
       <c r="B1087" s="1">
         <v>0</v>
       </c>
-      <c r="C1087" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1087" s="1"/>
       <c r="D1087" s="1"/>
     </row>
     <row r="1088" spans="1:4">
@@ -13799,9 +13429,7 @@
       <c r="B1088" s="1">
         <v>0</v>
       </c>
-      <c r="C1088" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1088" s="1"/>
       <c r="D1088" s="1"/>
     </row>
     <row r="1089" spans="1:4">
@@ -13811,9 +13439,7 @@
       <c r="B1089" s="1">
         <v>0</v>
       </c>
-      <c r="C1089" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1089" s="1"/>
       <c r="D1089" s="1"/>
     </row>
     <row r="1090" spans="1:4">
@@ -13823,9 +13449,7 @@
       <c r="B1090" s="1">
         <v>0</v>
       </c>
-      <c r="C1090" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1090" s="1"/>
       <c r="D1090" s="1"/>
     </row>
     <row r="1091" spans="1:4">
@@ -13835,9 +13459,7 @@
       <c r="B1091" s="1">
         <v>0</v>
       </c>
-      <c r="C1091" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1091" s="1"/>
       <c r="D1091" s="1"/>
     </row>
     <row r="1092" spans="1:4">
@@ -13847,9 +13469,7 @@
       <c r="B1092" s="1">
         <v>0</v>
       </c>
-      <c r="C1092" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1092" s="1"/>
       <c r="D1092" s="1"/>
     </row>
     <row r="1093" spans="1:4">
@@ -13859,9 +13479,7 @@
       <c r="B1093" s="1">
         <v>0</v>
       </c>
-      <c r="C1093" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1093" s="1"/>
       <c r="D1093" s="1"/>
     </row>
     <row r="1094" spans="1:4">
@@ -13871,9 +13489,7 @@
       <c r="B1094" s="1">
         <v>0</v>
       </c>
-      <c r="C1094" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1094" s="1"/>
       <c r="D1094" s="1"/>
     </row>
     <row r="1095" spans="1:4">
@@ -13883,9 +13499,7 @@
       <c r="B1095" s="1">
         <v>0</v>
       </c>
-      <c r="C1095" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1095" s="1"/>
       <c r="D1095" s="1"/>
     </row>
     <row r="1096" spans="1:4">
@@ -13895,9 +13509,7 @@
       <c r="B1096" s="1">
         <v>0</v>
       </c>
-      <c r="C1096" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1096" s="1"/>
       <c r="D1096" s="1"/>
     </row>
     <row r="1097" spans="1:4">
@@ -13907,9 +13519,7 @@
       <c r="B1097" s="1">
         <v>0</v>
       </c>
-      <c r="C1097" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1097" s="1"/>
       <c r="D1097" s="1"/>
     </row>
     <row r="1098" spans="1:4">
@@ -13919,9 +13529,7 @@
       <c r="B1098" s="1">
         <v>0</v>
       </c>
-      <c r="C1098" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1098" s="1"/>
       <c r="D1098" s="1"/>
     </row>
     <row r="1099" spans="1:4">
@@ -13931,9 +13539,7 @@
       <c r="B1099" s="1">
         <v>0</v>
       </c>
-      <c r="C1099" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1099" s="1"/>
       <c r="D1099" s="1"/>
     </row>
     <row r="1100" spans="1:4">
@@ -13943,9 +13549,7 @@
       <c r="B1100" s="1">
         <v>0</v>
       </c>
-      <c r="C1100" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1100" s="1"/>
       <c r="D1100" s="1"/>
     </row>
     <row r="1101" spans="1:4">
@@ -13955,9 +13559,7 @@
       <c r="B1101" s="1">
         <v>0</v>
       </c>
-      <c r="C1101" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1101" s="1"/>
       <c r="D1101" s="1"/>
     </row>
     <row r="1102" spans="1:4">
@@ -13967,9 +13569,7 @@
       <c r="B1102" s="1">
         <v>0</v>
       </c>
-      <c r="C1102" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1102" s="1"/>
       <c r="D1102" s="1"/>
     </row>
     <row r="1103" spans="1:4">
@@ -13979,9 +13579,7 @@
       <c r="B1103" s="1">
         <v>0</v>
       </c>
-      <c r="C1103" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1103" s="1"/>
       <c r="D1103" s="1"/>
     </row>
     <row r="1104" spans="1:4">
@@ -13991,9 +13589,7 @@
       <c r="B1104" s="1">
         <v>0</v>
       </c>
-      <c r="C1104" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1104" s="1"/>
       <c r="D1104" s="1"/>
     </row>
     <row r="1105" spans="1:4">
@@ -14003,9 +13599,7 @@
       <c r="B1105" s="1">
         <v>0</v>
       </c>
-      <c r="C1105" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1105" s="1"/>
       <c r="D1105" s="1"/>
     </row>
     <row r="1106" spans="1:4">
@@ -14015,9 +13609,7 @@
       <c r="B1106" s="1">
         <v>0</v>
       </c>
-      <c r="C1106" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1106" s="1"/>
       <c r="D1106" s="1"/>
     </row>
     <row r="1107" spans="1:4">
@@ -14027,9 +13619,7 @@
       <c r="B1107" s="1">
         <v>0</v>
       </c>
-      <c r="C1107" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1107" s="1"/>
       <c r="D1107" s="1"/>
     </row>
     <row r="1108" spans="1:4">
@@ -14039,9 +13629,7 @@
       <c r="B1108" s="1">
         <v>0</v>
       </c>
-      <c r="C1108" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1108" s="1"/>
       <c r="D1108" s="1"/>
     </row>
     <row r="1109" spans="1:4">
@@ -14051,9 +13639,7 @@
       <c r="B1109" s="1">
         <v>0</v>
       </c>
-      <c r="C1109" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1109" s="1"/>
       <c r="D1109" s="1"/>
     </row>
     <row r="1110" spans="1:4">
@@ -14063,9 +13649,7 @@
       <c r="B1110" s="1">
         <v>0</v>
       </c>
-      <c r="C1110" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1110" s="1"/>
       <c r="D1110" s="1"/>
     </row>
     <row r="1111" spans="1:4">
@@ -14075,9 +13659,7 @@
       <c r="B1111" s="1">
         <v>0</v>
       </c>
-      <c r="C1111" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1111" s="1"/>
       <c r="D1111" s="1"/>
     </row>
     <row r="1112" spans="1:4">
@@ -14087,9 +13669,7 @@
       <c r="B1112" s="1">
         <v>0</v>
       </c>
-      <c r="C1112" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1112" s="1"/>
       <c r="D1112" s="1"/>
     </row>
     <row r="1113" spans="1:4">
@@ -14099,9 +13679,7 @@
       <c r="B1113" s="1">
         <v>0</v>
       </c>
-      <c r="C1113" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1113" s="1"/>
       <c r="D1113" s="1"/>
     </row>
     <row r="1114" spans="1:4">
@@ -14111,9 +13689,7 @@
       <c r="B1114" s="1">
         <v>0</v>
       </c>
-      <c r="C1114" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1114" s="1"/>
       <c r="D1114" s="1"/>
     </row>
     <row r="1115" spans="1:4">
@@ -14123,9 +13699,7 @@
       <c r="B1115" s="1">
         <v>0</v>
       </c>
-      <c r="C1115" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1115" s="1"/>
       <c r="D1115" s="1"/>
     </row>
     <row r="1116" spans="1:4">
@@ -14135,9 +13709,7 @@
       <c r="B1116" s="1">
         <v>0</v>
       </c>
-      <c r="C1116" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1116" s="1"/>
       <c r="D1116" s="1"/>
     </row>
     <row r="1117" spans="1:4">
@@ -14147,9 +13719,7 @@
       <c r="B1117" s="1">
         <v>0</v>
       </c>
-      <c r="C1117" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1117" s="1"/>
       <c r="D1117" s="1"/>
     </row>
     <row r="1118" spans="1:4">
@@ -14159,9 +13729,7 @@
       <c r="B1118" s="1">
         <v>0</v>
       </c>
-      <c r="C1118" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1118" s="1"/>
       <c r="D1118" s="1"/>
     </row>
     <row r="1119" spans="1:4">
@@ -14171,9 +13739,7 @@
       <c r="B1119" s="1">
         <v>0</v>
       </c>
-      <c r="C1119" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1119" s="1"/>
       <c r="D1119" s="1"/>
     </row>
     <row r="1120" spans="1:4">
@@ -14183,9 +13749,7 @@
       <c r="B1120" s="1">
         <v>0</v>
       </c>
-      <c r="C1120" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1120" s="1"/>
       <c r="D1120" s="1"/>
     </row>
     <row r="1121" spans="1:4">
@@ -14195,9 +13759,7 @@
       <c r="B1121" s="1">
         <v>0</v>
       </c>
-      <c r="C1121" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1121" s="1"/>
       <c r="D1121" s="1"/>
     </row>
     <row r="1122" spans="1:4">
@@ -14207,9 +13769,7 @@
       <c r="B1122" s="1">
         <v>0</v>
       </c>
-      <c r="C1122" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1122" s="1"/>
       <c r="D1122" s="1"/>
     </row>
     <row r="1123" spans="1:4">
@@ -14219,9 +13779,7 @@
       <c r="B1123" s="1">
         <v>0</v>
       </c>
-      <c r="C1123" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1123" s="1"/>
       <c r="D1123" s="1"/>
     </row>
     <row r="1124" spans="1:4">
@@ -14231,9 +13789,7 @@
       <c r="B1124" s="1">
         <v>0</v>
       </c>
-      <c r="C1124" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1124" s="1"/>
       <c r="D1124" s="1"/>
     </row>
     <row r="1125" spans="1:4">
@@ -14243,9 +13799,7 @@
       <c r="B1125" s="1">
         <v>0</v>
       </c>
-      <c r="C1125" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1125" s="1"/>
       <c r="D1125" s="1"/>
     </row>
     <row r="1126" spans="1:4">
@@ -14255,9 +13809,7 @@
       <c r="B1126" s="1">
         <v>0</v>
       </c>
-      <c r="C1126" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1126" s="1"/>
       <c r="D1126" s="1"/>
     </row>
     <row r="1127" spans="1:4">
@@ -14267,9 +13819,7 @@
       <c r="B1127" s="1">
         <v>0</v>
       </c>
-      <c r="C1127" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1127" s="1"/>
       <c r="D1127" s="1"/>
     </row>
     <row r="1128" spans="1:4">
@@ -14279,9 +13829,7 @@
       <c r="B1128" s="1">
         <v>0</v>
       </c>
-      <c r="C1128" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1128" s="1"/>
       <c r="D1128" s="1"/>
     </row>
     <row r="1129" spans="1:4">
@@ -14291,9 +13839,7 @@
       <c r="B1129" s="1">
         <v>0</v>
       </c>
-      <c r="C1129" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1129" s="1"/>
       <c r="D1129" s="1"/>
     </row>
     <row r="1130" spans="1:4">
@@ -14303,9 +13849,7 @@
       <c r="B1130" s="1">
         <v>0</v>
       </c>
-      <c r="C1130" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1130" s="1"/>
       <c r="D1130" s="1"/>
     </row>
     <row r="1131" spans="1:4">
@@ -14315,9 +13859,7 @@
       <c r="B1131" s="1">
         <v>0</v>
       </c>
-      <c r="C1131" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1131" s="1"/>
       <c r="D1131" s="1"/>
     </row>
     <row r="1132" spans="1:4">
@@ -14327,9 +13869,7 @@
       <c r="B1132" s="1">
         <v>0</v>
       </c>
-      <c r="C1132" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1132" s="1"/>
       <c r="D1132" s="1"/>
     </row>
     <row r="1133" spans="1:4">
@@ -14339,9 +13879,7 @@
       <c r="B1133" s="1">
         <v>0</v>
       </c>
-      <c r="C1133" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1133" s="1"/>
       <c r="D1133" s="1"/>
     </row>
     <row r="1134" spans="1:4">
@@ -14351,9 +13889,7 @@
       <c r="B1134" s="1">
         <v>0</v>
       </c>
-      <c r="C1134" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1134" s="1"/>
       <c r="D1134" s="1"/>
     </row>
     <row r="1135" spans="1:4">
@@ -14363,9 +13899,7 @@
       <c r="B1135" s="1">
         <v>0</v>
       </c>
-      <c r="C1135" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1135" s="1"/>
       <c r="D1135" s="1"/>
     </row>
     <row r="1136" spans="1:4">
@@ -14375,9 +13909,7 @@
       <c r="B1136" s="1">
         <v>0</v>
       </c>
-      <c r="C1136" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1136" s="1"/>
       <c r="D1136" s="1"/>
     </row>
     <row r="1137" spans="1:4">
@@ -14387,9 +13919,7 @@
       <c r="B1137" s="1">
         <v>0</v>
       </c>
-      <c r="C1137" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1137" s="1"/>
       <c r="D1137" s="1"/>
     </row>
     <row r="1138" spans="1:4">
@@ -14399,9 +13929,7 @@
       <c r="B1138" s="1">
         <v>0</v>
       </c>
-      <c r="C1138" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1138" s="1"/>
       <c r="D1138" s="1"/>
     </row>
     <row r="1139" spans="1:4">
@@ -14411,9 +13939,7 @@
       <c r="B1139" s="1">
         <v>0</v>
       </c>
-      <c r="C1139" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1139" s="1"/>
       <c r="D1139" s="1"/>
     </row>
     <row r="1140" spans="1:4">
@@ -14423,9 +13949,7 @@
       <c r="B1140" s="1">
         <v>0</v>
       </c>
-      <c r="C1140" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1140" s="1"/>
       <c r="D1140" s="1"/>
     </row>
     <row r="1141" spans="1:4">
@@ -14435,9 +13959,7 @@
       <c r="B1141" s="1">
         <v>0</v>
       </c>
-      <c r="C1141" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1141" s="1"/>
       <c r="D1141" s="1"/>
     </row>
     <row r="1142" spans="1:4">
@@ -14447,9 +13969,7 @@
       <c r="B1142" s="1">
         <v>0</v>
       </c>
-      <c r="C1142" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1142" s="1"/>
       <c r="D1142" s="1"/>
     </row>
     <row r="1143" spans="1:4">
@@ -14459,9 +13979,7 @@
       <c r="B1143" s="1">
         <v>0</v>
       </c>
-      <c r="C1143" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1143" s="1"/>
       <c r="D1143" s="1"/>
     </row>
     <row r="1144" spans="1:4">
@@ -14471,9 +13989,7 @@
       <c r="B1144" s="1">
         <v>0</v>
       </c>
-      <c r="C1144" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1144" s="1"/>
       <c r="D1144" s="1"/>
     </row>
     <row r="1145" spans="1:4">
@@ -14483,9 +13999,7 @@
       <c r="B1145" s="1">
         <v>0</v>
       </c>
-      <c r="C1145" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1145" s="1"/>
       <c r="D1145" s="1"/>
     </row>
     <row r="1146" spans="1:4">
@@ -14495,9 +14009,7 @@
       <c r="B1146" s="1">
         <v>0</v>
       </c>
-      <c r="C1146" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1146" s="1"/>
       <c r="D1146" s="1"/>
     </row>
     <row r="1147" spans="1:4">
@@ -14507,9 +14019,7 @@
       <c r="B1147" s="1">
         <v>0</v>
       </c>
-      <c r="C1147" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1147" s="1"/>
       <c r="D1147" s="1"/>
     </row>
     <row r="1148" spans="1:4">
@@ -14519,9 +14029,7 @@
       <c r="B1148" s="1">
         <v>0</v>
       </c>
-      <c r="C1148" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1148" s="1"/>
       <c r="D1148" s="1"/>
     </row>
     <row r="1149" spans="1:4">
@@ -14531,9 +14039,7 @@
       <c r="B1149" s="1">
         <v>0</v>
       </c>
-      <c r="C1149" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1149" s="1"/>
       <c r="D1149" s="1"/>
     </row>
     <row r="1150" spans="1:4">
@@ -14543,9 +14049,7 @@
       <c r="B1150" s="1">
         <v>0</v>
       </c>
-      <c r="C1150" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1150" s="1"/>
       <c r="D1150" s="1"/>
     </row>
     <row r="1151" spans="1:4">
@@ -14555,9 +14059,7 @@
       <c r="B1151" s="1">
         <v>0</v>
       </c>
-      <c r="C1151" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1151" s="1"/>
       <c r="D1151" s="1"/>
     </row>
     <row r="1152" spans="1:4">
@@ -14567,9 +14069,7 @@
       <c r="B1152" s="1">
         <v>0</v>
       </c>
-      <c r="C1152" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1152" s="1"/>
       <c r="D1152" s="1"/>
     </row>
     <row r="1153" spans="1:4">
@@ -14579,9 +14079,7 @@
       <c r="B1153" s="1">
         <v>0</v>
       </c>
-      <c r="C1153" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1153" s="1"/>
       <c r="D1153" s="1"/>
     </row>
     <row r="1154" spans="1:4">
@@ -14591,9 +14089,7 @@
       <c r="B1154" s="1">
         <v>0</v>
       </c>
-      <c r="C1154" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1154" s="1"/>
       <c r="D1154" s="1"/>
     </row>
     <row r="1155" spans="1:4">
@@ -14603,9 +14099,7 @@
       <c r="B1155" s="1">
         <v>0</v>
       </c>
-      <c r="C1155" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1155" s="1"/>
       <c r="D1155" s="1"/>
     </row>
     <row r="1156" spans="1:4">
@@ -14615,9 +14109,7 @@
       <c r="B1156" s="1">
         <v>0</v>
       </c>
-      <c r="C1156" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1156" s="1"/>
       <c r="D1156" s="1"/>
     </row>
     <row r="1157" spans="1:4">
@@ -14627,9 +14119,7 @@
       <c r="B1157" s="1">
         <v>0</v>
       </c>
-      <c r="C1157" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1157" s="1"/>
       <c r="D1157" s="1"/>
     </row>
     <row r="1158" spans="1:4">
@@ -14639,9 +14129,7 @@
       <c r="B1158" s="1">
         <v>0</v>
       </c>
-      <c r="C1158" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1158" s="1"/>
       <c r="D1158" s="1"/>
     </row>
     <row r="1159" spans="1:4">
@@ -14651,9 +14139,7 @@
       <c r="B1159" s="1">
         <v>0</v>
       </c>
-      <c r="C1159" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1159" s="1"/>
       <c r="D1159" s="1"/>
     </row>
     <row r="1160" spans="1:4">
@@ -14663,9 +14149,7 @@
       <c r="B1160" s="1">
         <v>0</v>
       </c>
-      <c r="C1160" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1160" s="1"/>
       <c r="D1160" s="1"/>
     </row>
     <row r="1161" spans="1:4">
@@ -14675,9 +14159,7 @@
       <c r="B1161" s="1">
         <v>0</v>
       </c>
-      <c r="C1161" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1161" s="1"/>
       <c r="D1161" s="1"/>
     </row>
     <row r="1162" spans="1:4">
@@ -14687,9 +14169,7 @@
       <c r="B1162" s="1">
         <v>0</v>
       </c>
-      <c r="C1162" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1162" s="1"/>
       <c r="D1162" s="1"/>
     </row>
     <row r="1163" spans="1:4">
@@ -14699,9 +14179,7 @@
       <c r="B1163" s="1">
         <v>0</v>
       </c>
-      <c r="C1163" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1163" s="1"/>
       <c r="D1163" s="1"/>
     </row>
     <row r="1164" spans="1:4">
@@ -14711,9 +14189,7 @@
       <c r="B1164" s="1">
         <v>0</v>
       </c>
-      <c r="C1164" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1164" s="1"/>
       <c r="D1164" s="1"/>
     </row>
     <row r="1165" spans="1:4">
@@ -14723,9 +14199,7 @@
       <c r="B1165" s="1">
         <v>0</v>
       </c>
-      <c r="C1165" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1165" s="1"/>
       <c r="D1165" s="1"/>
     </row>
     <row r="1166" spans="1:4">
@@ -14735,9 +14209,7 @@
       <c r="B1166" s="1">
         <v>0</v>
       </c>
-      <c r="C1166" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1166" s="1"/>
       <c r="D1166" s="1"/>
     </row>
     <row r="1167" spans="1:4">
@@ -14747,9 +14219,7 @@
       <c r="B1167" s="1">
         <v>0</v>
       </c>
-      <c r="C1167" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1167" s="1"/>
       <c r="D1167" s="1"/>
     </row>
     <row r="1168" spans="1:4">
@@ -14759,9 +14229,7 @@
       <c r="B1168" s="1">
         <v>0</v>
       </c>
-      <c r="C1168" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1168" s="1"/>
       <c r="D1168" s="1"/>
     </row>
     <row r="1169" spans="1:4">
@@ -14771,9 +14239,7 @@
       <c r="B1169" s="1">
         <v>0</v>
       </c>
-      <c r="C1169" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1169" s="1"/>
       <c r="D1169" s="1"/>
     </row>
     <row r="1170" spans="1:4">
@@ -14783,9 +14249,7 @@
       <c r="B1170" s="1">
         <v>0</v>
       </c>
-      <c r="C1170" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1170" s="1"/>
       <c r="D1170" s="1"/>
     </row>
     <row r="1171" spans="1:4">
@@ -14795,9 +14259,7 @@
       <c r="B1171" s="1">
         <v>0</v>
       </c>
-      <c r="C1171" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1171" s="1"/>
       <c r="D1171" s="1"/>
     </row>
     <row r="1172" spans="1:4">
@@ -14807,9 +14269,7 @@
       <c r="B1172" s="1">
         <v>0</v>
       </c>
-      <c r="C1172" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1172" s="1"/>
       <c r="D1172" s="1"/>
     </row>
     <row r="1173" spans="1:4">
@@ -14819,9 +14279,7 @@
       <c r="B1173" s="1">
         <v>0</v>
       </c>
-      <c r="C1173" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1173" s="1"/>
       <c r="D1173" s="1"/>
     </row>
     <row r="1174" spans="1:4">
@@ -14831,9 +14289,7 @@
       <c r="B1174" s="1">
         <v>0</v>
       </c>
-      <c r="C1174" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1174" s="1"/>
       <c r="D1174" s="1"/>
     </row>
     <row r="1175" spans="1:4">
@@ -14843,9 +14299,7 @@
       <c r="B1175" s="1">
         <v>0</v>
       </c>
-      <c r="C1175" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1175" s="1"/>
       <c r="D1175" s="1"/>
     </row>
     <row r="1176" spans="1:4">
@@ -14855,9 +14309,7 @@
       <c r="B1176" s="1">
         <v>0</v>
       </c>
-      <c r="C1176" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1176" s="1"/>
       <c r="D1176" s="1"/>
     </row>
     <row r="1177" spans="1:4">
@@ -14867,9 +14319,7 @@
       <c r="B1177" s="1">
         <v>0</v>
       </c>
-      <c r="C1177" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1177" s="1"/>
       <c r="D1177" s="1"/>
     </row>
     <row r="1178" spans="1:4">
@@ -14879,9 +14329,7 @@
       <c r="B1178" s="1">
         <v>0</v>
       </c>
-      <c r="C1178" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1178" s="1"/>
       <c r="D1178" s="1"/>
     </row>
     <row r="1179" spans="1:4">
@@ -14891,9 +14339,7 @@
       <c r="B1179" s="1">
         <v>0</v>
       </c>
-      <c r="C1179" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1179" s="1"/>
       <c r="D1179" s="1"/>
     </row>
     <row r="1180" spans="1:4">
@@ -14903,9 +14349,7 @@
       <c r="B1180" s="1">
         <v>0</v>
       </c>
-      <c r="C1180" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1180" s="1"/>
       <c r="D1180" s="1"/>
     </row>
     <row r="1181" spans="1:4">
@@ -14915,9 +14359,7 @@
       <c r="B1181" s="1">
         <v>0</v>
       </c>
-      <c r="C1181" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1181" s="1"/>
       <c r="D1181" s="1"/>
     </row>
     <row r="1182" spans="1:4">
@@ -14927,9 +14369,7 @@
       <c r="B1182" s="1">
         <v>0</v>
       </c>
-      <c r="C1182" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1182" s="1"/>
       <c r="D1182" s="1"/>
     </row>
     <row r="1183" spans="1:4">
@@ -14939,9 +14379,7 @@
       <c r="B1183" s="1">
         <v>0</v>
       </c>
-      <c r="C1183" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1183" s="1"/>
       <c r="D1183" s="1"/>
     </row>
     <row r="1184" spans="1:4">
@@ -14951,9 +14389,7 @@
       <c r="B1184" s="1">
         <v>0</v>
       </c>
-      <c r="C1184" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1184" s="1"/>
       <c r="D1184" s="1"/>
     </row>
     <row r="1185" spans="1:4">
@@ -14963,9 +14399,7 @@
       <c r="B1185" s="1">
         <v>0</v>
       </c>
-      <c r="C1185" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1185" s="1"/>
       <c r="D1185" s="1"/>
     </row>
     <row r="1186" spans="1:4">
@@ -14975,9 +14409,7 @@
       <c r="B1186" s="1">
         <v>0</v>
       </c>
-      <c r="C1186" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1186" s="1"/>
       <c r="D1186" s="1"/>
     </row>
     <row r="1187" spans="1:4">
@@ -14987,9 +14419,7 @@
       <c r="B1187" s="1">
         <v>0</v>
       </c>
-      <c r="C1187" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1187" s="1"/>
       <c r="D1187" s="1"/>
     </row>
     <row r="1188" spans="1:4">
@@ -14999,9 +14429,7 @@
       <c r="B1188" s="1">
         <v>0</v>
       </c>
-      <c r="C1188" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1188" s="1"/>
       <c r="D1188" s="1"/>
     </row>
     <row r="1189" spans="1:4">
@@ -15011,9 +14439,7 @@
       <c r="B1189" s="1">
         <v>0</v>
       </c>
-      <c r="C1189" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1189" s="1"/>
       <c r="D1189" s="1"/>
     </row>
     <row r="1190" spans="1:4">
@@ -15023,9 +14449,7 @@
       <c r="B1190" s="1">
         <v>0</v>
       </c>
-      <c r="C1190" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1190" s="1"/>
       <c r="D1190" s="1"/>
     </row>
     <row r="1191" spans="1:4">
@@ -15035,9 +14459,7 @@
       <c r="B1191" s="1">
         <v>0</v>
       </c>
-      <c r="C1191" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1191" s="1"/>
       <c r="D1191" s="1"/>
     </row>
     <row r="1192" spans="1:4">
@@ -15047,9 +14469,7 @@
       <c r="B1192" s="1">
         <v>0</v>
       </c>
-      <c r="C1192" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1192" s="1"/>
       <c r="D1192" s="1"/>
     </row>
     <row r="1193" spans="1:4">
@@ -15059,9 +14479,7 @@
       <c r="B1193" s="1">
         <v>0</v>
       </c>
-      <c r="C1193" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1193" s="1"/>
       <c r="D1193" s="1"/>
     </row>
     <row r="1194" spans="1:4">
@@ -15071,9 +14489,7 @@
       <c r="B1194" s="1">
         <v>0</v>
       </c>
-      <c r="C1194" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1194" s="1"/>
       <c r="D1194" s="1"/>
     </row>
     <row r="1195" spans="1:4">
@@ -15083,9 +14499,7 @@
       <c r="B1195" s="1">
         <v>0</v>
       </c>
-      <c r="C1195" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1195" s="1"/>
       <c r="D1195" s="1"/>
     </row>
     <row r="1196" spans="1:4">
@@ -15095,9 +14509,7 @@
       <c r="B1196" s="1">
         <v>0</v>
       </c>
-      <c r="C1196" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1196" s="1"/>
       <c r="D1196" s="1"/>
     </row>
     <row r="1197" spans="1:4">
@@ -15107,9 +14519,7 @@
       <c r="B1197" s="1">
         <v>0</v>
       </c>
-      <c r="C1197" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1197" s="1"/>
       <c r="D1197" s="1"/>
     </row>
     <row r="1198" spans="1:4">
@@ -15119,9 +14529,7 @@
       <c r="B1198" s="1">
         <v>0</v>
       </c>
-      <c r="C1198" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1198" s="1"/>
       <c r="D1198" s="1"/>
     </row>
     <row r="1199" spans="1:4">
@@ -15131,9 +14539,7 @@
       <c r="B1199" s="1">
         <v>0</v>
       </c>
-      <c r="C1199" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1199" s="1"/>
       <c r="D1199" s="1"/>
     </row>
     <row r="1200" spans="1:4">
@@ -15143,9 +14549,7 @@
       <c r="B1200" s="1">
         <v>0</v>
       </c>
-      <c r="C1200" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1200" s="1"/>
       <c r="D1200" s="1"/>
     </row>
     <row r="1201" spans="1:4">
@@ -15155,9 +14559,7 @@
       <c r="B1201" s="1">
         <v>0</v>
       </c>
-      <c r="C1201" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1201" s="1"/>
       <c r="D1201" s="1"/>
     </row>
     <row r="1202" spans="1:4">
@@ -15167,9 +14569,7 @@
       <c r="B1202" s="1">
         <v>0</v>
       </c>
-      <c r="C1202" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1202" s="1"/>
       <c r="D1202" s="1"/>
     </row>
     <row r="1203" spans="1:4">
@@ -15179,9 +14579,7 @@
       <c r="B1203" s="1">
         <v>0</v>
       </c>
-      <c r="C1203" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1203" s="1"/>
       <c r="D1203" s="1"/>
     </row>
     <row r="1204" spans="1:4">
@@ -15191,9 +14589,7 @@
       <c r="B1204" s="1">
         <v>0</v>
       </c>
-      <c r="C1204" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1204" s="1"/>
       <c r="D1204" s="1"/>
     </row>
     <row r="1205" spans="1:4">
@@ -15203,9 +14599,7 @@
       <c r="B1205" s="1">
         <v>0</v>
       </c>
-      <c r="C1205" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1205" s="1"/>
       <c r="D1205" s="1"/>
     </row>
     <row r="1206" spans="1:4">
@@ -15215,9 +14609,7 @@
       <c r="B1206" s="1">
         <v>0</v>
       </c>
-      <c r="C1206" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1206" s="1"/>
       <c r="D1206" s="1"/>
     </row>
     <row r="1207" spans="1:4">
@@ -15227,9 +14619,7 @@
       <c r="B1207" s="1">
         <v>0</v>
       </c>
-      <c r="C1207" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1207" s="1"/>
       <c r="D1207" s="1"/>
     </row>
     <row r="1208" spans="1:4">
@@ -15239,9 +14629,7 @@
       <c r="B1208" s="1">
         <v>0</v>
       </c>
-      <c r="C1208" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1208" s="1"/>
       <c r="D1208" s="1"/>
     </row>
     <row r="1209" spans="1:4">
@@ -15251,9 +14639,7 @@
       <c r="B1209" s="1">
         <v>0</v>
       </c>
-      <c r="C1209" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1209" s="1"/>
       <c r="D1209" s="1"/>
     </row>
     <row r="1210" spans="1:4">
@@ -15263,9 +14649,7 @@
       <c r="B1210" s="1">
         <v>0</v>
       </c>
-      <c r="C1210" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1210" s="1"/>
       <c r="D1210" s="1"/>
     </row>
     <row r="1211" spans="1:4">
@@ -15275,9 +14659,7 @@
       <c r="B1211" s="1">
         <v>0</v>
       </c>
-      <c r="C1211" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1211" s="1"/>
       <c r="D1211" s="1"/>
     </row>
     <row r="1212" spans="1:4">
@@ -15287,9 +14669,7 @@
       <c r="B1212" s="1">
         <v>0</v>
       </c>
-      <c r="C1212" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1212" s="1"/>
       <c r="D1212" s="1"/>
     </row>
     <row r="1213" spans="1:4">
@@ -15299,9 +14679,7 @@
       <c r="B1213" s="1">
         <v>0</v>
       </c>
-      <c r="C1213" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1213" s="1"/>
       <c r="D1213" s="1"/>
     </row>
     <row r="1214" spans="1:4">
@@ -15311,9 +14689,7 @@
       <c r="B1214" s="1">
         <v>0</v>
       </c>
-      <c r="C1214" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1214" s="1"/>
       <c r="D1214" s="1"/>
     </row>
     <row r="1215" spans="1:4">
@@ -15323,9 +14699,7 @@
       <c r="B1215" s="1">
         <v>0</v>
       </c>
-      <c r="C1215" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1215" s="1"/>
       <c r="D1215" s="1"/>
     </row>
     <row r="1216" spans="1:4">
@@ -15335,9 +14709,7 @@
       <c r="B1216" s="1">
         <v>0</v>
       </c>
-      <c r="C1216" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1216" s="1"/>
       <c r="D1216" s="1"/>
     </row>
     <row r="1217" spans="1:4">
@@ -15347,9 +14719,7 @@
       <c r="B1217" s="1">
         <v>0</v>
       </c>
-      <c r="C1217" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1217" s="1"/>
       <c r="D1217" s="1"/>
     </row>
     <row r="1218" spans="1:4">
@@ -15359,9 +14729,7 @@
       <c r="B1218" s="1">
         <v>0</v>
       </c>
-      <c r="C1218" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1218" s="1"/>
       <c r="D1218" s="1"/>
     </row>
     <row r="1219" spans="1:4">
@@ -15371,9 +14739,7 @@
       <c r="B1219" s="1">
         <v>0</v>
       </c>
-      <c r="C1219" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1219" s="1"/>
       <c r="D1219" s="1"/>
     </row>
     <row r="1220" spans="1:4">
@@ -15383,9 +14749,7 @@
       <c r="B1220" s="1">
         <v>0</v>
       </c>
-      <c r="C1220" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1220" s="1"/>
       <c r="D1220" s="1"/>
     </row>
     <row r="1221" spans="1:4">
@@ -15395,9 +14759,7 @@
       <c r="B1221" s="1">
         <v>0</v>
       </c>
-      <c r="C1221" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1221" s="1"/>
       <c r="D1221" s="1"/>
     </row>
     <row r="1222" spans="1:4">
@@ -15407,9 +14769,7 @@
       <c r="B1222" s="1">
         <v>0</v>
       </c>
-      <c r="C1222" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1222" s="1"/>
       <c r="D1222" s="1"/>
     </row>
     <row r="1223" spans="1:4">
@@ -15419,9 +14779,7 @@
       <c r="B1223" s="1">
         <v>0</v>
       </c>
-      <c r="C1223" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1223" s="1"/>
       <c r="D1223" s="1"/>
     </row>
     <row r="1224" spans="1:4">
@@ -15431,9 +14789,7 @@
       <c r="B1224" s="1">
         <v>0</v>
       </c>
-      <c r="C1224" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1224" s="1"/>
       <c r="D1224" s="1"/>
     </row>
     <row r="1225" spans="1:4">
@@ -15443,9 +14799,7 @@
       <c r="B1225" s="1">
         <v>0</v>
       </c>
-      <c r="C1225" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1225" s="1"/>
       <c r="D1225" s="1"/>
     </row>
     <row r="1226" spans="1:4">
@@ -15455,9 +14809,7 @@
       <c r="B1226" s="1">
         <v>0</v>
       </c>
-      <c r="C1226" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1226" s="1"/>
       <c r="D1226" s="1"/>
     </row>
     <row r="1227" spans="1:4">
@@ -15467,9 +14819,7 @@
       <c r="B1227" s="1">
         <v>0</v>
       </c>
-      <c r="C1227" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1227" s="1"/>
       <c r="D1227" s="1"/>
     </row>
     <row r="1228" spans="1:4">
@@ -15479,9 +14829,7 @@
       <c r="B1228" s="1">
         <v>0</v>
       </c>
-      <c r="C1228" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1228" s="1"/>
       <c r="D1228" s="1"/>
     </row>
     <row r="1229" spans="1:4">
@@ -15491,9 +14839,7 @@
       <c r="B1229" s="1">
         <v>0</v>
       </c>
-      <c r="C1229" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1229" s="1"/>
       <c r="D1229" s="1"/>
     </row>
     <row r="1230" spans="1:4">
@@ -15503,9 +14849,7 @@
       <c r="B1230" s="1">
         <v>0</v>
       </c>
-      <c r="C1230" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1230" s="1"/>
       <c r="D1230" s="1"/>
     </row>
     <row r="1231" spans="1:4">
@@ -15515,9 +14859,7 @@
       <c r="B1231" s="1">
         <v>0</v>
       </c>
-      <c r="C1231" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1231" s="1"/>
       <c r="D1231" s="1"/>
     </row>
     <row r="1232" spans="1:4">
@@ -15527,9 +14869,7 @@
       <c r="B1232" s="1">
         <v>0</v>
       </c>
-      <c r="C1232" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1232" s="1"/>
       <c r="D1232" s="1"/>
     </row>
     <row r="1233" spans="1:4">
@@ -15539,9 +14879,7 @@
       <c r="B1233" s="1">
         <v>0</v>
       </c>
-      <c r="C1233" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1233" s="1"/>
       <c r="D1233" s="1"/>
     </row>
     <row r="1234" spans="1:4">
@@ -15551,9 +14889,7 @@
       <c r="B1234" s="1">
         <v>0</v>
       </c>
-      <c r="C1234" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1234" s="1"/>
       <c r="D1234" s="1"/>
     </row>
     <row r="1235" spans="1:4">
@@ -15563,9 +14899,7 @@
       <c r="B1235" s="1">
         <v>0</v>
       </c>
-      <c r="C1235" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1235" s="1"/>
       <c r="D1235" s="1"/>
     </row>
     <row r="1236" spans="1:4">
@@ -15575,9 +14909,7 @@
       <c r="B1236" s="1">
         <v>0</v>
       </c>
-      <c r="C1236" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1236" s="1"/>
       <c r="D1236" s="1"/>
     </row>
     <row r="1237" spans="1:4">
@@ -15587,9 +14919,7 @@
       <c r="B1237" s="1">
         <v>0</v>
       </c>
-      <c r="C1237" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1237" s="1"/>
       <c r="D1237" s="1"/>
     </row>
     <row r="1238" spans="1:4">
@@ -15599,9 +14929,7 @@
       <c r="B1238" s="1">
         <v>0</v>
       </c>
-      <c r="C1238" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1238" s="1"/>
       <c r="D1238" s="1"/>
     </row>
     <row r="1239" spans="1:4">
@@ -15611,9 +14939,7 @@
       <c r="B1239" s="1">
         <v>0</v>
       </c>
-      <c r="C1239" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1239" s="1"/>
       <c r="D1239" s="1"/>
     </row>
     <row r="1240" spans="1:4">
@@ -15623,9 +14949,7 @@
       <c r="B1240" s="1">
         <v>0</v>
       </c>
-      <c r="C1240" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1240" s="1"/>
       <c r="D1240" s="1"/>
     </row>
     <row r="1241" spans="1:4">
@@ -15635,9 +14959,7 @@
       <c r="B1241" s="1">
         <v>0</v>
       </c>
-      <c r="C1241" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1241" s="1"/>
       <c r="D1241" s="1"/>
     </row>
     <row r="1242" spans="1:4">
@@ -15647,9 +14969,7 @@
       <c r="B1242" s="1">
         <v>0</v>
       </c>
-      <c r="C1242" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1242" s="1"/>
       <c r="D1242" s="1"/>
     </row>
     <row r="1243" spans="1:4">
@@ -15659,9 +14979,7 @@
       <c r="B1243" s="1">
         <v>0</v>
       </c>
-      <c r="C1243" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1243" s="1"/>
       <c r="D1243" s="1"/>
     </row>
     <row r="1244" spans="1:4">
@@ -15671,9 +14989,7 @@
       <c r="B1244" s="1">
         <v>0</v>
       </c>
-      <c r="C1244" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1244" s="1"/>
       <c r="D1244" s="1"/>
     </row>
     <row r="1245" spans="1:4">
@@ -15683,9 +14999,7 @@
       <c r="B1245" s="1">
         <v>0</v>
       </c>
-      <c r="C1245" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1245" s="1"/>
       <c r="D1245" s="1"/>
     </row>
     <row r="1246" spans="1:4">
@@ -15695,9 +15009,7 @@
       <c r="B1246" s="1">
         <v>0</v>
       </c>
-      <c r="C1246" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1246" s="1"/>
       <c r="D1246" s="1"/>
     </row>
     <row r="1247" spans="1:4">
@@ -15707,9 +15019,7 @@
       <c r="B1247" s="1">
         <v>0</v>
       </c>
-      <c r="C1247" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1247" s="1"/>
       <c r="D1247" s="1"/>
     </row>
     <row r="1248" spans="1:4">
@@ -15719,9 +15029,7 @@
       <c r="B1248" s="1">
         <v>0</v>
       </c>
-      <c r="C1248" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1248" s="1"/>
       <c r="D1248" s="1"/>
     </row>
     <row r="1249" spans="1:4">
@@ -15731,9 +15039,7 @@
       <c r="B1249" s="1">
         <v>0</v>
       </c>
-      <c r="C1249" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1249" s="1"/>
       <c r="D1249" s="1"/>
     </row>
     <row r="1250" spans="1:4">
@@ -15743,9 +15049,7 @@
       <c r="B1250" s="1">
         <v>0</v>
       </c>
-      <c r="C1250" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1250" s="1"/>
       <c r="D1250" s="1"/>
     </row>
     <row r="1251" spans="1:4">
@@ -15755,9 +15059,7 @@
       <c r="B1251" s="1">
         <v>0</v>
       </c>
-      <c r="C1251" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1251" s="1"/>
       <c r="D1251" s="1"/>
     </row>
     <row r="1252" spans="1:4">
@@ -15767,9 +15069,7 @@
       <c r="B1252" s="1">
         <v>0</v>
       </c>
-      <c r="C1252" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1252" s="1"/>
       <c r="D1252" s="1"/>
     </row>
     <row r="1253" spans="1:4">
@@ -15779,9 +15079,7 @@
       <c r="B1253" s="1">
         <v>0</v>
       </c>
-      <c r="C1253" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1253" s="1"/>
       <c r="D1253" s="1"/>
     </row>
     <row r="1254" spans="1:4">
@@ -15791,9 +15089,7 @@
       <c r="B1254" s="1">
         <v>0</v>
       </c>
-      <c r="C1254" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1254" s="1"/>
       <c r="D1254" s="1"/>
     </row>
     <row r="1255" spans="1:4">
@@ -15803,9 +15099,7 @@
       <c r="B1255" s="1">
         <v>0</v>
       </c>
-      <c r="C1255" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1255" s="1"/>
       <c r="D1255" s="1"/>
     </row>
     <row r="1256" spans="1:4">
@@ -15815,9 +15109,7 @@
       <c r="B1256" s="1">
         <v>0</v>
       </c>
-      <c r="C1256" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1256" s="1"/>
       <c r="D1256" s="1"/>
     </row>
     <row r="1257" spans="1:4">
@@ -15827,9 +15119,7 @@
       <c r="B1257" s="1">
         <v>0</v>
       </c>
-      <c r="C1257" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1257" s="1"/>
       <c r="D1257" s="1"/>
     </row>
     <row r="1258" spans="1:4">
@@ -15839,9 +15129,7 @@
       <c r="B1258" s="1">
         <v>0</v>
       </c>
-      <c r="C1258" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1258" s="1"/>
       <c r="D1258" s="1"/>
     </row>
     <row r="1259" spans="1:4">
@@ -15851,9 +15139,7 @@
       <c r="B1259" s="1">
         <v>0</v>
       </c>
-      <c r="C1259" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1259" s="1"/>
       <c r="D1259" s="1"/>
     </row>
     <row r="1260" spans="1:4">
@@ -15863,9 +15149,7 @@
       <c r="B1260" s="1">
         <v>0</v>
       </c>
-      <c r="C1260" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1260" s="1"/>
       <c r="D1260" s="1"/>
     </row>
     <row r="1261" spans="1:4">
@@ -15875,9 +15159,7 @@
       <c r="B1261" s="1">
         <v>0</v>
       </c>
-      <c r="C1261" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1261" s="1"/>
       <c r="D1261" s="1"/>
     </row>
     <row r="1262" spans="1:4">
@@ -15887,9 +15169,7 @@
       <c r="B1262" s="1">
         <v>0</v>
       </c>
-      <c r="C1262" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1262" s="1"/>
       <c r="D1262" s="1"/>
     </row>
     <row r="1263" spans="1:4">
@@ -15899,9 +15179,7 @@
       <c r="B1263" s="1">
         <v>0</v>
       </c>
-      <c r="C1263" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1263" s="1"/>
       <c r="D1263" s="1"/>
     </row>
     <row r="1264" spans="1:4">
@@ -15911,9 +15189,7 @@
       <c r="B1264" s="1">
         <v>0</v>
       </c>
-      <c r="C1264" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1264" s="1"/>
       <c r="D1264" s="1"/>
     </row>
     <row r="1265" spans="1:4">
@@ -15923,9 +15199,7 @@
       <c r="B1265" s="1">
         <v>0</v>
       </c>
-      <c r="C1265" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1265" s="1"/>
       <c r="D1265" s="1"/>
     </row>
     <row r="1266" spans="1:4">
@@ -15935,9 +15209,7 @@
       <c r="B1266" s="1">
         <v>0</v>
       </c>
-      <c r="C1266" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1266" s="1"/>
       <c r="D1266" s="1"/>
     </row>
     <row r="1267" spans="1:4">
@@ -15947,9 +15219,7 @@
       <c r="B1267" s="1">
         <v>0</v>
       </c>
-      <c r="C1267" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1267" s="1"/>
       <c r="D1267" s="1"/>
     </row>
     <row r="1268" spans="1:4">
@@ -15959,9 +15229,7 @@
       <c r="B1268" s="1">
         <v>0</v>
       </c>
-      <c r="C1268" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1268" s="1"/>
       <c r="D1268" s="1"/>
     </row>
     <row r="1269" spans="1:4">
@@ -15971,9 +15239,7 @@
       <c r="B1269" s="1">
         <v>0</v>
       </c>
-      <c r="C1269" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1269" s="1"/>
       <c r="D1269" s="1"/>
     </row>
     <row r="1270" spans="1:4">
@@ -15983,9 +15249,7 @@
       <c r="B1270" s="1">
         <v>0</v>
       </c>
-      <c r="C1270" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1270" s="1"/>
       <c r="D1270" s="1"/>
     </row>
     <row r="1271" spans="1:4">
@@ -15995,9 +15259,7 @@
       <c r="B1271" s="1">
         <v>0</v>
       </c>
-      <c r="C1271" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1271" s="1"/>
       <c r="D1271" s="1"/>
     </row>
     <row r="1272" spans="1:4">
@@ -16007,9 +15269,7 @@
       <c r="B1272" s="1">
         <v>0</v>
       </c>
-      <c r="C1272" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1272" s="1"/>
       <c r="D1272" s="1"/>
     </row>
     <row r="1273" spans="1:4">
@@ -16019,9 +15279,7 @@
       <c r="B1273" s="1">
         <v>0</v>
       </c>
-      <c r="C1273" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1273" s="1"/>
       <c r="D1273" s="1"/>
     </row>
     <row r="1274" spans="1:4">
@@ -16031,9 +15289,7 @@
       <c r="B1274" s="1">
         <v>0</v>
       </c>
-      <c r="C1274" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1274" s="1"/>
       <c r="D1274" s="1"/>
     </row>
     <row r="1275" spans="1:4">
@@ -16043,9 +15299,7 @@
       <c r="B1275" s="1">
         <v>0</v>
       </c>
-      <c r="C1275" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1275" s="1"/>
       <c r="D1275" s="1"/>
     </row>
     <row r="1276" spans="1:4">
@@ -16055,9 +15309,7 @@
       <c r="B1276" s="1">
         <v>0</v>
       </c>
-      <c r="C1276" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1276" s="1"/>
       <c r="D1276" s="1"/>
     </row>
     <row r="1277" spans="1:4">
@@ -16067,9 +15319,7 @@
       <c r="B1277" s="1">
         <v>0</v>
       </c>
-      <c r="C1277" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1277" s="1"/>
       <c r="D1277" s="1"/>
     </row>
     <row r="1278" spans="1:4">
@@ -16079,9 +15329,7 @@
       <c r="B1278" s="1">
         <v>0</v>
       </c>
-      <c r="C1278" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1278" s="1"/>
       <c r="D1278" s="1"/>
     </row>
     <row r="1279" spans="1:4">
@@ -16091,9 +15339,7 @@
       <c r="B1279" s="1">
         <v>0</v>
       </c>
-      <c r="C1279" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1279" s="1"/>
       <c r="D1279" s="1"/>
     </row>
     <row r="1280" spans="1:4">
@@ -16103,9 +15349,7 @@
       <c r="B1280" s="1">
         <v>0</v>
       </c>
-      <c r="C1280" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1280" s="1"/>
       <c r="D1280" s="1"/>
     </row>
     <row r="1281" spans="1:4">
@@ -16115,9 +15359,7 @@
       <c r="B1281" s="1">
         <v>0</v>
       </c>
-      <c r="C1281" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1281" s="1"/>
       <c r="D1281" s="1"/>
     </row>
     <row r="1282" spans="1:4">
@@ -16127,9 +15369,7 @@
       <c r="B1282" s="1">
         <v>0</v>
       </c>
-      <c r="C1282" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1282" s="1"/>
       <c r="D1282" s="1"/>
     </row>
     <row r="1283" spans="1:4">
@@ -16139,9 +15379,7 @@
       <c r="B1283" s="1">
         <v>0</v>
       </c>
-      <c r="C1283" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1283" s="1"/>
       <c r="D1283" s="1"/>
     </row>
     <row r="1284" spans="1:4">
@@ -16151,9 +15389,7 @@
       <c r="B1284" s="1">
         <v>0</v>
       </c>
-      <c r="C1284" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1284" s="1"/>
       <c r="D1284" s="1"/>
     </row>
     <row r="1285" spans="1:4">
@@ -16163,9 +15399,7 @@
       <c r="B1285" s="1">
         <v>0</v>
       </c>
-      <c r="C1285" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1285" s="1"/>
       <c r="D1285" s="1"/>
     </row>
     <row r="1286" spans="1:4">
@@ -16175,9 +15409,7 @@
       <c r="B1286" s="1">
         <v>0</v>
       </c>
-      <c r="C1286" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1286" s="1"/>
       <c r="D1286" s="1"/>
     </row>
     <row r="1287" spans="1:4">
@@ -16187,9 +15419,7 @@
       <c r="B1287" s="1">
         <v>0</v>
       </c>
-      <c r="C1287" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1287" s="1"/>
       <c r="D1287" s="1"/>
     </row>
     <row r="1288" spans="1:4">
@@ -16199,9 +15429,7 @@
       <c r="B1288" s="1">
         <v>0</v>
       </c>
-      <c r="C1288" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1288" s="1"/>
       <c r="D1288" s="1"/>
     </row>
     <row r="1289" spans="1:4">
@@ -16211,9 +15439,7 @@
       <c r="B1289" s="1">
         <v>0</v>
       </c>
-      <c r="C1289" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1289" s="1"/>
       <c r="D1289" s="1"/>
     </row>
     <row r="1290" spans="1:4">
@@ -16223,9 +15449,7 @@
       <c r="B1290" s="1">
         <v>0</v>
       </c>
-      <c r="C1290" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1290" s="1"/>
       <c r="D1290" s="1"/>
     </row>
     <row r="1291" spans="1:4">
@@ -16235,9 +15459,7 @@
       <c r="B1291" s="1">
         <v>0</v>
       </c>
-      <c r="C1291" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1291" s="1"/>
       <c r="D1291" s="1"/>
     </row>
     <row r="1292" spans="1:4">
@@ -16247,9 +15469,7 @@
       <c r="B1292" s="1">
         <v>0</v>
       </c>
-      <c r="C1292" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1292" s="1"/>
       <c r="D1292" s="1"/>
     </row>
     <row r="1293" spans="1:4">
@@ -16259,9 +15479,7 @@
       <c r="B1293" s="1">
         <v>0</v>
       </c>
-      <c r="C1293" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1293" s="1"/>
       <c r="D1293" s="1"/>
     </row>
     <row r="1294" spans="1:4">
@@ -16271,9 +15489,7 @@
       <c r="B1294" s="1">
         <v>0</v>
       </c>
-      <c r="C1294" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1294" s="1"/>
       <c r="D1294" s="1"/>
     </row>
     <row r="1295" spans="1:4">
@@ -16283,9 +15499,7 @@
       <c r="B1295" s="1">
         <v>0</v>
       </c>
-      <c r="C1295" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1295" s="1"/>
       <c r="D1295" s="1"/>
     </row>
     <row r="1296" spans="1:4">
@@ -16295,9 +15509,7 @@
       <c r="B1296" s="1">
         <v>0</v>
       </c>
-      <c r="C1296" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1296" s="1"/>
       <c r="D1296" s="1"/>
     </row>
     <row r="1297" spans="1:4">
@@ -16307,9 +15519,7 @@
       <c r="B1297" s="1">
         <v>0</v>
       </c>
-      <c r="C1297" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1297" s="1"/>
       <c r="D1297" s="1"/>
     </row>
     <row r="1298" spans="1:4">
@@ -16319,9 +15529,7 @@
       <c r="B1298" s="1">
         <v>0</v>
       </c>
-      <c r="C1298" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1298" s="1"/>
       <c r="D1298" s="1"/>
     </row>
     <row r="1299" spans="1:4">
@@ -16331,9 +15539,7 @@
       <c r="B1299" s="1">
         <v>0</v>
       </c>
-      <c r="C1299" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1299" s="1"/>
       <c r="D1299" s="1"/>
     </row>
     <row r="1300" spans="1:4">
@@ -16343,9 +15549,7 @@
       <c r="B1300" s="1">
         <v>0</v>
       </c>
-      <c r="C1300" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1300" s="1"/>
       <c r="D1300" s="1"/>
     </row>
     <row r="1301" spans="1:4">
@@ -16355,9 +15559,7 @@
       <c r="B1301" s="1">
         <v>0</v>
       </c>
-      <c r="C1301" s="1">
-        <v>10000</v>
-      </c>
+      <c r="C1301" s="1"/>
       <c r="D1301" s="1"/>
     </row>
   </sheetData>

--- a/PNL.xlsx
+++ b/PNL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/apple/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9B55AAD-FDDD-BD40-BE17-BEB32C3B9BB7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B184F5D-AE54-454F-A1C0-E4F45C8AA5EB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16180" xr2:uid="{06C2047E-A20D-7B41-A100-9F165F6715E9}"/>
   </bookViews>
@@ -11579,7 +11579,9 @@
       <c r="B903" s="1">
         <v>0</v>
       </c>
-      <c r="C903" s="1"/>
+      <c r="C903" s="1">
+        <v>12973</v>
+      </c>
       <c r="D903" s="1"/>
     </row>
     <row r="904" spans="1:4">

--- a/PNL.xlsx
+++ b/PNL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/apple/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B184F5D-AE54-454F-A1C0-E4F45C8AA5EB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA7912D7-3CFB-4144-85AA-E7C9C4DDA2DA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16180" xr2:uid="{06C2047E-A20D-7B41-A100-9F165F6715E9}"/>
+    <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16100" xr2:uid="{06C2047E-A20D-7B41-A100-9F165F6715E9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -11580,7 +11580,7 @@
         <v>0</v>
       </c>
       <c r="C903" s="1">
-        <v>12973</v>
+        <v>12957</v>
       </c>
       <c r="D903" s="1"/>
     </row>
@@ -11591,7 +11591,9 @@
       <c r="B904" s="1">
         <v>0</v>
       </c>
-      <c r="C904" s="1"/>
+      <c r="C904" s="1">
+        <v>18893</v>
+      </c>
       <c r="D904" s="1"/>
     </row>
     <row r="905" spans="1:4">

--- a/PNL.xlsx
+++ b/PNL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/apple/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA7912D7-3CFB-4144-85AA-E7C9C4DDA2DA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{531F4611-00D3-8F4F-9138-358157E19085}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16100" xr2:uid="{06C2047E-A20D-7B41-A100-9F165F6715E9}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16100" xr2:uid="{06C2047E-A20D-7B41-A100-9F165F6715E9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -743,7 +743,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA31C75E-3792-5A48-80D5-B790838227C3}">
-  <dimension ref="A1:D1301"/>
+  <dimension ref="A1:J1301"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="26"/>
   <cols>
     <col min="1" max="1" width="16.1640625" style="2" bestFit="1" customWidth="1"/>
@@ -11500,7 +11500,7 @@
       </c>
       <c r="D896" s="1"/>
     </row>
-    <row r="897" spans="1:4">
+    <row r="897" spans="1:10">
       <c r="A897" s="4">
         <v>45821</v>
       </c>
@@ -11512,7 +11512,7 @@
       </c>
       <c r="D897" s="1"/>
     </row>
-    <row r="898" spans="1:4">
+    <row r="898" spans="1:10">
       <c r="A898" s="4">
         <v>45824</v>
       </c>
@@ -11524,7 +11524,7 @@
       </c>
       <c r="D898" s="1"/>
     </row>
-    <row r="899" spans="1:4">
+    <row r="899" spans="1:10">
       <c r="A899" s="4">
         <v>45825</v>
       </c>
@@ -11536,7 +11536,7 @@
       </c>
       <c r="D899" s="5"/>
     </row>
-    <row r="900" spans="1:4">
+    <row r="900" spans="1:10">
       <c r="A900" s="4">
         <v>45826</v>
       </c>
@@ -11547,8 +11547,18 @@
         <v>0</v>
       </c>
       <c r="D900" s="1"/>
-    </row>
-    <row r="901" spans="1:4">
+      <c r="H900" s="2">
+        <v>69709</v>
+      </c>
+      <c r="I900" s="2">
+        <v>7639</v>
+      </c>
+      <c r="J900" s="2">
+        <f>H900-I900</f>
+        <v>62070</v>
+      </c>
+    </row>
+    <row r="901" spans="1:10">
       <c r="A901" s="4">
         <v>45827</v>
       </c>
@@ -11560,7 +11570,7 @@
       </c>
       <c r="D901" s="1"/>
     </row>
-    <row r="902" spans="1:4">
+    <row r="902" spans="1:10">
       <c r="A902" s="4">
         <v>45828</v>
       </c>
@@ -11572,7 +11582,7 @@
       </c>
       <c r="D902" s="1"/>
     </row>
-    <row r="903" spans="1:4">
+    <row r="903" spans="1:10">
       <c r="A903" s="4">
         <v>45831</v>
       </c>
@@ -11584,7 +11594,7 @@
       </c>
       <c r="D903" s="1"/>
     </row>
-    <row r="904" spans="1:4">
+    <row r="904" spans="1:10">
       <c r="A904" s="4">
         <v>45832</v>
       </c>
@@ -11592,31 +11602,33 @@
         <v>0</v>
       </c>
       <c r="C904" s="1">
-        <v>18893</v>
+        <v>18866</v>
       </c>
       <c r="D904" s="1"/>
     </row>
-    <row r="905" spans="1:4">
+    <row r="905" spans="1:10">
       <c r="A905" s="4">
         <v>45833</v>
       </c>
       <c r="B905" s="1">
-        <v>0</v>
+        <v>16425</v>
       </c>
       <c r="C905" s="1"/>
       <c r="D905" s="1"/>
     </row>
-    <row r="906" spans="1:4">
+    <row r="906" spans="1:10">
       <c r="A906" s="4">
         <v>45834</v>
       </c>
       <c r="B906" s="1">
         <v>0</v>
       </c>
-      <c r="C906" s="1"/>
+      <c r="C906" s="1">
+        <v>62070</v>
+      </c>
       <c r="D906" s="1"/>
     </row>
-    <row r="907" spans="1:4">
+    <row r="907" spans="1:10">
       <c r="A907" s="4">
         <v>45835</v>
       </c>
@@ -11626,7 +11638,7 @@
       <c r="C907" s="1"/>
       <c r="D907" s="1"/>
     </row>
-    <row r="908" spans="1:4">
+    <row r="908" spans="1:10">
       <c r="A908" s="4">
         <v>45838</v>
       </c>
@@ -11636,7 +11648,7 @@
       <c r="C908" s="1"/>
       <c r="D908" s="1"/>
     </row>
-    <row r="909" spans="1:4">
+    <row r="909" spans="1:10">
       <c r="A909" s="4">
         <v>45839</v>
       </c>
@@ -11646,7 +11658,7 @@
       <c r="C909" s="1"/>
       <c r="D909" s="1"/>
     </row>
-    <row r="910" spans="1:4">
+    <row r="910" spans="1:10">
       <c r="A910" s="4">
         <v>45840</v>
       </c>
@@ -11656,7 +11668,7 @@
       <c r="C910" s="1"/>
       <c r="D910" s="1"/>
     </row>
-    <row r="911" spans="1:4">
+    <row r="911" spans="1:10">
       <c r="A911" s="4">
         <v>45841</v>
       </c>
@@ -11666,7 +11678,7 @@
       <c r="C911" s="1"/>
       <c r="D911" s="1"/>
     </row>
-    <row r="912" spans="1:4">
+    <row r="912" spans="1:10">
       <c r="A912" s="4">
         <v>45842</v>
       </c>

--- a/PNL.xlsx
+++ b/PNL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/apple/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{531F4611-00D3-8F4F-9138-358157E19085}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09B97D0C-E19C-DB4D-A019-C6A81BE9E0E1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16100" xr2:uid="{06C2047E-A20D-7B41-A100-9F165F6715E9}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16080" xr2:uid="{06C2047E-A20D-7B41-A100-9F165F6715E9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -743,13 +743,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA31C75E-3792-5A48-80D5-B790838227C3}">
-  <dimension ref="A1:J1301"/>
+  <dimension ref="A1:D1301"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="26"/>
   <cols>
     <col min="1" max="1" width="16.1640625" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="20" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.83203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="10.83203125" style="2"/>
+    <col min="5" max="5" width="20" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="10.83203125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -11397,7 +11400,7 @@
         <v>45810</v>
       </c>
       <c r="B888" s="2">
-        <v>12867.889800000001</v>
+        <v>12867</v>
       </c>
       <c r="C888" s="2">
         <v>0</v>
@@ -11412,7 +11415,7 @@
         <v>0</v>
       </c>
       <c r="C889" s="2">
-        <v>3224.7402999999999</v>
+        <v>3224</v>
       </c>
       <c r="D889" s="1"/>
     </row>
@@ -11421,7 +11424,7 @@
         <v>45812</v>
       </c>
       <c r="B890" s="2">
-        <v>4030.9348</v>
+        <v>4030</v>
       </c>
       <c r="C890" s="2">
         <v>0</v>
@@ -11433,7 +11436,7 @@
         <v>45813</v>
       </c>
       <c r="B891" s="2">
-        <v>31286.712599999999</v>
+        <v>31286</v>
       </c>
       <c r="C891" s="2">
         <v>0</v>
@@ -11445,7 +11448,7 @@
         <v>45814</v>
       </c>
       <c r="B892" s="2">
-        <v>9046.2230999999992</v>
+        <v>9046</v>
       </c>
       <c r="C892" s="2">
         <v>0</v>
@@ -11457,7 +11460,7 @@
         <v>45817</v>
       </c>
       <c r="B893" s="2">
-        <v>797.91110000000003</v>
+        <v>797</v>
       </c>
       <c r="C893" s="2">
         <v>0</v>
@@ -11472,7 +11475,7 @@
         <v>0</v>
       </c>
       <c r="C894" s="2">
-        <v>4238.5082000000002</v>
+        <v>4238</v>
       </c>
       <c r="D894" s="5"/>
     </row>
@@ -11481,7 +11484,7 @@
         <v>45819</v>
       </c>
       <c r="B895" s="2">
-        <v>7051.5983999999999</v>
+        <v>7051</v>
       </c>
       <c r="C895" s="2">
         <v>0</v>
@@ -11493,38 +11496,38 @@
         <v>45820</v>
       </c>
       <c r="B896" s="2">
-        <v>13718.6697</v>
+        <v>13718</v>
       </c>
       <c r="C896" s="2">
         <v>0</v>
       </c>
       <c r="D896" s="1"/>
     </row>
-    <row r="897" spans="1:10">
+    <row r="897" spans="1:4">
       <c r="A897" s="4">
         <v>45821</v>
       </c>
       <c r="B897" s="2">
-        <v>7780.9939000000004</v>
+        <v>7780</v>
       </c>
       <c r="C897" s="2">
         <v>0</v>
       </c>
       <c r="D897" s="1"/>
     </row>
-    <row r="898" spans="1:10">
+    <row r="898" spans="1:4">
       <c r="A898" s="4">
         <v>45824</v>
       </c>
       <c r="B898" s="2">
-        <v>1625.0594000000001</v>
+        <v>1625</v>
       </c>
       <c r="C898" s="2">
         <v>0</v>
       </c>
       <c r="D898" s="1"/>
     </row>
-    <row r="899" spans="1:10">
+    <row r="899" spans="1:4">
       <c r="A899" s="4">
         <v>45825</v>
       </c>
@@ -11532,45 +11535,35 @@
         <v>0</v>
       </c>
       <c r="C899" s="2">
-        <v>5973.0051000000003</v>
+        <v>5973</v>
       </c>
       <c r="D899" s="5"/>
     </row>
-    <row r="900" spans="1:10">
+    <row r="900" spans="1:4">
       <c r="A900" s="4">
         <v>45826</v>
       </c>
       <c r="B900" s="2">
-        <v>24588.638800000001</v>
+        <v>24588</v>
       </c>
       <c r="C900" s="2">
         <v>0</v>
       </c>
       <c r="D900" s="1"/>
-      <c r="H900" s="2">
-        <v>69709</v>
-      </c>
-      <c r="I900" s="2">
-        <v>7639</v>
-      </c>
-      <c r="J900" s="2">
-        <f>H900-I900</f>
-        <v>62070</v>
-      </c>
-    </row>
-    <row r="901" spans="1:10">
+    </row>
+    <row r="901" spans="1:4">
       <c r="A901" s="4">
         <v>45827</v>
       </c>
       <c r="B901" s="2">
-        <v>22474.568500000001</v>
+        <v>22474</v>
       </c>
       <c r="C901" s="2">
         <v>0</v>
       </c>
       <c r="D901" s="1"/>
     </row>
-    <row r="902" spans="1:10">
+    <row r="902" spans="1:4">
       <c r="A902" s="4">
         <v>45828</v>
       </c>
@@ -11578,11 +11571,11 @@
         <v>0</v>
       </c>
       <c r="C902" s="2">
-        <v>1025.2280000000001</v>
+        <v>1025</v>
       </c>
       <c r="D902" s="1"/>
     </row>
-    <row r="903" spans="1:10">
+    <row r="903" spans="1:4">
       <c r="A903" s="4">
         <v>45831</v>
       </c>
@@ -11594,7 +11587,7 @@
       </c>
       <c r="D903" s="1"/>
     </row>
-    <row r="904" spans="1:10">
+    <row r="904" spans="1:4">
       <c r="A904" s="4">
         <v>45832</v>
       </c>
@@ -11606,7 +11599,7 @@
       </c>
       <c r="D904" s="1"/>
     </row>
-    <row r="905" spans="1:10">
+    <row r="905" spans="1:4">
       <c r="A905" s="4">
         <v>45833</v>
       </c>
@@ -11616,7 +11609,7 @@
       <c r="C905" s="1"/>
       <c r="D905" s="1"/>
     </row>
-    <row r="906" spans="1:10">
+    <row r="906" spans="1:4">
       <c r="A906" s="4">
         <v>45834</v>
       </c>
@@ -11624,21 +11617,23 @@
         <v>0</v>
       </c>
       <c r="C906" s="1">
-        <v>62070</v>
+        <v>62045</v>
       </c>
       <c r="D906" s="1"/>
     </row>
-    <row r="907" spans="1:10">
+    <row r="907" spans="1:4">
       <c r="A907" s="4">
         <v>45835</v>
       </c>
       <c r="B907" s="1">
-        <v>0</v>
-      </c>
-      <c r="C907" s="1"/>
+        <v>466</v>
+      </c>
+      <c r="C907" s="1">
+        <v>3782</v>
+      </c>
       <c r="D907" s="1"/>
     </row>
-    <row r="908" spans="1:10">
+    <row r="908" spans="1:4">
       <c r="A908" s="4">
         <v>45838</v>
       </c>
@@ -11648,7 +11643,7 @@
       <c r="C908" s="1"/>
       <c r="D908" s="1"/>
     </row>
-    <row r="909" spans="1:10">
+    <row r="909" spans="1:4">
       <c r="A909" s="4">
         <v>45839</v>
       </c>
@@ -11658,7 +11653,7 @@
       <c r="C909" s="1"/>
       <c r="D909" s="1"/>
     </row>
-    <row r="910" spans="1:10">
+    <row r="910" spans="1:4">
       <c r="A910" s="4">
         <v>45840</v>
       </c>
@@ -11668,7 +11663,7 @@
       <c r="C910" s="1"/>
       <c r="D910" s="1"/>
     </row>
-    <row r="911" spans="1:10">
+    <row r="911" spans="1:4">
       <c r="A911" s="4">
         <v>45841</v>
       </c>
@@ -11678,7 +11673,7 @@
       <c r="C911" s="1"/>
       <c r="D911" s="1"/>
     </row>
-    <row r="912" spans="1:10">
+    <row r="912" spans="1:4">
       <c r="A912" s="4">
         <v>45842</v>
       </c>

--- a/PNL.xlsx
+++ b/PNL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/apple/Downloads/PNL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8A834F6-1C8D-E342-98F0-A3504FD23C02}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0BE554D-EFAB-6649-8A44-7CC5BEF1E6A2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16080" xr2:uid="{06C2047E-A20D-7B41-A100-9F165F6715E9}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16020" xr2:uid="{06C2047E-A20D-7B41-A100-9F165F6715E9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14856,7 +14856,7 @@
         <v>0</v>
       </c>
       <c r="C908" s="1">
-        <v>17194</v>
+        <v>17185</v>
       </c>
       <c r="D908" s="1"/>
     </row>
@@ -14913,7 +14913,7 @@
         <v>45845</v>
       </c>
       <c r="B913" s="1">
-        <v>0</v>
+        <v>15493</v>
       </c>
       <c r="C913" s="1"/>
       <c r="D913" s="1"/>
@@ -14925,7 +14925,9 @@
       <c r="B914" s="1">
         <v>0</v>
       </c>
-      <c r="C914" s="1"/>
+      <c r="C914" s="1">
+        <v>2698</v>
+      </c>
       <c r="D914" s="1"/>
     </row>
     <row r="915" spans="1:4">
@@ -14935,7 +14937,9 @@
       <c r="B915" s="1">
         <v>0</v>
       </c>
-      <c r="C915" s="1"/>
+      <c r="C915" s="1">
+        <v>4610</v>
+      </c>
       <c r="D915" s="1"/>
     </row>
     <row r="916" spans="1:4">
@@ -14943,7 +14947,7 @@
         <v>45848</v>
       </c>
       <c r="B916" s="1">
-        <v>0</v>
+        <v>22519</v>
       </c>
       <c r="C916" s="1"/>
       <c r="D916" s="1"/>
@@ -14953,7 +14957,7 @@
         <v>45849</v>
       </c>
       <c r="B917" s="1">
-        <v>0</v>
+        <v>8168</v>
       </c>
       <c r="C917" s="1"/>
       <c r="D917" s="1"/>
@@ -14965,7 +14969,9 @@
       <c r="B918" s="1">
         <v>0</v>
       </c>
-      <c r="C918" s="1"/>
+      <c r="C918" s="1">
+        <v>45</v>
+      </c>
       <c r="D918" s="1"/>
     </row>
     <row r="919" spans="1:4">
@@ -14975,7 +14981,9 @@
       <c r="B919" s="1">
         <v>0</v>
       </c>
-      <c r="C919" s="1"/>
+      <c r="C919" s="1">
+        <v>8586</v>
+      </c>
       <c r="D919" s="1"/>
     </row>
     <row r="920" spans="1:4">
@@ -14983,7 +14991,7 @@
         <v>45854</v>
       </c>
       <c r="B920" s="1">
-        <v>0</v>
+        <v>8409</v>
       </c>
       <c r="C920" s="1"/>
       <c r="D920" s="1"/>
@@ -14993,7 +15001,7 @@
         <v>45855</v>
       </c>
       <c r="B921" s="1">
-        <v>0</v>
+        <v>6399</v>
       </c>
       <c r="C921" s="1"/>
       <c r="D921" s="1"/>
@@ -15003,7 +15011,7 @@
         <v>45856</v>
       </c>
       <c r="B922" s="1">
-        <v>0</v>
+        <v>5319</v>
       </c>
       <c r="C922" s="1"/>
       <c r="D922" s="1"/>
@@ -15013,7 +15021,7 @@
         <v>45859</v>
       </c>
       <c r="B923" s="1">
-        <v>0</v>
+        <v>3228</v>
       </c>
       <c r="C923" s="1"/>
       <c r="D923" s="1"/>
@@ -15023,7 +15031,7 @@
         <v>45860</v>
       </c>
       <c r="B924" s="1">
-        <v>0</v>
+        <v>2747</v>
       </c>
       <c r="C924" s="1"/>
       <c r="D924" s="1"/>
@@ -15053,7 +15061,7 @@
         <v>45863</v>
       </c>
       <c r="B927" s="1">
-        <v>0</v>
+        <v>12456</v>
       </c>
       <c r="C927" s="1"/>
       <c r="D927" s="1"/>
@@ -15063,7 +15071,7 @@
         <v>45866</v>
       </c>
       <c r="B928" s="1">
-        <v>0</v>
+        <v>15546</v>
       </c>
       <c r="C928" s="1"/>
       <c r="D928" s="1"/>
@@ -15073,7 +15081,7 @@
         <v>45867</v>
       </c>
       <c r="B929" s="1">
-        <v>0</v>
+        <v>17280</v>
       </c>
       <c r="C929" s="1"/>
       <c r="D929" s="1"/>
@@ -15083,7 +15091,7 @@
         <v>45868</v>
       </c>
       <c r="B930" s="1">
-        <v>0</v>
+        <v>46215</v>
       </c>
       <c r="C930" s="1"/>
       <c r="D930" s="1"/>
@@ -15093,7 +15101,7 @@
         <v>45869</v>
       </c>
       <c r="B931" s="1">
-        <v>0</v>
+        <v>7317</v>
       </c>
       <c r="C931" s="1"/>
       <c r="D931" s="1"/>
@@ -15106,7 +15114,7 @@
         <v>0</v>
       </c>
       <c r="C932" s="1">
-        <v>0</v>
+        <v>3543</v>
       </c>
       <c r="D932" s="1"/>
     </row>

--- a/PNL.xlsx
+++ b/PNL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/apple/Downloads/PNL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0BE554D-EFAB-6649-8A44-7CC5BEF1E6A2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B059DDCA-4F44-4946-B367-FAABB7623C8C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16020" xr2:uid="{06C2047E-A20D-7B41-A100-9F165F6715E9}"/>
   </bookViews>

--- a/PNL.xlsx
+++ b/PNL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/apple/Downloads/PNL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B059DDCA-4F44-4946-B367-FAABB7623C8C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9BEEEF0-4AC9-E747-A4A5-248482AD7102}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16020" xr2:uid="{06C2047E-A20D-7B41-A100-9F165F6715E9}"/>
   </bookViews>
@@ -3958,19 +3958,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA31C75E-3792-5A48-80D5-B790838227C3}">
-  <dimension ref="A1:D1301"/>
+  <dimension ref="A1:N1301"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="26"/>
   <cols>
     <col min="1" max="1" width="16.1640625" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="20" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.83203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.83203125" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="10.83203125" style="2"/>
+    <col min="7" max="7" width="8.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="20" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.83203125" style="2"/>
+    <col min="14" max="14" width="11.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="10.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>109</v>
       </c>
@@ -3981,8 +3987,20 @@
         <v>108</v>
       </c>
       <c r="D1" s="1"/>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="H1" s="2">
+        <f>SUM(H2:H6)</f>
+        <v>9258681.9040000029</v>
+      </c>
+      <c r="I1" s="2">
+        <f>SUM(I2:I6)</f>
+        <v>5819872.3186000017</v>
+      </c>
+      <c r="J1" s="2">
+        <f>SUM(J2:J6)</f>
+        <v>-3438809.5854000021</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>44202</v>
       </c>
@@ -3993,8 +4011,23 @@
         <v>0</v>
       </c>
       <c r="D2" s="1"/>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="G2" s="2">
+        <v>2021</v>
+      </c>
+      <c r="H2" s="2">
+        <f>SUM(B2:B192)</f>
+        <v>224594.16380000013</v>
+      </c>
+      <c r="I2" s="2">
+        <f>SUM(C2:C192)</f>
+        <v>74707.2261</v>
+      </c>
+      <c r="J2" s="2">
+        <f>I2-H2</f>
+        <v>-149886.93770000013</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
         <v>44214</v>
       </c>
@@ -4005,8 +4038,23 @@
         <v>0</v>
       </c>
       <c r="D3" s="1"/>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="G3" s="2">
+        <v>2022</v>
+      </c>
+      <c r="H3" s="2">
+        <f>SUM(B193:B397)</f>
+        <v>368054.09150000004</v>
+      </c>
+      <c r="I3" s="2">
+        <f>SUM(C193:C397)</f>
+        <v>164587.17639999997</v>
+      </c>
+      <c r="J3" s="2">
+        <f>I3-H3</f>
+        <v>-203466.91510000007</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="3">
         <v>44216</v>
       </c>
@@ -4017,8 +4065,23 @@
         <v>11238.343000000001</v>
       </c>
       <c r="D4" s="1"/>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="G4" s="2">
+        <v>2023</v>
+      </c>
+      <c r="H4" s="2">
+        <f>SUM(B398:B540)</f>
+        <v>1722070.6315000004</v>
+      </c>
+      <c r="I4" s="2">
+        <f>SUM(C398:C540)</f>
+        <v>1456538.6866000004</v>
+      </c>
+      <c r="J4" s="2">
+        <f>I4-H4</f>
+        <v>-265531.9449</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="3">
         <v>44221</v>
       </c>
@@ -4029,8 +4092,23 @@
         <v>0</v>
       </c>
       <c r="D5" s="1"/>
-    </row>
-    <row r="6" spans="1:4">
+      <c r="G5" s="2">
+        <v>2024</v>
+      </c>
+      <c r="H5" s="2">
+        <f>SUM(B541:B776)</f>
+        <v>4858552.3411000036</v>
+      </c>
+      <c r="I5" s="2">
+        <f>SUM(C541:C776)</f>
+        <v>3346656.5383000011</v>
+      </c>
+      <c r="J5" s="2">
+        <f>I5-H5</f>
+        <v>-1511895.8028000025</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="3">
         <v>44223</v>
       </c>
@@ -4041,8 +4119,39 @@
         <v>238.73570000000001</v>
       </c>
       <c r="D6" s="1"/>
-    </row>
-    <row r="7" spans="1:4">
+      <c r="G6" s="2">
+        <v>2025</v>
+      </c>
+      <c r="H6" s="2">
+        <f>SUM(B777:B1040)</f>
+        <v>2085410.6760999998</v>
+      </c>
+      <c r="I6" s="2">
+        <f>SUM(C777:C1040)</f>
+        <v>777382.6912</v>
+      </c>
+      <c r="J6" s="2">
+        <f>I6-H6</f>
+        <v>-1308027.9848999998</v>
+      </c>
+      <c r="K6" s="2">
+        <f>SUM(E933:E1040)</f>
+        <v>1080000</v>
+      </c>
+      <c r="L6" s="2">
+        <f>J5+J6</f>
+        <v>-2819923.7877000021</v>
+      </c>
+      <c r="M6" s="2">
+        <f>L6/10000</f>
+        <v>-281.99237877000019</v>
+      </c>
+      <c r="N6" s="2">
+        <f>10000*2</f>
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
@@ -4053,8 +4162,16 @@
         <v>0</v>
       </c>
       <c r="D7" s="1"/>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="M7" s="2">
+        <f>L6/20000</f>
+        <v>-140.99618938500009</v>
+      </c>
+      <c r="N7" s="2">
+        <f>20000*2</f>
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="3">
         <v>44198</v>
       </c>
@@ -4065,8 +4182,16 @@
         <v>0</v>
       </c>
       <c r="D8" s="1"/>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="M8" s="2">
+        <f>L6/30000</f>
+        <v>-93.997459590000076</v>
+      </c>
+      <c r="N8" s="2">
+        <f>30000*2</f>
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" s="3">
         <v>44229</v>
       </c>
@@ -4077,8 +4202,16 @@
         <v>908.9443</v>
       </c>
       <c r="D9" s="1"/>
-    </row>
-    <row r="10" spans="1:4">
+      <c r="M9" s="2">
+        <f>L6/40000</f>
+        <v>-70.498094692500047</v>
+      </c>
+      <c r="N9" s="2">
+        <f>40000*2</f>
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" s="3">
         <v>44257</v>
       </c>
@@ -4089,8 +4222,16 @@
         <v>0</v>
       </c>
       <c r="D10" s="1"/>
-    </row>
-    <row r="11" spans="1:4">
+      <c r="M10" s="2">
+        <f>L6/50000</f>
+        <v>-56.398475754000039</v>
+      </c>
+      <c r="N10" s="2">
+        <f>50000*2</f>
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" s="3">
         <v>44288</v>
       </c>
@@ -4102,7 +4243,7 @@
       </c>
       <c r="D11" s="1"/>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:14">
       <c r="A12" s="3">
         <v>44318</v>
       </c>
@@ -4114,7 +4255,7 @@
       </c>
       <c r="D12" s="1"/>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:14">
       <c r="A13" s="3">
         <v>44410</v>
       </c>
@@ -4126,7 +4267,7 @@
       </c>
       <c r="D13" s="1"/>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:14">
       <c r="A14" s="3">
         <v>44236</v>
       </c>
@@ -4138,7 +4279,7 @@
       </c>
       <c r="D14" s="1"/>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:14">
       <c r="A15" s="3">
         <v>44245</v>
       </c>
@@ -4150,7 +4291,7 @@
       </c>
       <c r="D15" s="1"/>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:14">
       <c r="A16" s="3">
         <v>44249</v>
       </c>
@@ -15076,7 +15217,7 @@
       <c r="C928" s="1"/>
       <c r="D928" s="1"/>
     </row>
-    <row r="929" spans="1:4">
+    <row r="929" spans="1:5">
       <c r="A929" s="4">
         <v>45867</v>
       </c>
@@ -15086,7 +15227,7 @@
       <c r="C929" s="1"/>
       <c r="D929" s="1"/>
     </row>
-    <row r="930" spans="1:4">
+    <row r="930" spans="1:5">
       <c r="A930" s="4">
         <v>45868</v>
       </c>
@@ -15096,7 +15237,7 @@
       <c r="C930" s="1"/>
       <c r="D930" s="1"/>
     </row>
-    <row r="931" spans="1:4">
+    <row r="931" spans="1:5">
       <c r="A931" s="4">
         <v>45869</v>
       </c>
@@ -15106,7 +15247,7 @@
       <c r="C931" s="1"/>
       <c r="D931" s="1"/>
     </row>
-    <row r="932" spans="1:4">
+    <row r="932" spans="1:5">
       <c r="A932" s="4">
         <v>45870</v>
       </c>
@@ -15118,1301 +15259,1409 @@
       </c>
       <c r="D932" s="1"/>
     </row>
-    <row r="933" spans="1:4">
+    <row r="933" spans="1:5">
       <c r="A933" s="4">
         <v>45873</v>
       </c>
       <c r="B933" s="1">
         <v>0</v>
       </c>
-      <c r="C933" s="1">
-        <v>0</v>
-      </c>
+      <c r="C933" s="1"/>
       <c r="D933" s="1"/>
-    </row>
-    <row r="934" spans="1:4">
+      <c r="E933" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="934" spans="1:5">
       <c r="A934" s="4">
         <v>45874</v>
       </c>
       <c r="B934" s="1">
         <v>0</v>
       </c>
-      <c r="C934" s="1">
-        <v>0</v>
-      </c>
+      <c r="C934" s="1"/>
       <c r="D934" s="1"/>
-    </row>
-    <row r="935" spans="1:4">
+      <c r="E934" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="935" spans="1:5">
       <c r="A935" s="4">
         <v>45875</v>
       </c>
       <c r="B935" s="1">
         <v>0</v>
       </c>
-      <c r="C935" s="1">
-        <v>0</v>
-      </c>
+      <c r="C935" s="1"/>
       <c r="D935" s="1"/>
-    </row>
-    <row r="936" spans="1:4">
+      <c r="E935" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="936" spans="1:5">
       <c r="A936" s="4">
         <v>45876</v>
       </c>
       <c r="B936" s="1">
         <v>0</v>
       </c>
-      <c r="C936" s="1">
-        <v>0</v>
-      </c>
+      <c r="C936" s="1"/>
       <c r="D936" s="1"/>
-    </row>
-    <row r="937" spans="1:4">
+      <c r="E936" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="937" spans="1:5">
       <c r="A937" s="4">
         <v>45877</v>
       </c>
       <c r="B937" s="1">
         <v>0</v>
       </c>
-      <c r="C937" s="1">
-        <v>0</v>
-      </c>
+      <c r="C937" s="1"/>
       <c r="D937" s="1"/>
-    </row>
-    <row r="938" spans="1:4">
+      <c r="E937" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="938" spans="1:5">
       <c r="A938" s="4">
         <v>45880</v>
       </c>
       <c r="B938" s="1">
         <v>0</v>
       </c>
-      <c r="C938" s="1">
-        <v>0</v>
-      </c>
+      <c r="C938" s="1"/>
       <c r="D938" s="1"/>
-    </row>
-    <row r="939" spans="1:4">
+      <c r="E938" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="939" spans="1:5">
       <c r="A939" s="4">
         <v>45881</v>
       </c>
       <c r="B939" s="1">
         <v>0</v>
       </c>
-      <c r="C939" s="1">
-        <v>0</v>
-      </c>
+      <c r="C939" s="1"/>
       <c r="D939" s="1"/>
-    </row>
-    <row r="940" spans="1:4">
+      <c r="E939" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="940" spans="1:5">
       <c r="A940" s="4">
         <v>45882</v>
       </c>
       <c r="B940" s="1">
         <v>0</v>
       </c>
-      <c r="C940" s="1">
-        <v>0</v>
-      </c>
+      <c r="C940" s="1"/>
       <c r="D940" s="1"/>
-    </row>
-    <row r="941" spans="1:4">
+      <c r="E940" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="941" spans="1:5">
       <c r="A941" s="4">
         <v>45883</v>
       </c>
       <c r="B941" s="1">
         <v>0</v>
       </c>
-      <c r="C941" s="1">
-        <v>0</v>
-      </c>
+      <c r="C941" s="1"/>
       <c r="D941" s="1"/>
-    </row>
-    <row r="942" spans="1:4">
+      <c r="E941" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="942" spans="1:5">
       <c r="A942" s="4">
         <v>45884</v>
       </c>
       <c r="B942" s="1">
         <v>0</v>
       </c>
-      <c r="C942" s="1">
-        <v>0</v>
-      </c>
+      <c r="C942" s="1"/>
       <c r="D942" s="1"/>
-    </row>
-    <row r="943" spans="1:4">
+      <c r="E942" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="943" spans="1:5">
       <c r="A943" s="4">
         <v>45887</v>
       </c>
       <c r="B943" s="1">
         <v>0</v>
       </c>
-      <c r="C943" s="1">
-        <v>0</v>
-      </c>
+      <c r="C943" s="1"/>
       <c r="D943" s="1"/>
-    </row>
-    <row r="944" spans="1:4">
+      <c r="E943" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="944" spans="1:5">
       <c r="A944" s="4">
         <v>45888</v>
       </c>
       <c r="B944" s="1">
         <v>0</v>
       </c>
-      <c r="C944" s="1">
-        <v>0</v>
-      </c>
+      <c r="C944" s="1"/>
       <c r="D944" s="1"/>
-    </row>
-    <row r="945" spans="1:4">
+      <c r="E944" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="945" spans="1:5">
       <c r="A945" s="4">
         <v>45889</v>
       </c>
       <c r="B945" s="1">
         <v>0</v>
       </c>
-      <c r="C945" s="1">
-        <v>0</v>
-      </c>
+      <c r="C945" s="1"/>
       <c r="D945" s="1"/>
-    </row>
-    <row r="946" spans="1:4">
+      <c r="E945" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="946" spans="1:5">
       <c r="A946" s="4">
         <v>45890</v>
       </c>
       <c r="B946" s="1">
         <v>0</v>
       </c>
-      <c r="C946" s="1">
-        <v>0</v>
-      </c>
+      <c r="C946" s="1"/>
       <c r="D946" s="1"/>
-    </row>
-    <row r="947" spans="1:4">
+      <c r="E946" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="947" spans="1:5">
       <c r="A947" s="4">
         <v>45891</v>
       </c>
       <c r="B947" s="1">
         <v>0</v>
       </c>
-      <c r="C947" s="1">
-        <v>0</v>
-      </c>
+      <c r="C947" s="1"/>
       <c r="D947" s="1"/>
-    </row>
-    <row r="948" spans="1:4">
+      <c r="E947" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="948" spans="1:5">
       <c r="A948" s="4">
         <v>45894</v>
       </c>
       <c r="B948" s="1">
         <v>0</v>
       </c>
-      <c r="C948" s="1">
-        <v>0</v>
-      </c>
+      <c r="C948" s="1"/>
       <c r="D948" s="1"/>
-    </row>
-    <row r="949" spans="1:4">
+      <c r="E948" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="949" spans="1:5">
       <c r="A949" s="4">
         <v>45895</v>
       </c>
       <c r="B949" s="1">
         <v>0</v>
       </c>
-      <c r="C949" s="1">
-        <v>0</v>
-      </c>
+      <c r="C949" s="1"/>
       <c r="D949" s="1"/>
-    </row>
-    <row r="950" spans="1:4">
+      <c r="E949" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="950" spans="1:5">
       <c r="A950" s="4">
         <v>45896</v>
       </c>
       <c r="B950" s="1">
         <v>0</v>
       </c>
-      <c r="C950" s="1">
-        <v>0</v>
-      </c>
+      <c r="C950" s="1"/>
       <c r="D950" s="1"/>
-    </row>
-    <row r="951" spans="1:4">
+      <c r="E950" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="951" spans="1:5">
       <c r="A951" s="4">
         <v>45897</v>
       </c>
       <c r="B951" s="1">
         <v>0</v>
       </c>
-      <c r="C951" s="1">
-        <v>0</v>
-      </c>
+      <c r="C951" s="1"/>
       <c r="D951" s="1"/>
-    </row>
-    <row r="952" spans="1:4">
+      <c r="E951" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="952" spans="1:5">
       <c r="A952" s="4">
         <v>45898</v>
       </c>
       <c r="B952" s="1">
         <v>0</v>
       </c>
-      <c r="C952" s="1">
-        <v>0</v>
-      </c>
+      <c r="C952" s="1"/>
       <c r="D952" s="1"/>
-    </row>
-    <row r="953" spans="1:4">
+      <c r="E952" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="953" spans="1:5">
       <c r="A953" s="4">
         <v>45901</v>
       </c>
       <c r="B953" s="1">
         <v>0</v>
       </c>
-      <c r="C953" s="1">
-        <v>0</v>
-      </c>
+      <c r="C953" s="1"/>
       <c r="D953" s="1"/>
-    </row>
-    <row r="954" spans="1:4">
+      <c r="E953" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="954" spans="1:5">
       <c r="A954" s="4">
         <v>45902</v>
       </c>
       <c r="B954" s="1">
         <v>0</v>
       </c>
-      <c r="C954" s="1">
-        <v>0</v>
-      </c>
+      <c r="C954" s="1"/>
       <c r="D954" s="1"/>
-    </row>
-    <row r="955" spans="1:4">
+      <c r="E954" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="955" spans="1:5">
       <c r="A955" s="4">
         <v>45903</v>
       </c>
       <c r="B955" s="1">
         <v>0</v>
       </c>
-      <c r="C955" s="1">
-        <v>0</v>
-      </c>
+      <c r="C955" s="1"/>
       <c r="D955" s="1"/>
-    </row>
-    <row r="956" spans="1:4">
+      <c r="E955" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="956" spans="1:5">
       <c r="A956" s="4">
         <v>45904</v>
       </c>
       <c r="B956" s="1">
         <v>0</v>
       </c>
-      <c r="C956" s="1">
-        <v>0</v>
-      </c>
+      <c r="C956" s="1"/>
       <c r="D956" s="1"/>
-    </row>
-    <row r="957" spans="1:4">
+      <c r="E956" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="957" spans="1:5">
       <c r="A957" s="4">
         <v>45905</v>
       </c>
       <c r="B957" s="1">
         <v>0</v>
       </c>
-      <c r="C957" s="1">
-        <v>0</v>
-      </c>
+      <c r="C957" s="1"/>
       <c r="D957" s="1"/>
-    </row>
-    <row r="958" spans="1:4">
+      <c r="E957" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="958" spans="1:5">
       <c r="A958" s="4">
         <v>45908</v>
       </c>
       <c r="B958" s="1">
         <v>0</v>
       </c>
-      <c r="C958" s="1">
-        <v>0</v>
-      </c>
+      <c r="C958" s="1"/>
       <c r="D958" s="1"/>
-    </row>
-    <row r="959" spans="1:4">
+      <c r="E958" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="959" spans="1:5">
       <c r="A959" s="4">
         <v>45909</v>
       </c>
       <c r="B959" s="1">
         <v>0</v>
       </c>
-      <c r="C959" s="1">
-        <v>0</v>
-      </c>
+      <c r="C959" s="1"/>
       <c r="D959" s="1"/>
-    </row>
-    <row r="960" spans="1:4">
+      <c r="E959" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="960" spans="1:5">
       <c r="A960" s="4">
         <v>45910</v>
       </c>
       <c r="B960" s="1">
         <v>0</v>
       </c>
-      <c r="C960" s="1">
-        <v>0</v>
-      </c>
+      <c r="C960" s="1"/>
       <c r="D960" s="1"/>
-    </row>
-    <row r="961" spans="1:4">
+      <c r="E960" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="961" spans="1:5">
       <c r="A961" s="4">
         <v>45911</v>
       </c>
       <c r="B961" s="1">
         <v>0</v>
       </c>
-      <c r="C961" s="1">
-        <v>0</v>
-      </c>
+      <c r="C961" s="1"/>
       <c r="D961" s="1"/>
-    </row>
-    <row r="962" spans="1:4">
+      <c r="E961" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="962" spans="1:5">
       <c r="A962" s="4">
         <v>45912</v>
       </c>
       <c r="B962" s="1">
         <v>0</v>
       </c>
-      <c r="C962" s="1">
-        <v>0</v>
-      </c>
+      <c r="C962" s="1"/>
       <c r="D962" s="1"/>
-    </row>
-    <row r="963" spans="1:4">
+      <c r="E962" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="963" spans="1:5">
       <c r="A963" s="4">
         <v>45915</v>
       </c>
       <c r="B963" s="1">
         <v>0</v>
       </c>
-      <c r="C963" s="1">
-        <v>0</v>
-      </c>
+      <c r="C963" s="1"/>
       <c r="D963" s="1"/>
-    </row>
-    <row r="964" spans="1:4">
+      <c r="E963" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="964" spans="1:5">
       <c r="A964" s="4">
         <v>45916</v>
       </c>
       <c r="B964" s="1">
         <v>0</v>
       </c>
-      <c r="C964" s="1">
-        <v>0</v>
-      </c>
+      <c r="C964" s="1"/>
       <c r="D964" s="1"/>
-    </row>
-    <row r="965" spans="1:4">
+      <c r="E964" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="965" spans="1:5">
       <c r="A965" s="4">
         <v>45917</v>
       </c>
       <c r="B965" s="1">
         <v>0</v>
       </c>
-      <c r="C965" s="1">
-        <v>0</v>
-      </c>
+      <c r="C965" s="1"/>
       <c r="D965" s="1"/>
-    </row>
-    <row r="966" spans="1:4">
+      <c r="E965" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="966" spans="1:5">
       <c r="A966" s="4">
         <v>45918</v>
       </c>
       <c r="B966" s="1">
         <v>0</v>
       </c>
-      <c r="C966" s="1">
-        <v>0</v>
-      </c>
+      <c r="C966" s="1"/>
       <c r="D966" s="1"/>
-    </row>
-    <row r="967" spans="1:4">
+      <c r="E966" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="967" spans="1:5">
       <c r="A967" s="4">
         <v>45919</v>
       </c>
       <c r="B967" s="1">
         <v>0</v>
       </c>
-      <c r="C967" s="1">
-        <v>0</v>
-      </c>
+      <c r="C967" s="1"/>
       <c r="D967" s="1"/>
-    </row>
-    <row r="968" spans="1:4">
+      <c r="E967" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="968" spans="1:5">
       <c r="A968" s="4">
         <v>45922</v>
       </c>
       <c r="B968" s="1">
         <v>0</v>
       </c>
-      <c r="C968" s="1">
-        <v>0</v>
-      </c>
+      <c r="C968" s="1"/>
       <c r="D968" s="1"/>
-    </row>
-    <row r="969" spans="1:4">
+      <c r="E968" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="969" spans="1:5">
       <c r="A969" s="4">
         <v>45923</v>
       </c>
       <c r="B969" s="1">
         <v>0</v>
       </c>
-      <c r="C969" s="1">
-        <v>0</v>
-      </c>
+      <c r="C969" s="1"/>
       <c r="D969" s="1"/>
-    </row>
-    <row r="970" spans="1:4">
+      <c r="E969" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="970" spans="1:5">
       <c r="A970" s="4">
         <v>45924</v>
       </c>
       <c r="B970" s="1">
         <v>0</v>
       </c>
-      <c r="C970" s="1">
-        <v>0</v>
-      </c>
+      <c r="C970" s="1"/>
       <c r="D970" s="1"/>
-    </row>
-    <row r="971" spans="1:4">
+      <c r="E970" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="971" spans="1:5">
       <c r="A971" s="4">
         <v>45925</v>
       </c>
       <c r="B971" s="1">
         <v>0</v>
       </c>
-      <c r="C971" s="1">
-        <v>0</v>
-      </c>
+      <c r="C971" s="1"/>
       <c r="D971" s="1"/>
-    </row>
-    <row r="972" spans="1:4">
+      <c r="E971" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="972" spans="1:5">
       <c r="A972" s="4">
         <v>45926</v>
       </c>
       <c r="B972" s="1">
         <v>0</v>
       </c>
-      <c r="C972" s="1">
-        <v>0</v>
-      </c>
+      <c r="C972" s="1"/>
       <c r="D972" s="1"/>
-    </row>
-    <row r="973" spans="1:4">
+      <c r="E972" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="973" spans="1:5">
       <c r="A973" s="4">
         <v>45929</v>
       </c>
       <c r="B973" s="1">
         <v>0</v>
       </c>
-      <c r="C973" s="1">
-        <v>0</v>
-      </c>
+      <c r="C973" s="1"/>
       <c r="D973" s="1"/>
-    </row>
-    <row r="974" spans="1:4">
+      <c r="E973" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="974" spans="1:5">
       <c r="A974" s="4">
         <v>45930</v>
       </c>
       <c r="B974" s="1">
         <v>0</v>
       </c>
-      <c r="C974" s="1">
-        <v>0</v>
-      </c>
+      <c r="C974" s="1"/>
       <c r="D974" s="1"/>
-    </row>
-    <row r="975" spans="1:4">
+      <c r="E974" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="975" spans="1:5">
       <c r="A975" s="4">
         <v>45931</v>
       </c>
       <c r="B975" s="1">
         <v>0</v>
       </c>
-      <c r="C975" s="1">
-        <v>0</v>
-      </c>
+      <c r="C975" s="1"/>
       <c r="D975" s="1"/>
-    </row>
-    <row r="976" spans="1:4">
+      <c r="E975" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="976" spans="1:5">
       <c r="A976" s="4">
         <v>45932</v>
       </c>
       <c r="B976" s="1">
         <v>0</v>
       </c>
-      <c r="C976" s="1">
-        <v>0</v>
-      </c>
+      <c r="C976" s="1"/>
       <c r="D976" s="1"/>
-    </row>
-    <row r="977" spans="1:4">
+      <c r="E976" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="977" spans="1:5">
       <c r="A977" s="4">
         <v>45933</v>
       </c>
       <c r="B977" s="1">
         <v>0</v>
       </c>
-      <c r="C977" s="1">
-        <v>0</v>
-      </c>
+      <c r="C977" s="1"/>
       <c r="D977" s="1"/>
-    </row>
-    <row r="978" spans="1:4">
+      <c r="E977" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="978" spans="1:5">
       <c r="A978" s="4">
         <v>45936</v>
       </c>
       <c r="B978" s="1">
         <v>0</v>
       </c>
-      <c r="C978" s="1">
-        <v>0</v>
-      </c>
+      <c r="C978" s="1"/>
       <c r="D978" s="1"/>
-    </row>
-    <row r="979" spans="1:4">
+      <c r="E978" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="979" spans="1:5">
       <c r="A979" s="4">
         <v>45937</v>
       </c>
       <c r="B979" s="1">
         <v>0</v>
       </c>
-      <c r="C979" s="1">
-        <v>0</v>
-      </c>
+      <c r="C979" s="1"/>
       <c r="D979" s="1"/>
-    </row>
-    <row r="980" spans="1:4">
+      <c r="E979" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="980" spans="1:5">
       <c r="A980" s="4">
         <v>45938</v>
       </c>
       <c r="B980" s="1">
         <v>0</v>
       </c>
-      <c r="C980" s="1">
-        <v>0</v>
-      </c>
+      <c r="C980" s="1"/>
       <c r="D980" s="1"/>
-    </row>
-    <row r="981" spans="1:4">
+      <c r="E980" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="981" spans="1:5">
       <c r="A981" s="4">
         <v>45939</v>
       </c>
       <c r="B981" s="1">
         <v>0</v>
       </c>
-      <c r="C981" s="1">
-        <v>0</v>
-      </c>
+      <c r="C981" s="1"/>
       <c r="D981" s="1"/>
-    </row>
-    <row r="982" spans="1:4">
+      <c r="E981" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="982" spans="1:5">
       <c r="A982" s="4">
         <v>45940</v>
       </c>
       <c r="B982" s="1">
         <v>0</v>
       </c>
-      <c r="C982" s="1">
-        <v>0</v>
-      </c>
+      <c r="C982" s="1"/>
       <c r="D982" s="1"/>
-    </row>
-    <row r="983" spans="1:4">
+      <c r="E982" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="983" spans="1:5">
       <c r="A983" s="4">
         <v>45943</v>
       </c>
       <c r="B983" s="1">
         <v>0</v>
       </c>
-      <c r="C983" s="1">
-        <v>0</v>
-      </c>
+      <c r="C983" s="1"/>
       <c r="D983" s="1"/>
-    </row>
-    <row r="984" spans="1:4">
+      <c r="E983" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="984" spans="1:5">
       <c r="A984" s="4">
         <v>45944</v>
       </c>
       <c r="B984" s="1">
         <v>0</v>
       </c>
-      <c r="C984" s="1">
-        <v>0</v>
-      </c>
+      <c r="C984" s="1"/>
       <c r="D984" s="1"/>
-    </row>
-    <row r="985" spans="1:4">
+      <c r="E984" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="985" spans="1:5">
       <c r="A985" s="4">
         <v>45945</v>
       </c>
       <c r="B985" s="1">
         <v>0</v>
       </c>
-      <c r="C985" s="1">
-        <v>0</v>
-      </c>
+      <c r="C985" s="1"/>
       <c r="D985" s="1"/>
-    </row>
-    <row r="986" spans="1:4">
+      <c r="E985" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="986" spans="1:5">
       <c r="A986" s="4">
         <v>45946</v>
       </c>
       <c r="B986" s="1">
         <v>0</v>
       </c>
-      <c r="C986" s="1">
-        <v>0</v>
-      </c>
+      <c r="C986" s="1"/>
       <c r="D986" s="1"/>
-    </row>
-    <row r="987" spans="1:4">
+      <c r="E986" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="987" spans="1:5">
       <c r="A987" s="4">
         <v>45947</v>
       </c>
       <c r="B987" s="1">
         <v>0</v>
       </c>
-      <c r="C987" s="1">
-        <v>0</v>
-      </c>
+      <c r="C987" s="1"/>
       <c r="D987" s="1"/>
-    </row>
-    <row r="988" spans="1:4">
+      <c r="E987" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="988" spans="1:5">
       <c r="A988" s="4">
         <v>45950</v>
       </c>
       <c r="B988" s="1">
         <v>0</v>
       </c>
-      <c r="C988" s="1">
-        <v>0</v>
-      </c>
+      <c r="C988" s="1"/>
       <c r="D988" s="1"/>
-    </row>
-    <row r="989" spans="1:4">
+      <c r="E988" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="989" spans="1:5">
       <c r="A989" s="4">
         <v>45951</v>
       </c>
       <c r="B989" s="1">
         <v>0</v>
       </c>
-      <c r="C989" s="1">
-        <v>0</v>
-      </c>
+      <c r="C989" s="1"/>
       <c r="D989" s="1"/>
-    </row>
-    <row r="990" spans="1:4">
+      <c r="E989" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="990" spans="1:5">
       <c r="A990" s="4">
         <v>45952</v>
       </c>
       <c r="B990" s="1">
         <v>0</v>
       </c>
-      <c r="C990" s="1">
-        <v>0</v>
-      </c>
+      <c r="C990" s="1"/>
       <c r="D990" s="1"/>
-    </row>
-    <row r="991" spans="1:4">
+      <c r="E990" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="991" spans="1:5">
       <c r="A991" s="4">
         <v>45953</v>
       </c>
       <c r="B991" s="1">
         <v>0</v>
       </c>
-      <c r="C991" s="1">
-        <v>0</v>
-      </c>
+      <c r="C991" s="1"/>
       <c r="D991" s="1"/>
-    </row>
-    <row r="992" spans="1:4">
+      <c r="E991" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="992" spans="1:5">
       <c r="A992" s="4">
         <v>45954</v>
       </c>
       <c r="B992" s="1">
         <v>0</v>
       </c>
-      <c r="C992" s="1">
-        <v>0</v>
-      </c>
+      <c r="C992" s="1"/>
       <c r="D992" s="1"/>
-    </row>
-    <row r="993" spans="1:4">
+      <c r="E992" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="993" spans="1:5">
       <c r="A993" s="4">
         <v>45957</v>
       </c>
       <c r="B993" s="1">
         <v>0</v>
       </c>
-      <c r="C993" s="1">
-        <v>0</v>
-      </c>
+      <c r="C993" s="1"/>
       <c r="D993" s="1"/>
-    </row>
-    <row r="994" spans="1:4">
+      <c r="E993" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="994" spans="1:5">
       <c r="A994" s="4">
         <v>45958</v>
       </c>
       <c r="B994" s="1">
         <v>0</v>
       </c>
-      <c r="C994" s="1">
-        <v>0</v>
-      </c>
+      <c r="C994" s="1"/>
       <c r="D994" s="1"/>
-    </row>
-    <row r="995" spans="1:4">
+      <c r="E994" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="995" spans="1:5">
       <c r="A995" s="4">
         <v>45959</v>
       </c>
       <c r="B995" s="1">
         <v>0</v>
       </c>
-      <c r="C995" s="1">
-        <v>0</v>
-      </c>
+      <c r="C995" s="1"/>
       <c r="D995" s="1"/>
-    </row>
-    <row r="996" spans="1:4">
+      <c r="E995" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="996" spans="1:5">
       <c r="A996" s="4">
         <v>45960</v>
       </c>
       <c r="B996" s="1">
         <v>0</v>
       </c>
-      <c r="C996" s="1">
-        <v>0</v>
-      </c>
+      <c r="C996" s="1"/>
       <c r="D996" s="1"/>
-    </row>
-    <row r="997" spans="1:4">
+      <c r="E996" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="997" spans="1:5">
       <c r="A997" s="4">
         <v>45961</v>
       </c>
       <c r="B997" s="1">
         <v>0</v>
       </c>
-      <c r="C997" s="1">
-        <v>0</v>
-      </c>
+      <c r="C997" s="1"/>
       <c r="D997" s="1"/>
-    </row>
-    <row r="998" spans="1:4">
+      <c r="E997" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="998" spans="1:5">
       <c r="A998" s="4">
         <v>45964</v>
       </c>
       <c r="B998" s="1">
         <v>0</v>
       </c>
-      <c r="C998" s="1">
-        <v>0</v>
-      </c>
+      <c r="C998" s="1"/>
       <c r="D998" s="1"/>
-    </row>
-    <row r="999" spans="1:4">
+      <c r="E998" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="999" spans="1:5">
       <c r="A999" s="4">
         <v>45965</v>
       </c>
       <c r="B999" s="1">
         <v>0</v>
       </c>
-      <c r="C999" s="1">
-        <v>0</v>
-      </c>
+      <c r="C999" s="1"/>
       <c r="D999" s="1"/>
-    </row>
-    <row r="1000" spans="1:4">
+      <c r="E999" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:5">
       <c r="A1000" s="4">
         <v>45966</v>
       </c>
       <c r="B1000" s="1">
         <v>0</v>
       </c>
-      <c r="C1000" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1000" s="1"/>
       <c r="D1000" s="1"/>
-    </row>
-    <row r="1001" spans="1:4">
+      <c r="E1000" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:5">
       <c r="A1001" s="4">
         <v>45967</v>
       </c>
       <c r="B1001" s="1">
         <v>0</v>
       </c>
-      <c r="C1001" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1001" s="1"/>
       <c r="D1001" s="1"/>
-    </row>
-    <row r="1002" spans="1:4">
+      <c r="E1001" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:5">
       <c r="A1002" s="4">
         <v>45968</v>
       </c>
       <c r="B1002" s="1">
         <v>0</v>
       </c>
-      <c r="C1002" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1002" s="1"/>
       <c r="D1002" s="1"/>
-    </row>
-    <row r="1003" spans="1:4">
+      <c r="E1002" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:5">
       <c r="A1003" s="4">
         <v>45971</v>
       </c>
       <c r="B1003" s="1">
         <v>0</v>
       </c>
-      <c r="C1003" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1003" s="1"/>
       <c r="D1003" s="1"/>
-    </row>
-    <row r="1004" spans="1:4">
+      <c r="E1003" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="1004" spans="1:5">
       <c r="A1004" s="4">
         <v>45972</v>
       </c>
       <c r="B1004" s="1">
         <v>0</v>
       </c>
-      <c r="C1004" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1004" s="1"/>
       <c r="D1004" s="1"/>
-    </row>
-    <row r="1005" spans="1:4">
+      <c r="E1004" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="1005" spans="1:5">
       <c r="A1005" s="4">
         <v>45973</v>
       </c>
       <c r="B1005" s="1">
         <v>0</v>
       </c>
-      <c r="C1005" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1005" s="1"/>
       <c r="D1005" s="1"/>
-    </row>
-    <row r="1006" spans="1:4">
+      <c r="E1005" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="1006" spans="1:5">
       <c r="A1006" s="4">
         <v>45974</v>
       </c>
       <c r="B1006" s="1">
         <v>0</v>
       </c>
-      <c r="C1006" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1006" s="1"/>
       <c r="D1006" s="1"/>
-    </row>
-    <row r="1007" spans="1:4">
+      <c r="E1006" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="1007" spans="1:5">
       <c r="A1007" s="4">
         <v>45975</v>
       </c>
       <c r="B1007" s="1">
         <v>0</v>
       </c>
-      <c r="C1007" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1007" s="1"/>
       <c r="D1007" s="1"/>
-    </row>
-    <row r="1008" spans="1:4">
+      <c r="E1007" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="1008" spans="1:5">
       <c r="A1008" s="4">
         <v>45978</v>
       </c>
       <c r="B1008" s="1">
         <v>0</v>
       </c>
-      <c r="C1008" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1008" s="1"/>
       <c r="D1008" s="1"/>
-    </row>
-    <row r="1009" spans="1:4">
+      <c r="E1008" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:5">
       <c r="A1009" s="4">
         <v>45979</v>
       </c>
       <c r="B1009" s="1">
         <v>0</v>
       </c>
-      <c r="C1009" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1009" s="1"/>
       <c r="D1009" s="1"/>
-    </row>
-    <row r="1010" spans="1:4">
+      <c r="E1009" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="1010" spans="1:5">
       <c r="A1010" s="4">
         <v>45980</v>
       </c>
       <c r="B1010" s="1">
         <v>0</v>
       </c>
-      <c r="C1010" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1010" s="1"/>
       <c r="D1010" s="1"/>
-    </row>
-    <row r="1011" spans="1:4">
+      <c r="E1010" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="1011" spans="1:5">
       <c r="A1011" s="4">
         <v>45981</v>
       </c>
       <c r="B1011" s="1">
         <v>0</v>
       </c>
-      <c r="C1011" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1011" s="1"/>
       <c r="D1011" s="1"/>
-    </row>
-    <row r="1012" spans="1:4">
+      <c r="E1011" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="1012" spans="1:5">
       <c r="A1012" s="4">
         <v>45982</v>
       </c>
       <c r="B1012" s="1">
         <v>0</v>
       </c>
-      <c r="C1012" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1012" s="1"/>
       <c r="D1012" s="1"/>
-    </row>
-    <row r="1013" spans="1:4">
+      <c r="E1012" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="1013" spans="1:5">
       <c r="A1013" s="4">
         <v>45985</v>
       </c>
       <c r="B1013" s="1">
         <v>0</v>
       </c>
-      <c r="C1013" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1013" s="1"/>
       <c r="D1013" s="1"/>
-    </row>
-    <row r="1014" spans="1:4">
+      <c r="E1013" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="1014" spans="1:5">
       <c r="A1014" s="4">
         <v>45986</v>
       </c>
       <c r="B1014" s="1">
         <v>0</v>
       </c>
-      <c r="C1014" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1014" s="1"/>
       <c r="D1014" s="1"/>
-    </row>
-    <row r="1015" spans="1:4">
+      <c r="E1014" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="1015" spans="1:5">
       <c r="A1015" s="4">
         <v>45987</v>
       </c>
       <c r="B1015" s="1">
         <v>0</v>
       </c>
-      <c r="C1015" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1015" s="1"/>
       <c r="D1015" s="1"/>
-    </row>
-    <row r="1016" spans="1:4">
+      <c r="E1015" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="1016" spans="1:5">
       <c r="A1016" s="4">
         <v>45988</v>
       </c>
       <c r="B1016" s="1">
         <v>0</v>
       </c>
-      <c r="C1016" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1016" s="1"/>
       <c r="D1016" s="1"/>
-    </row>
-    <row r="1017" spans="1:4">
+      <c r="E1016" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="1017" spans="1:5">
       <c r="A1017" s="4">
         <v>45989</v>
       </c>
       <c r="B1017" s="1">
         <v>0</v>
       </c>
-      <c r="C1017" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1017" s="1"/>
       <c r="D1017" s="1"/>
-    </row>
-    <row r="1018" spans="1:4">
+      <c r="E1017" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:5">
       <c r="A1018" s="4">
         <v>45992</v>
       </c>
       <c r="B1018" s="1">
         <v>0</v>
       </c>
-      <c r="C1018" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1018" s="1"/>
       <c r="D1018" s="1"/>
-    </row>
-    <row r="1019" spans="1:4">
+      <c r="E1018" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="1019" spans="1:5">
       <c r="A1019" s="4">
         <v>45993</v>
       </c>
       <c r="B1019" s="1">
         <v>0</v>
       </c>
-      <c r="C1019" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1019" s="1"/>
       <c r="D1019" s="1"/>
-    </row>
-    <row r="1020" spans="1:4">
+      <c r="E1019" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:5">
       <c r="A1020" s="4">
         <v>45994</v>
       </c>
       <c r="B1020" s="1">
         <v>0</v>
       </c>
-      <c r="C1020" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1020" s="1"/>
       <c r="D1020" s="1"/>
-    </row>
-    <row r="1021" spans="1:4">
+      <c r="E1020" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:5">
       <c r="A1021" s="4">
         <v>45995</v>
       </c>
       <c r="B1021" s="1">
         <v>0</v>
       </c>
-      <c r="C1021" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1021" s="1"/>
       <c r="D1021" s="1"/>
-    </row>
-    <row r="1022" spans="1:4">
+      <c r="E1021" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="1022" spans="1:5">
       <c r="A1022" s="4">
         <v>45996</v>
       </c>
       <c r="B1022" s="1">
         <v>0</v>
       </c>
-      <c r="C1022" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1022" s="1"/>
       <c r="D1022" s="1"/>
-    </row>
-    <row r="1023" spans="1:4">
+      <c r="E1022" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="1023" spans="1:5">
       <c r="A1023" s="4">
         <v>45999</v>
       </c>
       <c r="B1023" s="1">
         <v>0</v>
       </c>
-      <c r="C1023" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1023" s="1"/>
       <c r="D1023" s="1"/>
-    </row>
-    <row r="1024" spans="1:4">
+      <c r="E1023" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:5">
       <c r="A1024" s="4">
         <v>46000</v>
       </c>
       <c r="B1024" s="1">
         <v>0</v>
       </c>
-      <c r="C1024" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1024" s="1"/>
       <c r="D1024" s="1"/>
-    </row>
-    <row r="1025" spans="1:4">
+      <c r="E1024" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:5">
       <c r="A1025" s="4">
         <v>46001</v>
       </c>
       <c r="B1025" s="1">
         <v>0</v>
       </c>
-      <c r="C1025" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1025" s="1"/>
       <c r="D1025" s="1"/>
-    </row>
-    <row r="1026" spans="1:4">
+      <c r="E1025" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:5">
       <c r="A1026" s="4">
         <v>46002</v>
       </c>
       <c r="B1026" s="1">
         <v>0</v>
       </c>
-      <c r="C1026" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1026" s="1"/>
       <c r="D1026" s="1"/>
-    </row>
-    <row r="1027" spans="1:4">
+      <c r="E1026" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:5">
       <c r="A1027" s="4">
         <v>46003</v>
       </c>
       <c r="B1027" s="1">
         <v>0</v>
       </c>
-      <c r="C1027" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1027" s="1"/>
       <c r="D1027" s="1"/>
-    </row>
-    <row r="1028" spans="1:4">
+      <c r="E1027" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:5">
       <c r="A1028" s="4">
         <v>46006</v>
       </c>
       <c r="B1028" s="1">
         <v>0</v>
       </c>
-      <c r="C1028" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1028" s="1"/>
       <c r="D1028" s="1"/>
-    </row>
-    <row r="1029" spans="1:4">
+      <c r="E1028" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:5">
       <c r="A1029" s="4">
         <v>46007</v>
       </c>
       <c r="B1029" s="1">
         <v>0</v>
       </c>
-      <c r="C1029" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1029" s="1"/>
       <c r="D1029" s="1"/>
-    </row>
-    <row r="1030" spans="1:4">
+      <c r="E1029" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:5">
       <c r="A1030" s="4">
         <v>46008</v>
       </c>
       <c r="B1030" s="1">
         <v>0</v>
       </c>
-      <c r="C1030" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1030" s="1"/>
       <c r="D1030" s="1"/>
-    </row>
-    <row r="1031" spans="1:4">
+      <c r="E1030" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="1031" spans="1:5">
       <c r="A1031" s="4">
         <v>46009</v>
       </c>
       <c r="B1031" s="1">
         <v>0</v>
       </c>
-      <c r="C1031" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1031" s="1"/>
       <c r="D1031" s="1"/>
-    </row>
-    <row r="1032" spans="1:4">
+      <c r="E1031" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:5">
       <c r="A1032" s="4">
         <v>46010</v>
       </c>
       <c r="B1032" s="1">
         <v>0</v>
       </c>
-      <c r="C1032" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1032" s="1"/>
       <c r="D1032" s="1"/>
-    </row>
-    <row r="1033" spans="1:4">
+      <c r="E1032" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:5">
       <c r="A1033" s="4">
         <v>46013</v>
       </c>
       <c r="B1033" s="1">
         <v>0</v>
       </c>
-      <c r="C1033" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1033" s="1"/>
       <c r="D1033" s="1"/>
-    </row>
-    <row r="1034" spans="1:4">
+      <c r="E1033" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:5">
       <c r="A1034" s="4">
         <v>46014</v>
       </c>
       <c r="B1034" s="1">
         <v>0</v>
       </c>
-      <c r="C1034" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1034" s="1"/>
       <c r="D1034" s="1"/>
-    </row>
-    <row r="1035" spans="1:4">
+      <c r="E1034" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:5">
       <c r="A1035" s="4">
         <v>46015</v>
       </c>
       <c r="B1035" s="1">
         <v>0</v>
       </c>
-      <c r="C1035" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1035" s="1"/>
       <c r="D1035" s="1"/>
-    </row>
-    <row r="1036" spans="1:4">
+      <c r="E1035" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:5">
       <c r="A1036" s="4">
         <v>46016</v>
       </c>
       <c r="B1036" s="1">
         <v>0</v>
       </c>
-      <c r="C1036" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1036" s="1"/>
       <c r="D1036" s="1"/>
-    </row>
-    <row r="1037" spans="1:4">
+      <c r="E1036" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:5">
       <c r="A1037" s="4">
         <v>46017</v>
       </c>
       <c r="B1037" s="1">
         <v>0</v>
       </c>
-      <c r="C1037" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1037" s="1"/>
       <c r="D1037" s="1"/>
-    </row>
-    <row r="1038" spans="1:4">
+      <c r="E1037" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="1038" spans="1:5">
       <c r="A1038" s="4">
         <v>46020</v>
       </c>
       <c r="B1038" s="1">
         <v>0</v>
       </c>
-      <c r="C1038" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1038" s="1"/>
       <c r="D1038" s="1"/>
-    </row>
-    <row r="1039" spans="1:4">
+      <c r="E1038" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:5">
       <c r="A1039" s="4">
         <v>46021</v>
       </c>
       <c r="B1039" s="1">
         <v>0</v>
       </c>
-      <c r="C1039" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1039" s="1"/>
       <c r="D1039" s="1"/>
-    </row>
-    <row r="1040" spans="1:4">
+      <c r="E1039" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="1040" spans="1:5">
       <c r="A1040" s="4">
         <v>46022</v>
       </c>
       <c r="B1040" s="1">
         <v>0</v>
       </c>
-      <c r="C1040" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1040" s="1"/>
       <c r="D1040" s="1"/>
+      <c r="E1040" s="1">
+        <v>10000</v>
+      </c>
     </row>
     <row r="1041" spans="1:4">
       <c r="A1041" s="4">
@@ -16421,9 +16670,7 @@
       <c r="B1041" s="1">
         <v>0</v>
       </c>
-      <c r="C1041" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1041" s="1"/>
       <c r="D1041" s="1"/>
     </row>
     <row r="1042" spans="1:4">
@@ -16433,9 +16680,7 @@
       <c r="B1042" s="1">
         <v>0</v>
       </c>
-      <c r="C1042" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1042" s="1"/>
       <c r="D1042" s="1"/>
     </row>
     <row r="1043" spans="1:4">
@@ -16445,9 +16690,7 @@
       <c r="B1043" s="1">
         <v>0</v>
       </c>
-      <c r="C1043" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1043" s="1"/>
       <c r="D1043" s="1"/>
     </row>
     <row r="1044" spans="1:4">
@@ -16457,9 +16700,7 @@
       <c r="B1044" s="1">
         <v>0</v>
       </c>
-      <c r="C1044" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1044" s="1"/>
       <c r="D1044" s="1"/>
     </row>
     <row r="1045" spans="1:4">
@@ -16469,9 +16710,7 @@
       <c r="B1045" s="1">
         <v>0</v>
       </c>
-      <c r="C1045" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1045" s="1"/>
       <c r="D1045" s="1"/>
     </row>
     <row r="1046" spans="1:4">
@@ -16481,9 +16720,7 @@
       <c r="B1046" s="1">
         <v>0</v>
       </c>
-      <c r="C1046" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1046" s="1"/>
       <c r="D1046" s="1"/>
     </row>
     <row r="1047" spans="1:4">
@@ -16493,9 +16730,7 @@
       <c r="B1047" s="1">
         <v>0</v>
       </c>
-      <c r="C1047" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1047" s="1"/>
       <c r="D1047" s="1"/>
     </row>
     <row r="1048" spans="1:4">
@@ -16505,9 +16740,7 @@
       <c r="B1048" s="1">
         <v>0</v>
       </c>
-      <c r="C1048" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1048" s="1"/>
       <c r="D1048" s="1"/>
     </row>
     <row r="1049" spans="1:4">
@@ -16517,9 +16750,7 @@
       <c r="B1049" s="1">
         <v>0</v>
       </c>
-      <c r="C1049" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1049" s="1"/>
       <c r="D1049" s="1"/>
     </row>
     <row r="1050" spans="1:4">
@@ -16529,9 +16760,7 @@
       <c r="B1050" s="1">
         <v>0</v>
       </c>
-      <c r="C1050" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1050" s="1"/>
       <c r="D1050" s="1"/>
     </row>
     <row r="1051" spans="1:4">
@@ -16541,9 +16770,7 @@
       <c r="B1051" s="1">
         <v>0</v>
       </c>
-      <c r="C1051" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1051" s="1"/>
       <c r="D1051" s="1"/>
     </row>
     <row r="1052" spans="1:4">
@@ -16553,9 +16780,7 @@
       <c r="B1052" s="1">
         <v>0</v>
       </c>
-      <c r="C1052" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1052" s="1"/>
       <c r="D1052" s="1"/>
     </row>
     <row r="1053" spans="1:4">
@@ -16565,9 +16790,7 @@
       <c r="B1053" s="1">
         <v>0</v>
       </c>
-      <c r="C1053" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1053" s="1"/>
       <c r="D1053" s="1"/>
     </row>
     <row r="1054" spans="1:4">
@@ -16577,9 +16800,7 @@
       <c r="B1054" s="1">
         <v>0</v>
       </c>
-      <c r="C1054" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1054" s="1"/>
       <c r="D1054" s="1"/>
     </row>
     <row r="1055" spans="1:4">
@@ -16589,9 +16810,7 @@
       <c r="B1055" s="1">
         <v>0</v>
       </c>
-      <c r="C1055" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1055" s="1"/>
       <c r="D1055" s="1"/>
     </row>
     <row r="1056" spans="1:4">
@@ -16601,9 +16820,7 @@
       <c r="B1056" s="1">
         <v>0</v>
       </c>
-      <c r="C1056" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1056" s="1"/>
       <c r="D1056" s="1"/>
     </row>
     <row r="1057" spans="1:4">
@@ -16613,9 +16830,7 @@
       <c r="B1057" s="1">
         <v>0</v>
       </c>
-      <c r="C1057" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1057" s="1"/>
       <c r="D1057" s="1"/>
     </row>
     <row r="1058" spans="1:4">
@@ -16625,9 +16840,7 @@
       <c r="B1058" s="1">
         <v>0</v>
       </c>
-      <c r="C1058" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1058" s="1"/>
       <c r="D1058" s="1"/>
     </row>
     <row r="1059" spans="1:4">
@@ -16637,9 +16850,7 @@
       <c r="B1059" s="1">
         <v>0</v>
       </c>
-      <c r="C1059" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1059" s="1"/>
       <c r="D1059" s="1"/>
     </row>
     <row r="1060" spans="1:4">
@@ -16649,9 +16860,7 @@
       <c r="B1060" s="1">
         <v>0</v>
       </c>
-      <c r="C1060" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1060" s="1"/>
       <c r="D1060" s="1"/>
     </row>
     <row r="1061" spans="1:4">
@@ -16661,9 +16870,7 @@
       <c r="B1061" s="1">
         <v>0</v>
       </c>
-      <c r="C1061" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1061" s="1"/>
       <c r="D1061" s="1"/>
     </row>
     <row r="1062" spans="1:4">
@@ -16673,9 +16880,7 @@
       <c r="B1062" s="1">
         <v>0</v>
       </c>
-      <c r="C1062" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1062" s="1"/>
       <c r="D1062" s="1"/>
     </row>
     <row r="1063" spans="1:4">
@@ -16685,9 +16890,7 @@
       <c r="B1063" s="1">
         <v>0</v>
       </c>
-      <c r="C1063" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1063" s="1"/>
       <c r="D1063" s="1"/>
     </row>
     <row r="1064" spans="1:4">
@@ -16697,9 +16900,7 @@
       <c r="B1064" s="1">
         <v>0</v>
       </c>
-      <c r="C1064" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1064" s="1"/>
       <c r="D1064" s="1"/>
     </row>
     <row r="1065" spans="1:4">
@@ -16709,9 +16910,7 @@
       <c r="B1065" s="1">
         <v>0</v>
       </c>
-      <c r="C1065" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1065" s="1"/>
       <c r="D1065" s="1"/>
     </row>
     <row r="1066" spans="1:4">
@@ -16721,9 +16920,7 @@
       <c r="B1066" s="1">
         <v>0</v>
       </c>
-      <c r="C1066" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1066" s="1"/>
       <c r="D1066" s="1"/>
     </row>
     <row r="1067" spans="1:4">
@@ -16733,9 +16930,7 @@
       <c r="B1067" s="1">
         <v>0</v>
       </c>
-      <c r="C1067" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1067" s="1"/>
       <c r="D1067" s="1"/>
     </row>
     <row r="1068" spans="1:4">
@@ -16745,9 +16940,7 @@
       <c r="B1068" s="1">
         <v>0</v>
       </c>
-      <c r="C1068" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1068" s="1"/>
       <c r="D1068" s="1"/>
     </row>
     <row r="1069" spans="1:4">
@@ -16757,9 +16950,7 @@
       <c r="B1069" s="1">
         <v>0</v>
       </c>
-      <c r="C1069" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1069" s="1"/>
       <c r="D1069" s="1"/>
     </row>
     <row r="1070" spans="1:4">
@@ -16769,9 +16960,7 @@
       <c r="B1070" s="1">
         <v>0</v>
       </c>
-      <c r="C1070" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1070" s="1"/>
       <c r="D1070" s="1"/>
     </row>
     <row r="1071" spans="1:4">
@@ -16781,9 +16970,7 @@
       <c r="B1071" s="1">
         <v>0</v>
       </c>
-      <c r="C1071" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1071" s="1"/>
       <c r="D1071" s="1"/>
     </row>
     <row r="1072" spans="1:4">
@@ -16793,9 +16980,7 @@
       <c r="B1072" s="1">
         <v>0</v>
       </c>
-      <c r="C1072" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1072" s="1"/>
       <c r="D1072" s="1"/>
     </row>
     <row r="1073" spans="1:4">
@@ -16805,9 +16990,7 @@
       <c r="B1073" s="1">
         <v>0</v>
       </c>
-      <c r="C1073" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1073" s="1"/>
       <c r="D1073" s="1"/>
     </row>
     <row r="1074" spans="1:4">
@@ -16817,9 +17000,7 @@
       <c r="B1074" s="1">
         <v>0</v>
       </c>
-      <c r="C1074" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1074" s="1"/>
       <c r="D1074" s="1"/>
     </row>
     <row r="1075" spans="1:4">
@@ -16829,9 +17010,7 @@
       <c r="B1075" s="1">
         <v>0</v>
       </c>
-      <c r="C1075" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1075" s="1"/>
       <c r="D1075" s="1"/>
     </row>
     <row r="1076" spans="1:4">
@@ -16841,9 +17020,7 @@
       <c r="B1076" s="1">
         <v>0</v>
       </c>
-      <c r="C1076" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1076" s="1"/>
       <c r="D1076" s="1"/>
     </row>
     <row r="1077" spans="1:4">
@@ -16853,9 +17030,7 @@
       <c r="B1077" s="1">
         <v>0</v>
       </c>
-      <c r="C1077" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1077" s="1"/>
       <c r="D1077" s="1"/>
     </row>
     <row r="1078" spans="1:4">
@@ -16865,9 +17040,7 @@
       <c r="B1078" s="1">
         <v>0</v>
       </c>
-      <c r="C1078" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1078" s="1"/>
       <c r="D1078" s="1"/>
     </row>
     <row r="1079" spans="1:4">
@@ -16877,9 +17050,7 @@
       <c r="B1079" s="1">
         <v>0</v>
       </c>
-      <c r="C1079" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1079" s="1"/>
       <c r="D1079" s="1"/>
     </row>
     <row r="1080" spans="1:4">
@@ -16889,9 +17060,7 @@
       <c r="B1080" s="1">
         <v>0</v>
       </c>
-      <c r="C1080" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1080" s="1"/>
       <c r="D1080" s="1"/>
     </row>
     <row r="1081" spans="1:4">
@@ -16901,9 +17070,7 @@
       <c r="B1081" s="1">
         <v>0</v>
       </c>
-      <c r="C1081" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1081" s="1"/>
       <c r="D1081" s="1"/>
     </row>
     <row r="1082" spans="1:4">
@@ -16913,9 +17080,7 @@
       <c r="B1082" s="1">
         <v>0</v>
       </c>
-      <c r="C1082" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1082" s="1"/>
       <c r="D1082" s="1"/>
     </row>
     <row r="1083" spans="1:4">
@@ -16925,9 +17090,7 @@
       <c r="B1083" s="1">
         <v>0</v>
       </c>
-      <c r="C1083" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1083" s="1"/>
       <c r="D1083" s="1"/>
     </row>
     <row r="1084" spans="1:4">
@@ -16937,9 +17100,7 @@
       <c r="B1084" s="1">
         <v>0</v>
       </c>
-      <c r="C1084" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1084" s="1"/>
       <c r="D1084" s="1"/>
     </row>
     <row r="1085" spans="1:4">
@@ -16949,9 +17110,7 @@
       <c r="B1085" s="1">
         <v>0</v>
       </c>
-      <c r="C1085" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1085" s="1"/>
       <c r="D1085" s="1"/>
     </row>
     <row r="1086" spans="1:4">
@@ -16961,9 +17120,7 @@
       <c r="B1086" s="1">
         <v>0</v>
       </c>
-      <c r="C1086" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1086" s="1"/>
       <c r="D1086" s="1"/>
     </row>
     <row r="1087" spans="1:4">
@@ -16973,9 +17130,7 @@
       <c r="B1087" s="1">
         <v>0</v>
       </c>
-      <c r="C1087" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1087" s="1"/>
       <c r="D1087" s="1"/>
     </row>
     <row r="1088" spans="1:4">
@@ -16985,9 +17140,7 @@
       <c r="B1088" s="1">
         <v>0</v>
       </c>
-      <c r="C1088" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1088" s="1"/>
       <c r="D1088" s="1"/>
     </row>
     <row r="1089" spans="1:4">
@@ -16997,9 +17150,7 @@
       <c r="B1089" s="1">
         <v>0</v>
       </c>
-      <c r="C1089" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1089" s="1"/>
       <c r="D1089" s="1"/>
     </row>
     <row r="1090" spans="1:4">
@@ -17009,9 +17160,7 @@
       <c r="B1090" s="1">
         <v>0</v>
       </c>
-      <c r="C1090" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1090" s="1"/>
       <c r="D1090" s="1"/>
     </row>
     <row r="1091" spans="1:4">
@@ -17021,9 +17170,7 @@
       <c r="B1091" s="1">
         <v>0</v>
       </c>
-      <c r="C1091" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1091" s="1"/>
       <c r="D1091" s="1"/>
     </row>
     <row r="1092" spans="1:4">
@@ -17033,9 +17180,7 @@
       <c r="B1092" s="1">
         <v>0</v>
       </c>
-      <c r="C1092" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1092" s="1"/>
       <c r="D1092" s="1"/>
     </row>
     <row r="1093" spans="1:4">
@@ -17045,9 +17190,7 @@
       <c r="B1093" s="1">
         <v>0</v>
       </c>
-      <c r="C1093" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1093" s="1"/>
       <c r="D1093" s="1"/>
     </row>
     <row r="1094" spans="1:4">
@@ -17057,9 +17200,7 @@
       <c r="B1094" s="1">
         <v>0</v>
       </c>
-      <c r="C1094" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1094" s="1"/>
       <c r="D1094" s="1"/>
     </row>
     <row r="1095" spans="1:4">
@@ -17069,9 +17210,7 @@
       <c r="B1095" s="1">
         <v>0</v>
       </c>
-      <c r="C1095" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1095" s="1"/>
       <c r="D1095" s="1"/>
     </row>
     <row r="1096" spans="1:4">
@@ -17081,9 +17220,7 @@
       <c r="B1096" s="1">
         <v>0</v>
       </c>
-      <c r="C1096" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1096" s="1"/>
       <c r="D1096" s="1"/>
     </row>
     <row r="1097" spans="1:4">
@@ -17093,9 +17230,7 @@
       <c r="B1097" s="1">
         <v>0</v>
       </c>
-      <c r="C1097" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1097" s="1"/>
       <c r="D1097" s="1"/>
     </row>
     <row r="1098" spans="1:4">
@@ -17105,9 +17240,7 @@
       <c r="B1098" s="1">
         <v>0</v>
       </c>
-      <c r="C1098" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1098" s="1"/>
       <c r="D1098" s="1"/>
     </row>
     <row r="1099" spans="1:4">
@@ -17117,9 +17250,7 @@
       <c r="B1099" s="1">
         <v>0</v>
       </c>
-      <c r="C1099" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1099" s="1"/>
       <c r="D1099" s="1"/>
     </row>
     <row r="1100" spans="1:4">
@@ -17129,9 +17260,7 @@
       <c r="B1100" s="1">
         <v>0</v>
       </c>
-      <c r="C1100" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1100" s="1"/>
       <c r="D1100" s="1"/>
     </row>
     <row r="1101" spans="1:4">
@@ -17141,9 +17270,7 @@
       <c r="B1101" s="1">
         <v>0</v>
       </c>
-      <c r="C1101" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1101" s="1"/>
       <c r="D1101" s="1"/>
     </row>
     <row r="1102" spans="1:4">
@@ -17153,9 +17280,7 @@
       <c r="B1102" s="1">
         <v>0</v>
       </c>
-      <c r="C1102" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1102" s="1"/>
       <c r="D1102" s="1"/>
     </row>
     <row r="1103" spans="1:4">
@@ -17165,9 +17290,7 @@
       <c r="B1103" s="1">
         <v>0</v>
       </c>
-      <c r="C1103" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1103" s="1"/>
       <c r="D1103" s="1"/>
     </row>
     <row r="1104" spans="1:4">
@@ -17177,9 +17300,7 @@
       <c r="B1104" s="1">
         <v>0</v>
       </c>
-      <c r="C1104" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1104" s="1"/>
       <c r="D1104" s="1"/>
     </row>
     <row r="1105" spans="1:4">
@@ -17189,9 +17310,7 @@
       <c r="B1105" s="1">
         <v>0</v>
       </c>
-      <c r="C1105" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1105" s="1"/>
       <c r="D1105" s="1"/>
     </row>
     <row r="1106" spans="1:4">
@@ -17201,9 +17320,7 @@
       <c r="B1106" s="1">
         <v>0</v>
       </c>
-      <c r="C1106" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1106" s="1"/>
       <c r="D1106" s="1"/>
     </row>
     <row r="1107" spans="1:4">
@@ -17213,9 +17330,7 @@
       <c r="B1107" s="1">
         <v>0</v>
       </c>
-      <c r="C1107" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1107" s="1"/>
       <c r="D1107" s="1"/>
     </row>
     <row r="1108" spans="1:4">
@@ -17225,9 +17340,7 @@
       <c r="B1108" s="1">
         <v>0</v>
       </c>
-      <c r="C1108" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1108" s="1"/>
       <c r="D1108" s="1"/>
     </row>
     <row r="1109" spans="1:4">
@@ -17237,9 +17350,7 @@
       <c r="B1109" s="1">
         <v>0</v>
       </c>
-      <c r="C1109" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1109" s="1"/>
       <c r="D1109" s="1"/>
     </row>
     <row r="1110" spans="1:4">
@@ -17249,9 +17360,7 @@
       <c r="B1110" s="1">
         <v>0</v>
       </c>
-      <c r="C1110" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1110" s="1"/>
       <c r="D1110" s="1"/>
     </row>
     <row r="1111" spans="1:4">
@@ -17261,9 +17370,7 @@
       <c r="B1111" s="1">
         <v>0</v>
       </c>
-      <c r="C1111" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1111" s="1"/>
       <c r="D1111" s="1"/>
     </row>
     <row r="1112" spans="1:4">
@@ -17273,9 +17380,7 @@
       <c r="B1112" s="1">
         <v>0</v>
       </c>
-      <c r="C1112" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1112" s="1"/>
       <c r="D1112" s="1"/>
     </row>
     <row r="1113" spans="1:4">
@@ -17285,9 +17390,7 @@
       <c r="B1113" s="1">
         <v>0</v>
       </c>
-      <c r="C1113" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1113" s="1"/>
       <c r="D1113" s="1"/>
     </row>
     <row r="1114" spans="1:4">
@@ -17297,9 +17400,7 @@
       <c r="B1114" s="1">
         <v>0</v>
       </c>
-      <c r="C1114" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1114" s="1"/>
       <c r="D1114" s="1"/>
     </row>
     <row r="1115" spans="1:4">
@@ -17309,9 +17410,7 @@
       <c r="B1115" s="1">
         <v>0</v>
       </c>
-      <c r="C1115" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1115" s="1"/>
       <c r="D1115" s="1"/>
     </row>
     <row r="1116" spans="1:4">
@@ -17321,9 +17420,7 @@
       <c r="B1116" s="1">
         <v>0</v>
       </c>
-      <c r="C1116" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1116" s="1"/>
       <c r="D1116" s="1"/>
     </row>
     <row r="1117" spans="1:4">
@@ -17333,9 +17430,7 @@
       <c r="B1117" s="1">
         <v>0</v>
       </c>
-      <c r="C1117" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1117" s="1"/>
       <c r="D1117" s="1"/>
     </row>
     <row r="1118" spans="1:4">
@@ -17345,9 +17440,7 @@
       <c r="B1118" s="1">
         <v>0</v>
       </c>
-      <c r="C1118" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1118" s="1"/>
       <c r="D1118" s="1"/>
     </row>
     <row r="1119" spans="1:4">
@@ -17357,9 +17450,7 @@
       <c r="B1119" s="1">
         <v>0</v>
       </c>
-      <c r="C1119" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1119" s="1"/>
       <c r="D1119" s="1"/>
     </row>
     <row r="1120" spans="1:4">
@@ -17369,9 +17460,7 @@
       <c r="B1120" s="1">
         <v>0</v>
       </c>
-      <c r="C1120" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1120" s="1"/>
       <c r="D1120" s="1"/>
     </row>
     <row r="1121" spans="1:4">
@@ -17381,9 +17470,7 @@
       <c r="B1121" s="1">
         <v>0</v>
       </c>
-      <c r="C1121" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1121" s="1"/>
       <c r="D1121" s="1"/>
     </row>
     <row r="1122" spans="1:4">
@@ -17393,9 +17480,7 @@
       <c r="B1122" s="1">
         <v>0</v>
       </c>
-      <c r="C1122" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1122" s="1"/>
       <c r="D1122" s="1"/>
     </row>
     <row r="1123" spans="1:4">
@@ -17405,9 +17490,7 @@
       <c r="B1123" s="1">
         <v>0</v>
       </c>
-      <c r="C1123" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1123" s="1"/>
       <c r="D1123" s="1"/>
     </row>
     <row r="1124" spans="1:4">
@@ -17417,9 +17500,7 @@
       <c r="B1124" s="1">
         <v>0</v>
       </c>
-      <c r="C1124" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1124" s="1"/>
       <c r="D1124" s="1"/>
     </row>
     <row r="1125" spans="1:4">
@@ -17429,9 +17510,7 @@
       <c r="B1125" s="1">
         <v>0</v>
       </c>
-      <c r="C1125" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1125" s="1"/>
       <c r="D1125" s="1"/>
     </row>
     <row r="1126" spans="1:4">
@@ -17441,9 +17520,7 @@
       <c r="B1126" s="1">
         <v>0</v>
       </c>
-      <c r="C1126" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1126" s="1"/>
       <c r="D1126" s="1"/>
     </row>
     <row r="1127" spans="1:4">
@@ -17453,9 +17530,7 @@
       <c r="B1127" s="1">
         <v>0</v>
       </c>
-      <c r="C1127" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1127" s="1"/>
       <c r="D1127" s="1"/>
     </row>
     <row r="1128" spans="1:4">
@@ -17465,9 +17540,7 @@
       <c r="B1128" s="1">
         <v>0</v>
       </c>
-      <c r="C1128" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1128" s="1"/>
       <c r="D1128" s="1"/>
     </row>
     <row r="1129" spans="1:4">
@@ -17477,9 +17550,7 @@
       <c r="B1129" s="1">
         <v>0</v>
       </c>
-      <c r="C1129" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1129" s="1"/>
       <c r="D1129" s="1"/>
     </row>
     <row r="1130" spans="1:4">
@@ -17489,9 +17560,7 @@
       <c r="B1130" s="1">
         <v>0</v>
       </c>
-      <c r="C1130" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1130" s="1"/>
       <c r="D1130" s="1"/>
     </row>
     <row r="1131" spans="1:4">
@@ -17501,9 +17570,7 @@
       <c r="B1131" s="1">
         <v>0</v>
       </c>
-      <c r="C1131" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1131" s="1"/>
       <c r="D1131" s="1"/>
     </row>
     <row r="1132" spans="1:4">
@@ -17513,9 +17580,7 @@
       <c r="B1132" s="1">
         <v>0</v>
       </c>
-      <c r="C1132" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1132" s="1"/>
       <c r="D1132" s="1"/>
     </row>
     <row r="1133" spans="1:4">
@@ -17525,9 +17590,7 @@
       <c r="B1133" s="1">
         <v>0</v>
       </c>
-      <c r="C1133" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1133" s="1"/>
       <c r="D1133" s="1"/>
     </row>
     <row r="1134" spans="1:4">
@@ -17537,9 +17600,7 @@
       <c r="B1134" s="1">
         <v>0</v>
       </c>
-      <c r="C1134" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1134" s="1"/>
       <c r="D1134" s="1"/>
     </row>
     <row r="1135" spans="1:4">
@@ -17549,9 +17610,7 @@
       <c r="B1135" s="1">
         <v>0</v>
       </c>
-      <c r="C1135" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1135" s="1"/>
       <c r="D1135" s="1"/>
     </row>
     <row r="1136" spans="1:4">
@@ -17561,9 +17620,7 @@
       <c r="B1136" s="1">
         <v>0</v>
       </c>
-      <c r="C1136" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1136" s="1"/>
       <c r="D1136" s="1"/>
     </row>
     <row r="1137" spans="1:4">
@@ -17573,9 +17630,7 @@
       <c r="B1137" s="1">
         <v>0</v>
       </c>
-      <c r="C1137" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1137" s="1"/>
       <c r="D1137" s="1"/>
     </row>
     <row r="1138" spans="1:4">
@@ -17585,9 +17640,7 @@
       <c r="B1138" s="1">
         <v>0</v>
       </c>
-      <c r="C1138" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1138" s="1"/>
       <c r="D1138" s="1"/>
     </row>
     <row r="1139" spans="1:4">
@@ -17597,9 +17650,7 @@
       <c r="B1139" s="1">
         <v>0</v>
       </c>
-      <c r="C1139" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1139" s="1"/>
       <c r="D1139" s="1"/>
     </row>
     <row r="1140" spans="1:4">
@@ -17609,9 +17660,7 @@
       <c r="B1140" s="1">
         <v>0</v>
       </c>
-      <c r="C1140" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1140" s="1"/>
       <c r="D1140" s="1"/>
     </row>
     <row r="1141" spans="1:4">
@@ -17621,9 +17670,7 @@
       <c r="B1141" s="1">
         <v>0</v>
       </c>
-      <c r="C1141" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1141" s="1"/>
       <c r="D1141" s="1"/>
     </row>
     <row r="1142" spans="1:4">
@@ -17633,9 +17680,7 @@
       <c r="B1142" s="1">
         <v>0</v>
       </c>
-      <c r="C1142" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1142" s="1"/>
       <c r="D1142" s="1"/>
     </row>
     <row r="1143" spans="1:4">
@@ -17645,9 +17690,7 @@
       <c r="B1143" s="1">
         <v>0</v>
       </c>
-      <c r="C1143" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1143" s="1"/>
       <c r="D1143" s="1"/>
     </row>
     <row r="1144" spans="1:4">
@@ -17657,9 +17700,7 @@
       <c r="B1144" s="1">
         <v>0</v>
       </c>
-      <c r="C1144" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1144" s="1"/>
       <c r="D1144" s="1"/>
     </row>
     <row r="1145" spans="1:4">
@@ -17669,9 +17710,7 @@
       <c r="B1145" s="1">
         <v>0</v>
       </c>
-      <c r="C1145" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1145" s="1"/>
       <c r="D1145" s="1"/>
     </row>
     <row r="1146" spans="1:4">
@@ -17681,9 +17720,7 @@
       <c r="B1146" s="1">
         <v>0</v>
       </c>
-      <c r="C1146" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1146" s="1"/>
       <c r="D1146" s="1"/>
     </row>
     <row r="1147" spans="1:4">
@@ -17693,9 +17730,7 @@
       <c r="B1147" s="1">
         <v>0</v>
       </c>
-      <c r="C1147" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1147" s="1"/>
       <c r="D1147" s="1"/>
     </row>
     <row r="1148" spans="1:4">
@@ -17705,9 +17740,7 @@
       <c r="B1148" s="1">
         <v>0</v>
       </c>
-      <c r="C1148" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1148" s="1"/>
       <c r="D1148" s="1"/>
     </row>
     <row r="1149" spans="1:4">
@@ -17717,9 +17750,7 @@
       <c r="B1149" s="1">
         <v>0</v>
       </c>
-      <c r="C1149" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1149" s="1"/>
       <c r="D1149" s="1"/>
     </row>
     <row r="1150" spans="1:4">
@@ -17729,9 +17760,7 @@
       <c r="B1150" s="1">
         <v>0</v>
       </c>
-      <c r="C1150" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1150" s="1"/>
       <c r="D1150" s="1"/>
     </row>
     <row r="1151" spans="1:4">
@@ -17741,9 +17770,7 @@
       <c r="B1151" s="1">
         <v>0</v>
       </c>
-      <c r="C1151" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1151" s="1"/>
       <c r="D1151" s="1"/>
     </row>
     <row r="1152" spans="1:4">
@@ -17753,9 +17780,7 @@
       <c r="B1152" s="1">
         <v>0</v>
       </c>
-      <c r="C1152" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1152" s="1"/>
       <c r="D1152" s="1"/>
     </row>
     <row r="1153" spans="1:4">
@@ -17765,9 +17790,7 @@
       <c r="B1153" s="1">
         <v>0</v>
       </c>
-      <c r="C1153" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1153" s="1"/>
       <c r="D1153" s="1"/>
     </row>
     <row r="1154" spans="1:4">
@@ -17777,9 +17800,7 @@
       <c r="B1154" s="1">
         <v>0</v>
       </c>
-      <c r="C1154" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1154" s="1"/>
       <c r="D1154" s="1"/>
     </row>
     <row r="1155" spans="1:4">
@@ -17789,9 +17810,7 @@
       <c r="B1155" s="1">
         <v>0</v>
       </c>
-      <c r="C1155" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1155" s="1"/>
       <c r="D1155" s="1"/>
     </row>
     <row r="1156" spans="1:4">
@@ -17801,9 +17820,7 @@
       <c r="B1156" s="1">
         <v>0</v>
       </c>
-      <c r="C1156" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1156" s="1"/>
       <c r="D1156" s="1"/>
     </row>
     <row r="1157" spans="1:4">
@@ -17813,9 +17830,7 @@
       <c r="B1157" s="1">
         <v>0</v>
       </c>
-      <c r="C1157" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1157" s="1"/>
       <c r="D1157" s="1"/>
     </row>
     <row r="1158" spans="1:4">
@@ -17825,9 +17840,7 @@
       <c r="B1158" s="1">
         <v>0</v>
       </c>
-      <c r="C1158" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1158" s="1"/>
       <c r="D1158" s="1"/>
     </row>
     <row r="1159" spans="1:4">
@@ -17837,9 +17850,7 @@
       <c r="B1159" s="1">
         <v>0</v>
       </c>
-      <c r="C1159" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1159" s="1"/>
       <c r="D1159" s="1"/>
     </row>
     <row r="1160" spans="1:4">
@@ -17849,9 +17860,7 @@
       <c r="B1160" s="1">
         <v>0</v>
       </c>
-      <c r="C1160" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1160" s="1"/>
       <c r="D1160" s="1"/>
     </row>
     <row r="1161" spans="1:4">
@@ -17861,9 +17870,7 @@
       <c r="B1161" s="1">
         <v>0</v>
       </c>
-      <c r="C1161" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1161" s="1"/>
       <c r="D1161" s="1"/>
     </row>
     <row r="1162" spans="1:4">
@@ -17873,9 +17880,7 @@
       <c r="B1162" s="1">
         <v>0</v>
       </c>
-      <c r="C1162" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1162" s="1"/>
       <c r="D1162" s="1"/>
     </row>
     <row r="1163" spans="1:4">
@@ -17885,9 +17890,7 @@
       <c r="B1163" s="1">
         <v>0</v>
       </c>
-      <c r="C1163" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1163" s="1"/>
       <c r="D1163" s="1"/>
     </row>
     <row r="1164" spans="1:4">
@@ -17897,9 +17900,7 @@
       <c r="B1164" s="1">
         <v>0</v>
       </c>
-      <c r="C1164" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1164" s="1"/>
       <c r="D1164" s="1"/>
     </row>
     <row r="1165" spans="1:4">
@@ -17909,9 +17910,7 @@
       <c r="B1165" s="1">
         <v>0</v>
       </c>
-      <c r="C1165" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1165" s="1"/>
       <c r="D1165" s="1"/>
     </row>
     <row r="1166" spans="1:4">
@@ -17921,9 +17920,7 @@
       <c r="B1166" s="1">
         <v>0</v>
       </c>
-      <c r="C1166" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1166" s="1"/>
       <c r="D1166" s="1"/>
     </row>
     <row r="1167" spans="1:4">
@@ -17933,9 +17930,7 @@
       <c r="B1167" s="1">
         <v>0</v>
       </c>
-      <c r="C1167" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1167" s="1"/>
       <c r="D1167" s="1"/>
     </row>
     <row r="1168" spans="1:4">
@@ -17945,9 +17940,7 @@
       <c r="B1168" s="1">
         <v>0</v>
       </c>
-      <c r="C1168" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1168" s="1"/>
       <c r="D1168" s="1"/>
     </row>
     <row r="1169" spans="1:4">
@@ -17957,9 +17950,7 @@
       <c r="B1169" s="1">
         <v>0</v>
       </c>
-      <c r="C1169" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1169" s="1"/>
       <c r="D1169" s="1"/>
     </row>
     <row r="1170" spans="1:4">
@@ -17969,9 +17960,7 @@
       <c r="B1170" s="1">
         <v>0</v>
       </c>
-      <c r="C1170" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1170" s="1"/>
       <c r="D1170" s="1"/>
     </row>
     <row r="1171" spans="1:4">
@@ -17981,9 +17970,7 @@
       <c r="B1171" s="1">
         <v>0</v>
       </c>
-      <c r="C1171" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1171" s="1"/>
       <c r="D1171" s="1"/>
     </row>
     <row r="1172" spans="1:4">
@@ -17993,9 +17980,7 @@
       <c r="B1172" s="1">
         <v>0</v>
       </c>
-      <c r="C1172" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1172" s="1"/>
       <c r="D1172" s="1"/>
     </row>
     <row r="1173" spans="1:4">
@@ -18005,9 +17990,7 @@
       <c r="B1173" s="1">
         <v>0</v>
       </c>
-      <c r="C1173" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1173" s="1"/>
       <c r="D1173" s="1"/>
     </row>
     <row r="1174" spans="1:4">
@@ -18017,9 +18000,7 @@
       <c r="B1174" s="1">
         <v>0</v>
       </c>
-      <c r="C1174" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1174" s="1"/>
       <c r="D1174" s="1"/>
     </row>
     <row r="1175" spans="1:4">
@@ -18029,9 +18010,7 @@
       <c r="B1175" s="1">
         <v>0</v>
       </c>
-      <c r="C1175" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1175" s="1"/>
       <c r="D1175" s="1"/>
     </row>
     <row r="1176" spans="1:4">
@@ -18041,9 +18020,7 @@
       <c r="B1176" s="1">
         <v>0</v>
       </c>
-      <c r="C1176" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1176" s="1"/>
       <c r="D1176" s="1"/>
     </row>
     <row r="1177" spans="1:4">
@@ -18053,9 +18030,7 @@
       <c r="B1177" s="1">
         <v>0</v>
       </c>
-      <c r="C1177" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1177" s="1"/>
       <c r="D1177" s="1"/>
     </row>
     <row r="1178" spans="1:4">
@@ -18065,9 +18040,7 @@
       <c r="B1178" s="1">
         <v>0</v>
       </c>
-      <c r="C1178" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1178" s="1"/>
       <c r="D1178" s="1"/>
     </row>
     <row r="1179" spans="1:4">
@@ -18077,9 +18050,7 @@
       <c r="B1179" s="1">
         <v>0</v>
       </c>
-      <c r="C1179" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1179" s="1"/>
       <c r="D1179" s="1"/>
     </row>
     <row r="1180" spans="1:4">
@@ -18089,9 +18060,7 @@
       <c r="B1180" s="1">
         <v>0</v>
       </c>
-      <c r="C1180" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1180" s="1"/>
       <c r="D1180" s="1"/>
     </row>
     <row r="1181" spans="1:4">
@@ -18101,9 +18070,7 @@
       <c r="B1181" s="1">
         <v>0</v>
       </c>
-      <c r="C1181" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1181" s="1"/>
       <c r="D1181" s="1"/>
     </row>
     <row r="1182" spans="1:4">
@@ -18113,9 +18080,7 @@
       <c r="B1182" s="1">
         <v>0</v>
       </c>
-      <c r="C1182" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1182" s="1"/>
       <c r="D1182" s="1"/>
     </row>
     <row r="1183" spans="1:4">
@@ -18125,9 +18090,7 @@
       <c r="B1183" s="1">
         <v>0</v>
       </c>
-      <c r="C1183" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1183" s="1"/>
       <c r="D1183" s="1"/>
     </row>
     <row r="1184" spans="1:4">
@@ -18137,9 +18100,7 @@
       <c r="B1184" s="1">
         <v>0</v>
       </c>
-      <c r="C1184" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1184" s="1"/>
       <c r="D1184" s="1"/>
     </row>
     <row r="1185" spans="1:4">
@@ -18149,9 +18110,7 @@
       <c r="B1185" s="1">
         <v>0</v>
       </c>
-      <c r="C1185" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1185" s="1"/>
       <c r="D1185" s="1"/>
     </row>
     <row r="1186" spans="1:4">
@@ -18161,9 +18120,7 @@
       <c r="B1186" s="1">
         <v>0</v>
       </c>
-      <c r="C1186" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1186" s="1"/>
       <c r="D1186" s="1"/>
     </row>
     <row r="1187" spans="1:4">
@@ -18173,9 +18130,7 @@
       <c r="B1187" s="1">
         <v>0</v>
       </c>
-      <c r="C1187" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1187" s="1"/>
       <c r="D1187" s="1"/>
     </row>
     <row r="1188" spans="1:4">
@@ -18185,9 +18140,7 @@
       <c r="B1188" s="1">
         <v>0</v>
       </c>
-      <c r="C1188" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1188" s="1"/>
       <c r="D1188" s="1"/>
     </row>
     <row r="1189" spans="1:4">
@@ -18197,9 +18150,7 @@
       <c r="B1189" s="1">
         <v>0</v>
       </c>
-      <c r="C1189" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1189" s="1"/>
       <c r="D1189" s="1"/>
     </row>
     <row r="1190" spans="1:4">
@@ -18209,9 +18160,7 @@
       <c r="B1190" s="1">
         <v>0</v>
       </c>
-      <c r="C1190" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1190" s="1"/>
       <c r="D1190" s="1"/>
     </row>
     <row r="1191" spans="1:4">
@@ -18221,9 +18170,7 @@
       <c r="B1191" s="1">
         <v>0</v>
       </c>
-      <c r="C1191" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1191" s="1"/>
       <c r="D1191" s="1"/>
     </row>
     <row r="1192" spans="1:4">
@@ -18233,9 +18180,7 @@
       <c r="B1192" s="1">
         <v>0</v>
       </c>
-      <c r="C1192" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1192" s="1"/>
       <c r="D1192" s="1"/>
     </row>
     <row r="1193" spans="1:4">
@@ -18245,9 +18190,7 @@
       <c r="B1193" s="1">
         <v>0</v>
       </c>
-      <c r="C1193" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1193" s="1"/>
       <c r="D1193" s="1"/>
     </row>
     <row r="1194" spans="1:4">
@@ -18257,9 +18200,7 @@
       <c r="B1194" s="1">
         <v>0</v>
       </c>
-      <c r="C1194" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1194" s="1"/>
       <c r="D1194" s="1"/>
     </row>
     <row r="1195" spans="1:4">
@@ -18269,9 +18210,7 @@
       <c r="B1195" s="1">
         <v>0</v>
       </c>
-      <c r="C1195" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1195" s="1"/>
       <c r="D1195" s="1"/>
     </row>
     <row r="1196" spans="1:4">
@@ -18281,9 +18220,7 @@
       <c r="B1196" s="1">
         <v>0</v>
       </c>
-      <c r="C1196" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1196" s="1"/>
       <c r="D1196" s="1"/>
     </row>
     <row r="1197" spans="1:4">
@@ -18293,9 +18230,7 @@
       <c r="B1197" s="1">
         <v>0</v>
       </c>
-      <c r="C1197" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1197" s="1"/>
       <c r="D1197" s="1"/>
     </row>
     <row r="1198" spans="1:4">
@@ -18305,9 +18240,7 @@
       <c r="B1198" s="1">
         <v>0</v>
       </c>
-      <c r="C1198" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1198" s="1"/>
       <c r="D1198" s="1"/>
     </row>
     <row r="1199" spans="1:4">
@@ -18317,9 +18250,7 @@
       <c r="B1199" s="1">
         <v>0</v>
       </c>
-      <c r="C1199" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1199" s="1"/>
       <c r="D1199" s="1"/>
     </row>
     <row r="1200" spans="1:4">
@@ -18329,9 +18260,7 @@
       <c r="B1200" s="1">
         <v>0</v>
       </c>
-      <c r="C1200" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1200" s="1"/>
       <c r="D1200" s="1"/>
     </row>
     <row r="1201" spans="1:4">
@@ -18341,9 +18270,7 @@
       <c r="B1201" s="1">
         <v>0</v>
       </c>
-      <c r="C1201" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1201" s="1"/>
       <c r="D1201" s="1"/>
     </row>
     <row r="1202" spans="1:4">
@@ -18353,9 +18280,7 @@
       <c r="B1202" s="1">
         <v>0</v>
       </c>
-      <c r="C1202" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1202" s="1"/>
       <c r="D1202" s="1"/>
     </row>
     <row r="1203" spans="1:4">
@@ -18365,9 +18290,7 @@
       <c r="B1203" s="1">
         <v>0</v>
       </c>
-      <c r="C1203" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1203" s="1"/>
       <c r="D1203" s="1"/>
     </row>
     <row r="1204" spans="1:4">
@@ -18377,9 +18300,7 @@
       <c r="B1204" s="1">
         <v>0</v>
       </c>
-      <c r="C1204" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1204" s="1"/>
       <c r="D1204" s="1"/>
     </row>
     <row r="1205" spans="1:4">
@@ -18389,9 +18310,7 @@
       <c r="B1205" s="1">
         <v>0</v>
       </c>
-      <c r="C1205" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1205" s="1"/>
       <c r="D1205" s="1"/>
     </row>
     <row r="1206" spans="1:4">
@@ -18401,9 +18320,7 @@
       <c r="B1206" s="1">
         <v>0</v>
       </c>
-      <c r="C1206" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1206" s="1"/>
       <c r="D1206" s="1"/>
     </row>
     <row r="1207" spans="1:4">
@@ -18413,9 +18330,7 @@
       <c r="B1207" s="1">
         <v>0</v>
       </c>
-      <c r="C1207" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1207" s="1"/>
       <c r="D1207" s="1"/>
     </row>
     <row r="1208" spans="1:4">
@@ -18425,9 +18340,7 @@
       <c r="B1208" s="1">
         <v>0</v>
       </c>
-      <c r="C1208" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1208" s="1"/>
       <c r="D1208" s="1"/>
     </row>
     <row r="1209" spans="1:4">
@@ -18437,9 +18350,7 @@
       <c r="B1209" s="1">
         <v>0</v>
       </c>
-      <c r="C1209" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1209" s="1"/>
       <c r="D1209" s="1"/>
     </row>
     <row r="1210" spans="1:4">
@@ -18449,9 +18360,7 @@
       <c r="B1210" s="1">
         <v>0</v>
       </c>
-      <c r="C1210" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1210" s="1"/>
       <c r="D1210" s="1"/>
     </row>
     <row r="1211" spans="1:4">
@@ -18461,9 +18370,7 @@
       <c r="B1211" s="1">
         <v>0</v>
       </c>
-      <c r="C1211" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1211" s="1"/>
       <c r="D1211" s="1"/>
     </row>
     <row r="1212" spans="1:4">
@@ -18473,9 +18380,7 @@
       <c r="B1212" s="1">
         <v>0</v>
       </c>
-      <c r="C1212" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1212" s="1"/>
       <c r="D1212" s="1"/>
     </row>
     <row r="1213" spans="1:4">
@@ -18485,9 +18390,7 @@
       <c r="B1213" s="1">
         <v>0</v>
       </c>
-      <c r="C1213" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1213" s="1"/>
       <c r="D1213" s="1"/>
     </row>
     <row r="1214" spans="1:4">
@@ -18497,9 +18400,7 @@
       <c r="B1214" s="1">
         <v>0</v>
       </c>
-      <c r="C1214" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1214" s="1"/>
       <c r="D1214" s="1"/>
     </row>
     <row r="1215" spans="1:4">
@@ -18509,9 +18410,7 @@
       <c r="B1215" s="1">
         <v>0</v>
       </c>
-      <c r="C1215" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1215" s="1"/>
       <c r="D1215" s="1"/>
     </row>
     <row r="1216" spans="1:4">
@@ -18521,9 +18420,7 @@
       <c r="B1216" s="1">
         <v>0</v>
       </c>
-      <c r="C1216" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1216" s="1"/>
       <c r="D1216" s="1"/>
     </row>
     <row r="1217" spans="1:4">
@@ -18533,9 +18430,7 @@
       <c r="B1217" s="1">
         <v>0</v>
       </c>
-      <c r="C1217" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1217" s="1"/>
       <c r="D1217" s="1"/>
     </row>
     <row r="1218" spans="1:4">
@@ -18545,9 +18440,7 @@
       <c r="B1218" s="1">
         <v>0</v>
       </c>
-      <c r="C1218" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1218" s="1"/>
       <c r="D1218" s="1"/>
     </row>
     <row r="1219" spans="1:4">
@@ -18557,9 +18450,7 @@
       <c r="B1219" s="1">
         <v>0</v>
       </c>
-      <c r="C1219" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1219" s="1"/>
       <c r="D1219" s="1"/>
     </row>
     <row r="1220" spans="1:4">
@@ -18569,9 +18460,7 @@
       <c r="B1220" s="1">
         <v>0</v>
       </c>
-      <c r="C1220" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1220" s="1"/>
       <c r="D1220" s="1"/>
     </row>
     <row r="1221" spans="1:4">
@@ -18581,9 +18470,7 @@
       <c r="B1221" s="1">
         <v>0</v>
       </c>
-      <c r="C1221" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1221" s="1"/>
       <c r="D1221" s="1"/>
     </row>
     <row r="1222" spans="1:4">
@@ -18593,9 +18480,7 @@
       <c r="B1222" s="1">
         <v>0</v>
       </c>
-      <c r="C1222" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1222" s="1"/>
       <c r="D1222" s="1"/>
     </row>
     <row r="1223" spans="1:4">
@@ -18605,9 +18490,7 @@
       <c r="B1223" s="1">
         <v>0</v>
       </c>
-      <c r="C1223" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1223" s="1"/>
       <c r="D1223" s="1"/>
     </row>
     <row r="1224" spans="1:4">
@@ -18617,9 +18500,7 @@
       <c r="B1224" s="1">
         <v>0</v>
       </c>
-      <c r="C1224" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1224" s="1"/>
       <c r="D1224" s="1"/>
     </row>
     <row r="1225" spans="1:4">
@@ -18629,9 +18510,7 @@
       <c r="B1225" s="1">
         <v>0</v>
       </c>
-      <c r="C1225" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1225" s="1"/>
       <c r="D1225" s="1"/>
     </row>
     <row r="1226" spans="1:4">
@@ -18641,9 +18520,7 @@
       <c r="B1226" s="1">
         <v>0</v>
       </c>
-      <c r="C1226" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1226" s="1"/>
       <c r="D1226" s="1"/>
     </row>
     <row r="1227" spans="1:4">
@@ -18653,9 +18530,7 @@
       <c r="B1227" s="1">
         <v>0</v>
       </c>
-      <c r="C1227" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1227" s="1"/>
       <c r="D1227" s="1"/>
     </row>
     <row r="1228" spans="1:4">
@@ -18665,9 +18540,7 @@
       <c r="B1228" s="1">
         <v>0</v>
       </c>
-      <c r="C1228" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1228" s="1"/>
       <c r="D1228" s="1"/>
     </row>
     <row r="1229" spans="1:4">
@@ -18677,9 +18550,7 @@
       <c r="B1229" s="1">
         <v>0</v>
       </c>
-      <c r="C1229" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1229" s="1"/>
       <c r="D1229" s="1"/>
     </row>
     <row r="1230" spans="1:4">
@@ -18689,9 +18560,7 @@
       <c r="B1230" s="1">
         <v>0</v>
       </c>
-      <c r="C1230" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1230" s="1"/>
       <c r="D1230" s="1"/>
     </row>
     <row r="1231" spans="1:4">
@@ -18701,9 +18570,7 @@
       <c r="B1231" s="1">
         <v>0</v>
       </c>
-      <c r="C1231" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1231" s="1"/>
       <c r="D1231" s="1"/>
     </row>
     <row r="1232" spans="1:4">
@@ -18713,9 +18580,7 @@
       <c r="B1232" s="1">
         <v>0</v>
       </c>
-      <c r="C1232" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1232" s="1"/>
       <c r="D1232" s="1"/>
     </row>
     <row r="1233" spans="1:4">
@@ -18725,9 +18590,7 @@
       <c r="B1233" s="1">
         <v>0</v>
       </c>
-      <c r="C1233" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1233" s="1"/>
       <c r="D1233" s="1"/>
     </row>
     <row r="1234" spans="1:4">
@@ -18737,9 +18600,7 @@
       <c r="B1234" s="1">
         <v>0</v>
       </c>
-      <c r="C1234" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1234" s="1"/>
       <c r="D1234" s="1"/>
     </row>
     <row r="1235" spans="1:4">
@@ -18749,9 +18610,7 @@
       <c r="B1235" s="1">
         <v>0</v>
       </c>
-      <c r="C1235" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1235" s="1"/>
       <c r="D1235" s="1"/>
     </row>
     <row r="1236" spans="1:4">
@@ -18761,9 +18620,7 @@
       <c r="B1236" s="1">
         <v>0</v>
       </c>
-      <c r="C1236" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1236" s="1"/>
       <c r="D1236" s="1"/>
     </row>
     <row r="1237" spans="1:4">
@@ -18773,9 +18630,7 @@
       <c r="B1237" s="1">
         <v>0</v>
       </c>
-      <c r="C1237" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1237" s="1"/>
       <c r="D1237" s="1"/>
     </row>
     <row r="1238" spans="1:4">
@@ -18785,9 +18640,7 @@
       <c r="B1238" s="1">
         <v>0</v>
       </c>
-      <c r="C1238" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1238" s="1"/>
       <c r="D1238" s="1"/>
     </row>
     <row r="1239" spans="1:4">
@@ -18797,9 +18650,7 @@
       <c r="B1239" s="1">
         <v>0</v>
       </c>
-      <c r="C1239" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1239" s="1"/>
       <c r="D1239" s="1"/>
     </row>
     <row r="1240" spans="1:4">
@@ -18809,9 +18660,7 @@
       <c r="B1240" s="1">
         <v>0</v>
       </c>
-      <c r="C1240" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1240" s="1"/>
       <c r="D1240" s="1"/>
     </row>
     <row r="1241" spans="1:4">
@@ -18821,9 +18670,7 @@
       <c r="B1241" s="1">
         <v>0</v>
       </c>
-      <c r="C1241" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1241" s="1"/>
       <c r="D1241" s="1"/>
     </row>
     <row r="1242" spans="1:4">
@@ -18833,9 +18680,7 @@
       <c r="B1242" s="1">
         <v>0</v>
       </c>
-      <c r="C1242" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1242" s="1"/>
       <c r="D1242" s="1"/>
     </row>
     <row r="1243" spans="1:4">
@@ -18845,9 +18690,7 @@
       <c r="B1243" s="1">
         <v>0</v>
       </c>
-      <c r="C1243" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1243" s="1"/>
       <c r="D1243" s="1"/>
     </row>
     <row r="1244" spans="1:4">
@@ -18857,9 +18700,7 @@
       <c r="B1244" s="1">
         <v>0</v>
       </c>
-      <c r="C1244" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1244" s="1"/>
       <c r="D1244" s="1"/>
     </row>
     <row r="1245" spans="1:4">
@@ -18869,9 +18710,7 @@
       <c r="B1245" s="1">
         <v>0</v>
       </c>
-      <c r="C1245" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1245" s="1"/>
       <c r="D1245" s="1"/>
     </row>
     <row r="1246" spans="1:4">
@@ -18881,9 +18720,7 @@
       <c r="B1246" s="1">
         <v>0</v>
       </c>
-      <c r="C1246" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1246" s="1"/>
       <c r="D1246" s="1"/>
     </row>
     <row r="1247" spans="1:4">
@@ -18893,9 +18730,7 @@
       <c r="B1247" s="1">
         <v>0</v>
       </c>
-      <c r="C1247" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1247" s="1"/>
       <c r="D1247" s="1"/>
     </row>
     <row r="1248" spans="1:4">
@@ -18905,9 +18740,7 @@
       <c r="B1248" s="1">
         <v>0</v>
       </c>
-      <c r="C1248" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1248" s="1"/>
       <c r="D1248" s="1"/>
     </row>
     <row r="1249" spans="1:4">
@@ -18917,9 +18750,7 @@
       <c r="B1249" s="1">
         <v>0</v>
       </c>
-      <c r="C1249" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1249" s="1"/>
       <c r="D1249" s="1"/>
     </row>
     <row r="1250" spans="1:4">
@@ -18929,9 +18760,7 @@
       <c r="B1250" s="1">
         <v>0</v>
       </c>
-      <c r="C1250" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1250" s="1"/>
       <c r="D1250" s="1"/>
     </row>
     <row r="1251" spans="1:4">
@@ -18941,9 +18770,7 @@
       <c r="B1251" s="1">
         <v>0</v>
       </c>
-      <c r="C1251" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1251" s="1"/>
       <c r="D1251" s="1"/>
     </row>
     <row r="1252" spans="1:4">
@@ -18953,9 +18780,7 @@
       <c r="B1252" s="1">
         <v>0</v>
       </c>
-      <c r="C1252" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1252" s="1"/>
       <c r="D1252" s="1"/>
     </row>
     <row r="1253" spans="1:4">
@@ -18965,9 +18790,7 @@
       <c r="B1253" s="1">
         <v>0</v>
       </c>
-      <c r="C1253" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1253" s="1"/>
       <c r="D1253" s="1"/>
     </row>
     <row r="1254" spans="1:4">
@@ -18977,9 +18800,7 @@
       <c r="B1254" s="1">
         <v>0</v>
       </c>
-      <c r="C1254" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1254" s="1"/>
       <c r="D1254" s="1"/>
     </row>
     <row r="1255" spans="1:4">
@@ -18989,9 +18810,7 @@
       <c r="B1255" s="1">
         <v>0</v>
       </c>
-      <c r="C1255" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1255" s="1"/>
       <c r="D1255" s="1"/>
     </row>
     <row r="1256" spans="1:4">
@@ -19001,9 +18820,7 @@
       <c r="B1256" s="1">
         <v>0</v>
       </c>
-      <c r="C1256" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1256" s="1"/>
       <c r="D1256" s="1"/>
     </row>
     <row r="1257" spans="1:4">
@@ -19013,9 +18830,7 @@
       <c r="B1257" s="1">
         <v>0</v>
       </c>
-      <c r="C1257" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1257" s="1"/>
       <c r="D1257" s="1"/>
     </row>
     <row r="1258" spans="1:4">
@@ -19025,9 +18840,7 @@
       <c r="B1258" s="1">
         <v>0</v>
       </c>
-      <c r="C1258" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1258" s="1"/>
       <c r="D1258" s="1"/>
     </row>
     <row r="1259" spans="1:4">
@@ -19037,9 +18850,7 @@
       <c r="B1259" s="1">
         <v>0</v>
       </c>
-      <c r="C1259" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1259" s="1"/>
       <c r="D1259" s="1"/>
     </row>
     <row r="1260" spans="1:4">
@@ -19049,9 +18860,7 @@
       <c r="B1260" s="1">
         <v>0</v>
       </c>
-      <c r="C1260" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1260" s="1"/>
       <c r="D1260" s="1"/>
     </row>
     <row r="1261" spans="1:4">
@@ -19061,9 +18870,7 @@
       <c r="B1261" s="1">
         <v>0</v>
       </c>
-      <c r="C1261" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1261" s="1"/>
       <c r="D1261" s="1"/>
     </row>
     <row r="1262" spans="1:4">
@@ -19073,9 +18880,7 @@
       <c r="B1262" s="1">
         <v>0</v>
       </c>
-      <c r="C1262" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1262" s="1"/>
       <c r="D1262" s="1"/>
     </row>
     <row r="1263" spans="1:4">
@@ -19085,9 +18890,7 @@
       <c r="B1263" s="1">
         <v>0</v>
       </c>
-      <c r="C1263" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1263" s="1"/>
       <c r="D1263" s="1"/>
     </row>
     <row r="1264" spans="1:4">
@@ -19097,9 +18900,7 @@
       <c r="B1264" s="1">
         <v>0</v>
       </c>
-      <c r="C1264" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1264" s="1"/>
       <c r="D1264" s="1"/>
     </row>
     <row r="1265" spans="1:4">
@@ -19109,9 +18910,7 @@
       <c r="B1265" s="1">
         <v>0</v>
       </c>
-      <c r="C1265" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1265" s="1"/>
       <c r="D1265" s="1"/>
     </row>
     <row r="1266" spans="1:4">
@@ -19121,9 +18920,7 @@
       <c r="B1266" s="1">
         <v>0</v>
       </c>
-      <c r="C1266" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1266" s="1"/>
       <c r="D1266" s="1"/>
     </row>
     <row r="1267" spans="1:4">
@@ -19133,9 +18930,7 @@
       <c r="B1267" s="1">
         <v>0</v>
       </c>
-      <c r="C1267" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1267" s="1"/>
       <c r="D1267" s="1"/>
     </row>
     <row r="1268" spans="1:4">
@@ -19145,9 +18940,7 @@
       <c r="B1268" s="1">
         <v>0</v>
       </c>
-      <c r="C1268" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1268" s="1"/>
       <c r="D1268" s="1"/>
     </row>
     <row r="1269" spans="1:4">
@@ -19157,9 +18950,7 @@
       <c r="B1269" s="1">
         <v>0</v>
       </c>
-      <c r="C1269" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1269" s="1"/>
       <c r="D1269" s="1"/>
     </row>
     <row r="1270" spans="1:4">
@@ -19169,9 +18960,7 @@
       <c r="B1270" s="1">
         <v>0</v>
       </c>
-      <c r="C1270" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1270" s="1"/>
       <c r="D1270" s="1"/>
     </row>
     <row r="1271" spans="1:4">
@@ -19181,9 +18970,7 @@
       <c r="B1271" s="1">
         <v>0</v>
       </c>
-      <c r="C1271" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1271" s="1"/>
       <c r="D1271" s="1"/>
     </row>
     <row r="1272" spans="1:4">
@@ -19193,9 +18980,7 @@
       <c r="B1272" s="1">
         <v>0</v>
       </c>
-      <c r="C1272" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1272" s="1"/>
       <c r="D1272" s="1"/>
     </row>
     <row r="1273" spans="1:4">
@@ -19205,9 +18990,7 @@
       <c r="B1273" s="1">
         <v>0</v>
       </c>
-      <c r="C1273" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1273" s="1"/>
       <c r="D1273" s="1"/>
     </row>
     <row r="1274" spans="1:4">
@@ -19217,9 +19000,7 @@
       <c r="B1274" s="1">
         <v>0</v>
       </c>
-      <c r="C1274" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1274" s="1"/>
       <c r="D1274" s="1"/>
     </row>
     <row r="1275" spans="1:4">
@@ -19229,9 +19010,7 @@
       <c r="B1275" s="1">
         <v>0</v>
       </c>
-      <c r="C1275" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1275" s="1"/>
       <c r="D1275" s="1"/>
     </row>
     <row r="1276" spans="1:4">
@@ -19241,9 +19020,7 @@
       <c r="B1276" s="1">
         <v>0</v>
       </c>
-      <c r="C1276" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1276" s="1"/>
       <c r="D1276" s="1"/>
     </row>
     <row r="1277" spans="1:4">
@@ -19253,9 +19030,7 @@
       <c r="B1277" s="1">
         <v>0</v>
       </c>
-      <c r="C1277" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1277" s="1"/>
       <c r="D1277" s="1"/>
     </row>
     <row r="1278" spans="1:4">
@@ -19265,9 +19040,7 @@
       <c r="B1278" s="1">
         <v>0</v>
       </c>
-      <c r="C1278" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1278" s="1"/>
       <c r="D1278" s="1"/>
     </row>
     <row r="1279" spans="1:4">
@@ -19277,9 +19050,7 @@
       <c r="B1279" s="1">
         <v>0</v>
       </c>
-      <c r="C1279" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1279" s="1"/>
       <c r="D1279" s="1"/>
     </row>
     <row r="1280" spans="1:4">
@@ -19289,9 +19060,7 @@
       <c r="B1280" s="1">
         <v>0</v>
       </c>
-      <c r="C1280" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1280" s="1"/>
       <c r="D1280" s="1"/>
     </row>
     <row r="1281" spans="1:4">
@@ -19301,9 +19070,7 @@
       <c r="B1281" s="1">
         <v>0</v>
       </c>
-      <c r="C1281" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1281" s="1"/>
       <c r="D1281" s="1"/>
     </row>
     <row r="1282" spans="1:4">
@@ -19313,9 +19080,7 @@
       <c r="B1282" s="1">
         <v>0</v>
       </c>
-      <c r="C1282" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1282" s="1"/>
       <c r="D1282" s="1"/>
     </row>
     <row r="1283" spans="1:4">
@@ -19325,9 +19090,7 @@
       <c r="B1283" s="1">
         <v>0</v>
       </c>
-      <c r="C1283" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1283" s="1"/>
       <c r="D1283" s="1"/>
     </row>
     <row r="1284" spans="1:4">
@@ -19337,9 +19100,7 @@
       <c r="B1284" s="1">
         <v>0</v>
       </c>
-      <c r="C1284" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1284" s="1"/>
       <c r="D1284" s="1"/>
     </row>
     <row r="1285" spans="1:4">
@@ -19349,9 +19110,7 @@
       <c r="B1285" s="1">
         <v>0</v>
       </c>
-      <c r="C1285" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1285" s="1"/>
       <c r="D1285" s="1"/>
     </row>
     <row r="1286" spans="1:4">
@@ -19361,9 +19120,7 @@
       <c r="B1286" s="1">
         <v>0</v>
       </c>
-      <c r="C1286" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1286" s="1"/>
       <c r="D1286" s="1"/>
     </row>
     <row r="1287" spans="1:4">
@@ -19373,9 +19130,7 @@
       <c r="B1287" s="1">
         <v>0</v>
       </c>
-      <c r="C1287" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1287" s="1"/>
       <c r="D1287" s="1"/>
     </row>
     <row r="1288" spans="1:4">
@@ -19385,9 +19140,7 @@
       <c r="B1288" s="1">
         <v>0</v>
       </c>
-      <c r="C1288" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1288" s="1"/>
       <c r="D1288" s="1"/>
     </row>
     <row r="1289" spans="1:4">
@@ -19397,9 +19150,7 @@
       <c r="B1289" s="1">
         <v>0</v>
       </c>
-      <c r="C1289" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1289" s="1"/>
       <c r="D1289" s="1"/>
     </row>
     <row r="1290" spans="1:4">
@@ -19409,9 +19160,7 @@
       <c r="B1290" s="1">
         <v>0</v>
       </c>
-      <c r="C1290" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1290" s="1"/>
       <c r="D1290" s="1"/>
     </row>
     <row r="1291" spans="1:4">
@@ -19421,9 +19170,7 @@
       <c r="B1291" s="1">
         <v>0</v>
       </c>
-      <c r="C1291" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1291" s="1"/>
       <c r="D1291" s="1"/>
     </row>
     <row r="1292" spans="1:4">
@@ -19433,9 +19180,7 @@
       <c r="B1292" s="1">
         <v>0</v>
       </c>
-      <c r="C1292" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1292" s="1"/>
       <c r="D1292" s="1"/>
     </row>
     <row r="1293" spans="1:4">
@@ -19445,9 +19190,7 @@
       <c r="B1293" s="1">
         <v>0</v>
       </c>
-      <c r="C1293" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1293" s="1"/>
       <c r="D1293" s="1"/>
     </row>
     <row r="1294" spans="1:4">
@@ -19457,9 +19200,7 @@
       <c r="B1294" s="1">
         <v>0</v>
       </c>
-      <c r="C1294" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1294" s="1"/>
       <c r="D1294" s="1"/>
     </row>
     <row r="1295" spans="1:4">
@@ -19469,9 +19210,7 @@
       <c r="B1295" s="1">
         <v>0</v>
       </c>
-      <c r="C1295" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1295" s="1"/>
       <c r="D1295" s="1"/>
     </row>
     <row r="1296" spans="1:4">
@@ -19481,9 +19220,7 @@
       <c r="B1296" s="1">
         <v>0</v>
       </c>
-      <c r="C1296" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1296" s="1"/>
       <c r="D1296" s="1"/>
     </row>
     <row r="1297" spans="1:4">
@@ -19493,9 +19230,7 @@
       <c r="B1297" s="1">
         <v>0</v>
       </c>
-      <c r="C1297" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1297" s="1"/>
       <c r="D1297" s="1"/>
     </row>
     <row r="1298" spans="1:4">
@@ -19505,9 +19240,7 @@
       <c r="B1298" s="1">
         <v>0</v>
       </c>
-      <c r="C1298" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1298" s="1"/>
       <c r="D1298" s="1"/>
     </row>
     <row r="1299" spans="1:4">
@@ -19517,9 +19250,7 @@
       <c r="B1299" s="1">
         <v>0</v>
       </c>
-      <c r="C1299" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1299" s="1"/>
       <c r="D1299" s="1"/>
     </row>
     <row r="1300" spans="1:4">
@@ -19529,9 +19260,7 @@
       <c r="B1300" s="1">
         <v>0</v>
       </c>
-      <c r="C1300" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1300" s="1"/>
       <c r="D1300" s="1"/>
     </row>
     <row r="1301" spans="1:4">
@@ -19541,9 +19270,7 @@
       <c r="B1301" s="1">
         <v>0</v>
       </c>
-      <c r="C1301" s="1">
-        <v>0</v>
-      </c>
+      <c r="C1301" s="1"/>
       <c r="D1301" s="1"/>
     </row>
   </sheetData>
